--- a/xlsx/dre/DRE_03_2026.xlsx
+++ b/xlsx/dre/DRE_03_2026.xlsx
@@ -588,21 +588,6 @@
     <t>R$  4.689,29</t>
   </si>
   <si>
-    <t>12/1</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  736,71</t>
-  </si>
-  <si>
-    <t>23/04/26</t>
-  </si>
-  <si>
-    <t>Digisac</t>
-  </si>
-  <si>
     <t>5/1</t>
   </si>
   <si>
@@ -614,6 +599,21 @@
   <si>
     <t xml:space="preserve">Reembolso Pushing
 </t>
+  </si>
+  <si>
+    <t>12/1</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  736,71</t>
+  </si>
+  <si>
+    <t>23/04/26</t>
+  </si>
+  <si>
+    <t>Digisac</t>
   </si>
   <si>
     <t>9/1</t>
@@ -2190,9 +2190,36 @@
     <t>R$ 9.161,99</t>
   </si>
   <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.588,50</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
     <t>12/3</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>01/03/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
@@ -2202,21 +2229,6 @@
     <t>Google 2026</t>
   </si>
   <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>01/03/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
     <t>1/1</t>
   </si>
   <si>
@@ -2232,18 +2244,6 @@
     <t>Facebook 2026</t>
   </si>
   <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.588,50</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
     <t>4.03.03.09.06 Marketing - outros gastos (CV)</t>
   </si>
   <si>
@@ -2625,6 +2625,18 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
+    <t>595/1</t>
+  </si>
+  <si>
+    <t>Oxxo</t>
+  </si>
+  <si>
+    <t>R$  110,94</t>
+  </si>
+  <si>
+    <t>Cafés loja</t>
+  </si>
+  <si>
     <t>593/1</t>
   </si>
   <si>
@@ -2641,18 +2653,6 @@
   </si>
   <si>
     <t>R$  19,98</t>
-  </si>
-  <si>
-    <t>595/1</t>
-  </si>
-  <si>
-    <t>Oxxo</t>
-  </si>
-  <si>
-    <t>R$  110,94</t>
-  </si>
-  <si>
-    <t>Cafés loja</t>
   </si>
   <si>
     <t>569/1</t>
@@ -2741,6 +2741,21 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>3/2</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>592/1</t>
   </si>
   <si>
@@ -2759,21 +2774,6 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>3/2</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
-  </si>
-  <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
   </si>
   <si>
@@ -2840,6 +2840,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
+    <t>R$  150,00</t>
+  </si>
+  <si>
+    <t>Segurança 2026</t>
+  </si>
+  <si>
     <t>VERISURE</t>
   </si>
   <si>
@@ -2847,15 +2856,6 @@
   </si>
   <si>
     <t>Verisure - Alarme 2026</t>
-  </si>
-  <si>
-    <t>Jackson Fernando de Araujo</t>
-  </si>
-  <si>
-    <t>R$  150,00</t>
-  </si>
-  <si>
-    <t>Segurança 2026</t>
   </si>
   <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
@@ -6022,13 +6022,13 @@
         <v>193</v>
       </c>
       <c r="J61" t="s">
+        <v>83</v>
+      </c>
+      <c r="K61" t="s">
+        <v>67</v>
+      </c>
+      <c r="L61" t="s">
         <v>194</v>
-      </c>
-      <c r="K61" t="s">
-        <v>133</v>
-      </c>
-      <c r="L61" t="s">
-        <v>195</v>
       </c>
       <c r="M61" t="s">
         <v>183</v>
@@ -6063,7 +6063,7 @@
         <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F62" t="s">
         <v>64</v>
@@ -6072,16 +6072,16 @@
         <v>41</v>
       </c>
       <c r="H62" t="s">
+        <v>196</v>
+      </c>
+      <c r="I62" t="s">
         <v>197</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>198</v>
       </c>
-      <c r="J62" t="s">
-        <v>83</v>
-      </c>
       <c r="K62" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="L62" t="s">
         <v>199</v>
@@ -6096,7 +6096,7 @@
         <v>48</v>
       </c>
       <c r="P62" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q62" t="s">
         <v>47</v>
@@ -6128,7 +6128,7 @@
         <v>41</v>
       </c>
       <c r="H63" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I63" t="s">
         <v>201</v>
@@ -6302,7 +6302,7 @@
         <v>210</v>
       </c>
       <c r="J66" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K66" t="s">
         <v>159</v>
@@ -18224,7 +18224,7 @@
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I279" t="s">
         <v>581</v>
@@ -18280,7 +18280,7 @@
         <v>41</v>
       </c>
       <c r="H280" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I280" t="s">
         <v>494</v>
@@ -18336,7 +18336,7 @@
         <v>41</v>
       </c>
       <c r="H281" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I281" t="s">
         <v>550</v>
@@ -18392,7 +18392,7 @@
         <v>41</v>
       </c>
       <c r="H282" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I282" t="s">
         <v>489</v>
@@ -18504,7 +18504,7 @@
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I284" t="s">
         <v>585</v>
@@ -18560,7 +18560,7 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I285" t="s">
         <v>588</v>
@@ -18616,7 +18616,7 @@
         <v>41</v>
       </c>
       <c r="H286" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I286" t="s">
         <v>589</v>
@@ -18672,7 +18672,7 @@
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I287" t="s">
         <v>590</v>
@@ -18728,7 +18728,7 @@
         <v>41</v>
       </c>
       <c r="H288" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I288" t="s">
         <v>591</v>
@@ -19400,7 +19400,7 @@
         <v>41</v>
       </c>
       <c r="H300" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I300" t="s">
         <v>612</v>
@@ -21967,7 +21967,7 @@
         <v>33</v>
       </c>
       <c r="E346" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F346" t="s">
         <v>40</v>
@@ -21982,10 +21982,10 @@
         <v>92</v>
       </c>
       <c r="J346" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="K346" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="L346" t="s">
         <v>34</v>
@@ -21997,7 +21997,7 @@
         <v>47</v>
       </c>
       <c r="O346" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="P346" t="s">
         <v>92</v>
@@ -22023,7 +22023,7 @@
         <v>34</v>
       </c>
       <c r="E347" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="F347" t="s">
         <v>40</v>
@@ -22053,7 +22053,7 @@
         <v>47</v>
       </c>
       <c r="O347" t="s">
-        <v>294</v>
+        <v>115</v>
       </c>
       <c r="P347" t="s">
         <v>92</v>
@@ -22135,10 +22135,10 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>250</v>
+        <v>531</v>
       </c>
       <c r="F349" t="s">
-        <v>40</v>
+        <v>709</v>
       </c>
       <c r="G349" t="s">
         <v>41</v>
@@ -22150,10 +22150,10 @@
         <v>92</v>
       </c>
       <c r="J349" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="K349" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="L349" t="s">
         <v>34</v>
@@ -22165,13 +22165,13 @@
         <v>47</v>
       </c>
       <c r="O349" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="P349" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="Q349" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R349" t="s">
         <v>34</v>
@@ -22191,7 +22191,7 @@
         <v>34</v>
       </c>
       <c r="E350" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="F350" t="s">
         <v>40</v>
@@ -22206,10 +22206,10 @@
         <v>92</v>
       </c>
       <c r="J350" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K350" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L350" t="s">
         <v>34</v>
@@ -22221,7 +22221,7 @@
         <v>47</v>
       </c>
       <c r="O350" t="s">
-        <v>169</v>
+        <v>294</v>
       </c>
       <c r="P350" t="s">
         <v>92</v>
@@ -22247,7 +22247,7 @@
         <v>34</v>
       </c>
       <c r="E351" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F351" t="s">
         <v>40</v>
@@ -22262,10 +22262,10 @@
         <v>92</v>
       </c>
       <c r="J351" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="K351" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L351" t="s">
         <v>34</v>
@@ -22277,7 +22277,7 @@
         <v>47</v>
       </c>
       <c r="O351" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="P351" t="s">
         <v>92</v>
@@ -22303,7 +22303,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="F352" t="s">
         <v>40</v>
@@ -22318,10 +22318,10 @@
         <v>92</v>
       </c>
       <c r="J352" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="K352" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L352" t="s">
         <v>34</v>
@@ -22333,7 +22333,7 @@
         <v>47</v>
       </c>
       <c r="O352" t="s">
-        <v>88</v>
+        <v>269</v>
       </c>
       <c r="P352" t="s">
         <v>92</v>
@@ -22415,7 +22415,7 @@
         <v>34</v>
       </c>
       <c r="E354" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="F354" t="s">
         <v>40</v>
@@ -22430,10 +22430,10 @@
         <v>92</v>
       </c>
       <c r="J354" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K354" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L354" t="s">
         <v>34</v>
@@ -22445,7 +22445,7 @@
         <v>47</v>
       </c>
       <c r="O354" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="P354" t="s">
         <v>92</v>
@@ -22471,10 +22471,10 @@
         <v>34</v>
       </c>
       <c r="E355" t="s">
-        <v>531</v>
+        <v>272</v>
       </c>
       <c r="F355" t="s">
-        <v>709</v>
+        <v>40</v>
       </c>
       <c r="G355" t="s">
         <v>41</v>
@@ -22486,10 +22486,10 @@
         <v>92</v>
       </c>
       <c r="J355" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K355" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="L355" t="s">
         <v>34</v>
@@ -22501,13 +22501,13 @@
         <v>47</v>
       </c>
       <c r="O355" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="P355" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="Q355" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R355" t="s">
         <v>34</v>
@@ -22527,7 +22527,7 @@
         <v>34</v>
       </c>
       <c r="E356" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F356" t="s">
         <v>40</v>
@@ -22542,10 +22542,10 @@
         <v>92</v>
       </c>
       <c r="J356" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K356" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="L356" t="s">
         <v>34</v>
@@ -22557,7 +22557,7 @@
         <v>47</v>
       </c>
       <c r="O356" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="P356" t="s">
         <v>92</v>
@@ -22639,7 +22639,7 @@
         <v>34</v>
       </c>
       <c r="E358" t="s">
-        <v>260</v>
+        <v>487</v>
       </c>
       <c r="F358" t="s">
         <v>40</v>
@@ -22654,10 +22654,10 @@
         <v>92</v>
       </c>
       <c r="J358" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K358" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="L358" t="s">
         <v>34</v>
@@ -22669,7 +22669,7 @@
         <v>47</v>
       </c>
       <c r="O358" t="s">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="P358" t="s">
         <v>92</v>
@@ -22695,7 +22695,7 @@
         <v>34</v>
       </c>
       <c r="E359" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="F359" t="s">
         <v>40</v>
@@ -22710,10 +22710,10 @@
         <v>92</v>
       </c>
       <c r="J359" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="K359" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="L359" t="s">
         <v>34</v>
@@ -22725,7 +22725,7 @@
         <v>47</v>
       </c>
       <c r="O359" t="s">
-        <v>269</v>
+        <v>98</v>
       </c>
       <c r="P359" t="s">
         <v>92</v>
@@ -22751,7 +22751,7 @@
         <v>34</v>
       </c>
       <c r="E360" t="s">
-        <v>487</v>
+        <v>260</v>
       </c>
       <c r="F360" t="s">
         <v>40</v>
@@ -22766,10 +22766,10 @@
         <v>92</v>
       </c>
       <c r="J360" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K360" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="L360" t="s">
         <v>34</v>
@@ -22781,7 +22781,7 @@
         <v>47</v>
       </c>
       <c r="O360" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="P360" t="s">
         <v>92</v>
@@ -22919,7 +22919,7 @@
         <v>33</v>
       </c>
       <c r="E363" t="s">
-        <v>720</v>
+        <v>227</v>
       </c>
       <c r="F363" t="s">
         <v>40</v>
@@ -22928,16 +22928,16 @@
         <v>41</v>
       </c>
       <c r="H363" t="s">
+        <v>720</v>
+      </c>
+      <c r="I363" t="s">
         <v>721</v>
       </c>
-      <c r="I363" t="s">
+      <c r="J363" t="s">
         <v>722</v>
       </c>
-      <c r="J363" t="s">
-        <v>369</v>
-      </c>
       <c r="K363" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="L363" t="s">
         <v>723</v>
@@ -22952,7 +22952,7 @@
         <v>48</v>
       </c>
       <c r="P363" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="Q363" t="s">
         <v>47</v>
@@ -22975,7 +22975,7 @@
         <v>34</v>
       </c>
       <c r="E364" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F364" t="s">
         <v>40</v>
@@ -22984,19 +22984,19 @@
         <v>41</v>
       </c>
       <c r="H364" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I364" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J364" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K364" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L364" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M364" t="s">
         <v>718</v>
@@ -23008,7 +23008,7 @@
         <v>48</v>
       </c>
       <c r="P364" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="Q364" t="s">
         <v>47</v>
@@ -23031,7 +23031,7 @@
         <v>34</v>
       </c>
       <c r="E365" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="F365" t="s">
         <v>40</v>
@@ -23046,13 +23046,13 @@
         <v>731</v>
       </c>
       <c r="J365" t="s">
-        <v>230</v>
+        <v>369</v>
       </c>
       <c r="K365" t="s">
+        <v>45</v>
+      </c>
+      <c r="L365" t="s">
         <v>732</v>
-      </c>
-      <c r="L365" t="s">
-        <v>733</v>
       </c>
       <c r="M365" t="s">
         <v>718</v>
@@ -23087,7 +23087,7 @@
         <v>34</v>
       </c>
       <c r="E366" t="s">
-        <v>227</v>
+        <v>733</v>
       </c>
       <c r="F366" t="s">
         <v>40</v>
@@ -23102,10 +23102,10 @@
         <v>735</v>
       </c>
       <c r="J366" t="s">
+        <v>230</v>
+      </c>
+      <c r="K366" t="s">
         <v>736</v>
-      </c>
-      <c r="K366" t="s">
-        <v>67</v>
       </c>
       <c r="L366" t="s">
         <v>737</v>
@@ -23367,7 +23367,7 @@
         <v>33</v>
       </c>
       <c r="E371" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F371" t="s">
         <v>40</v>
@@ -23382,7 +23382,7 @@
         <v>750</v>
       </c>
       <c r="J371" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K371" t="s">
         <v>45</v>
@@ -23591,7 +23591,7 @@
         <v>34</v>
       </c>
       <c r="E375" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="F375" t="s">
         <v>40</v>
@@ -23647,7 +23647,7 @@
         <v>34</v>
       </c>
       <c r="E376" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F376" t="s">
         <v>40</v>
@@ -23662,7 +23662,7 @@
         <v>761</v>
       </c>
       <c r="J376" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K376" t="s">
         <v>45</v>
@@ -23703,7 +23703,7 @@
         <v>34</v>
       </c>
       <c r="E377" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F377" t="s">
         <v>40</v>
@@ -23718,7 +23718,7 @@
         <v>750</v>
       </c>
       <c r="J377" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K377" t="s">
         <v>45</v>
@@ -23815,7 +23815,7 @@
         <v>34</v>
       </c>
       <c r="E379" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F379" t="s">
         <v>40</v>
@@ -23927,7 +23927,7 @@
         <v>34</v>
       </c>
       <c r="E381" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F381" t="s">
         <v>40</v>
@@ -23942,7 +23942,7 @@
         <v>774</v>
       </c>
       <c r="J381" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K381" t="s">
         <v>45</v>
@@ -23983,7 +23983,7 @@
         <v>34</v>
       </c>
       <c r="E382" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F382" t="s">
         <v>40</v>
@@ -23998,7 +23998,7 @@
         <v>777</v>
       </c>
       <c r="J382" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K382" t="s">
         <v>45</v>
@@ -24039,7 +24039,7 @@
         <v>34</v>
       </c>
       <c r="E383" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F383" t="s">
         <v>40</v>
@@ -24054,7 +24054,7 @@
         <v>780</v>
       </c>
       <c r="J383" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K383" t="s">
         <v>45</v>
@@ -24095,7 +24095,7 @@
         <v>34</v>
       </c>
       <c r="E384" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F384" t="s">
         <v>40</v>
@@ -24110,7 +24110,7 @@
         <v>782</v>
       </c>
       <c r="J384" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K384" t="s">
         <v>45</v>
@@ -24608,7 +24608,7 @@
         <v>41</v>
       </c>
       <c r="H393" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I393" t="s">
         <v>804</v>
@@ -24838,7 +24838,7 @@
         <v>813</v>
       </c>
       <c r="J397" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
       <c r="K397" t="s">
         <v>68</v>
@@ -25006,10 +25006,10 @@
         <v>822</v>
       </c>
       <c r="J400" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K400" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L400" t="s">
         <v>823</v>
@@ -25271,7 +25271,7 @@
         <v>33</v>
       </c>
       <c r="E405" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F405" t="s">
         <v>40</v>
@@ -25286,7 +25286,7 @@
         <v>842</v>
       </c>
       <c r="J405" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K405" t="s">
         <v>45</v>
@@ -25439,7 +25439,7 @@
         <v>33</v>
       </c>
       <c r="E408" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F408" t="s">
         <v>40</v>
@@ -25454,7 +25454,7 @@
         <v>854</v>
       </c>
       <c r="J408" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K408" t="s">
         <v>320</v>
@@ -25566,10 +25566,10 @@
         <v>860</v>
       </c>
       <c r="J410" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K410" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L410" t="s">
         <v>861</v>
@@ -25681,10 +25681,10 @@
         <v>179</v>
       </c>
       <c r="K412" t="s">
-        <v>293</v>
+        <v>664</v>
       </c>
       <c r="L412" t="s">
-        <v>34</v>
+        <v>868</v>
       </c>
       <c r="M412" t="s">
         <v>864</v>
@@ -25719,7 +25719,7 @@
         <v>34</v>
       </c>
       <c r="E413" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F413" t="s">
         <v>208</v>
@@ -25728,16 +25728,16 @@
         <v>41</v>
       </c>
       <c r="H413" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="I413" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="J413" t="s">
         <v>179</v>
       </c>
       <c r="K413" t="s">
-        <v>109</v>
+        <v>293</v>
       </c>
       <c r="L413" t="s">
         <v>34</v>
@@ -25752,7 +25752,7 @@
         <v>48</v>
       </c>
       <c r="P413" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="Q413" t="s">
         <v>47</v>
@@ -25775,7 +25775,7 @@
         <v>34</v>
       </c>
       <c r="E414" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F414" t="s">
         <v>208</v>
@@ -25784,19 +25784,19 @@
         <v>41</v>
       </c>
       <c r="H414" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="I414" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="J414" t="s">
         <v>179</v>
       </c>
       <c r="K414" t="s">
-        <v>664</v>
+        <v>109</v>
       </c>
       <c r="L414" t="s">
-        <v>874</v>
+        <v>34</v>
       </c>
       <c r="M414" t="s">
         <v>864</v>
@@ -25808,7 +25808,7 @@
         <v>48</v>
       </c>
       <c r="P414" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Q414" t="s">
         <v>47</v>
@@ -25999,7 +25999,7 @@
         <v>33</v>
       </c>
       <c r="E418" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F418" t="s">
         <v>40</v>
@@ -26014,7 +26014,7 @@
         <v>887</v>
       </c>
       <c r="J418" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K418" t="s">
         <v>45</v>
@@ -26226,25 +26226,25 @@
         <v>902</v>
       </c>
       <c r="F422" t="s">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="G422" t="s">
         <v>41</v>
       </c>
       <c r="H422" t="s">
+        <v>897</v>
+      </c>
+      <c r="I422" t="s">
         <v>903</v>
       </c>
-      <c r="I422" t="s">
+      <c r="J422" t="s">
+        <v>373</v>
+      </c>
+      <c r="K422" t="s">
+        <v>45</v>
+      </c>
+      <c r="L422" t="s">
         <v>904</v>
-      </c>
-      <c r="J422" t="s">
-        <v>179</v>
-      </c>
-      <c r="K422" t="s">
-        <v>293</v>
-      </c>
-      <c r="L422" t="s">
-        <v>34</v>
       </c>
       <c r="M422" t="s">
         <v>901</v>
@@ -26256,7 +26256,7 @@
         <v>48</v>
       </c>
       <c r="P422" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="Q422" t="s">
         <v>47</v>
@@ -26279,7 +26279,7 @@
         <v>34</v>
       </c>
       <c r="E423" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F423" t="s">
         <v>40</v>
@@ -26288,19 +26288,19 @@
         <v>41</v>
       </c>
       <c r="H423" t="s">
+        <v>897</v>
+      </c>
+      <c r="I423" t="s">
         <v>905</v>
-      </c>
-      <c r="I423" t="s">
-        <v>906</v>
       </c>
       <c r="J423" t="s">
         <v>369</v>
       </c>
       <c r="K423" t="s">
-        <v>45</v>
+        <v>674</v>
       </c>
       <c r="L423" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="M423" t="s">
         <v>901</v>
@@ -26312,7 +26312,7 @@
         <v>48</v>
       </c>
       <c r="P423" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="Q423" t="s">
         <v>47</v>
@@ -26335,28 +26335,28 @@
         <v>34</v>
       </c>
       <c r="E424" t="s">
-        <v>720</v>
+        <v>907</v>
       </c>
       <c r="F424" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G424" t="s">
         <v>41</v>
       </c>
       <c r="H424" t="s">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="I424" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J424" t="s">
-        <v>369</v>
+        <v>179</v>
       </c>
       <c r="K424" t="s">
-        <v>674</v>
+        <v>293</v>
       </c>
       <c r="L424" t="s">
-        <v>909</v>
+        <v>34</v>
       </c>
       <c r="M424" t="s">
         <v>901</v>
@@ -26368,7 +26368,7 @@
         <v>48</v>
       </c>
       <c r="P424" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="Q424" t="s">
         <v>47</v>
@@ -26391,7 +26391,7 @@
         <v>34</v>
       </c>
       <c r="E425" t="s">
-        <v>910</v>
+        <v>724</v>
       </c>
       <c r="F425" t="s">
         <v>40</v>
@@ -26400,13 +26400,13 @@
         <v>41</v>
       </c>
       <c r="H425" t="s">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="I425" t="s">
         <v>911</v>
       </c>
       <c r="J425" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="K425" t="s">
         <v>45</v>
@@ -26615,7 +26615,7 @@
         <v>33</v>
       </c>
       <c r="E429" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F429" t="s">
         <v>40</v>
@@ -26630,7 +26630,7 @@
         <v>924</v>
       </c>
       <c r="J429" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K429" t="s">
         <v>45</v>
@@ -26783,7 +26783,7 @@
         <v>33</v>
       </c>
       <c r="E432" t="s">
-        <v>820</v>
+        <v>724</v>
       </c>
       <c r="F432" t="s">
         <v>40</v>
@@ -26798,10 +26798,10 @@
         <v>936</v>
       </c>
       <c r="J432" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="K432" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="L432" t="s">
         <v>937</v>
@@ -26839,7 +26839,7 @@
         <v>34</v>
       </c>
       <c r="E433" t="s">
-        <v>720</v>
+        <v>820</v>
       </c>
       <c r="F433" t="s">
         <v>40</v>
@@ -26854,10 +26854,10 @@
         <v>939</v>
       </c>
       <c r="J433" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="K433" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="L433" t="s">
         <v>940</v>
@@ -27063,7 +27063,7 @@
         <v>33</v>
       </c>
       <c r="E437" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="F437" t="s">
         <v>40</v>

--- a/xlsx/dre/DRE_03_2026.xlsx
+++ b/xlsx/dre/DRE_03_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9526" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9526" uniqueCount="1093">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -2374,6 +2374,9 @@
   </si>
   <si>
     <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
   </si>
   <si>
     <t>R$  1.819,86</t>
@@ -24104,10 +24107,10 @@
         <v>41</v>
       </c>
       <c r="H384" t="s">
-        <v>554</v>
+        <v>782</v>
       </c>
       <c r="I384" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="J384" t="s">
         <v>727</v>
@@ -24116,7 +24119,7 @@
         <v>45</v>
       </c>
       <c r="L384" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M384" t="s">
         <v>756</v>
@@ -24128,7 +24131,7 @@
         <v>48</v>
       </c>
       <c r="P384" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="Q384" t="s">
         <v>47</v>
@@ -24160,10 +24163,10 @@
         <v>41</v>
       </c>
       <c r="H385" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="I385" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="J385" t="s">
         <v>766</v>
@@ -24172,7 +24175,7 @@
         <v>120</v>
       </c>
       <c r="L385" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M385" t="s">
         <v>756</v>
@@ -24184,7 +24187,7 @@
         <v>48</v>
       </c>
       <c r="P385" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Q385" t="s">
         <v>47</v>
@@ -24195,13 +24198,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="1">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B386" t="s" s="1">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C386" t="s" s="1">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D386" t="s" s="1">
         <v>33</v>
@@ -24251,13 +24254,13 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
+        <v>790</v>
+      </c>
+      <c r="B387" t="s">
         <v>789</v>
       </c>
-      <c r="B387" t="s">
-        <v>788</v>
-      </c>
       <c r="C387" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D387" t="s">
         <v>33</v>
@@ -24284,10 +24287,10 @@
         <v>124</v>
       </c>
       <c r="L387" t="s">
+        <v>791</v>
+      </c>
+      <c r="M387" t="s">
         <v>790</v>
-      </c>
-      <c r="M387" t="s">
-        <v>789</v>
       </c>
       <c r="N387" t="s">
         <v>47</v>
@@ -24307,13 +24310,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="1">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B388" t="s" s="1">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C388" t="s" s="1">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D388" t="s" s="1">
         <v>33</v>
@@ -24363,13 +24366,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
+        <v>794</v>
+      </c>
+      <c r="B389" t="s">
         <v>793</v>
       </c>
-      <c r="B389" t="s">
-        <v>792</v>
-      </c>
       <c r="C389" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D389" t="s">
         <v>33</v>
@@ -24396,10 +24399,10 @@
         <v>124</v>
       </c>
       <c r="L389" t="s">
+        <v>795</v>
+      </c>
+      <c r="M389" t="s">
         <v>794</v>
-      </c>
-      <c r="M389" t="s">
-        <v>793</v>
       </c>
       <c r="N389" t="s">
         <v>47</v>
@@ -24419,13 +24422,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="1">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B390" t="s" s="1">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C390" t="s" s="1">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D390" t="s" s="1">
         <v>33</v>
@@ -24475,13 +24478,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
+        <v>798</v>
+      </c>
+      <c r="B391" t="s">
         <v>797</v>
       </c>
-      <c r="B391" t="s">
-        <v>796</v>
-      </c>
       <c r="C391" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D391" t="s">
         <v>33</v>
@@ -24496,10 +24499,10 @@
         <v>41</v>
       </c>
       <c r="H391" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="I391" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J391" t="s">
         <v>223</v>
@@ -24508,10 +24511,10 @@
         <v>124</v>
       </c>
       <c r="L391" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M391" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N391" t="s">
         <v>47</v>
@@ -24520,7 +24523,7 @@
         <v>48</v>
       </c>
       <c r="P391" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="Q391" t="s">
         <v>47</v>
@@ -24531,13 +24534,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="1">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B392" t="s" s="1">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C392" t="s" s="1">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D392" t="s" s="1">
         <v>33</v>
@@ -24587,13 +24590,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
+        <v>804</v>
+      </c>
+      <c r="B393" t="s">
         <v>803</v>
       </c>
-      <c r="B393" t="s">
-        <v>802</v>
-      </c>
       <c r="C393" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D393" t="s">
         <v>33</v>
@@ -24611,7 +24614,7 @@
         <v>192</v>
       </c>
       <c r="I393" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J393" t="s">
         <v>223</v>
@@ -24623,7 +24626,7 @@
         <v>34</v>
       </c>
       <c r="M393" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="N393" t="s">
         <v>47</v>
@@ -24643,13 +24646,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="1">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B394" t="s" s="1">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C394" t="s" s="1">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D394" t="s" s="1">
         <v>33</v>
@@ -24699,13 +24702,13 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="1">
+        <v>808</v>
+      </c>
+      <c r="B395" t="s" s="1">
         <v>807</v>
       </c>
-      <c r="B395" t="s" s="1">
-        <v>806</v>
-      </c>
       <c r="C395" t="s" s="1">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D395" t="s" s="1">
         <v>33</v>
@@ -24755,19 +24758,19 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B396" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C396" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D396" t="s">
         <v>33</v>
       </c>
       <c r="E396" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F396" t="s">
         <v>208</v>
@@ -24779,10 +24782,10 @@
         <v>522</v>
       </c>
       <c r="I396" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="J396" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="K396" t="s">
         <v>67</v>
@@ -24791,7 +24794,7 @@
         <v>34</v>
       </c>
       <c r="M396" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N396" t="s">
         <v>47</v>
@@ -24800,7 +24803,7 @@
         <v>48</v>
       </c>
       <c r="P396" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="Q396" t="s">
         <v>47</v>
@@ -24811,7 +24814,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B397" t="s">
         <v>34</v>
@@ -24823,7 +24826,7 @@
         <v>34</v>
       </c>
       <c r="E397" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F397" t="s">
         <v>208</v>
@@ -24835,7 +24838,7 @@
         <v>485</v>
       </c>
       <c r="I397" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="J397" t="s">
         <v>722</v>
@@ -24847,7 +24850,7 @@
         <v>34</v>
       </c>
       <c r="M397" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N397" t="s">
         <v>47</v>
@@ -24856,7 +24859,7 @@
         <v>48</v>
       </c>
       <c r="P397" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="Q397" t="s">
         <v>47</v>
@@ -24867,13 +24870,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="1">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B398" t="s" s="1">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C398" t="s" s="1">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D398" t="s" s="1">
         <v>33</v>
@@ -24923,13 +24926,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="1">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B399" t="s" s="1">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C399" t="s" s="1">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D399" t="s" s="1">
         <v>33</v>
@@ -24979,19 +24982,19 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B400" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C400" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D400" t="s">
         <v>33</v>
       </c>
       <c r="E400" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F400" t="s">
         <v>40</v>
@@ -25000,10 +25003,10 @@
         <v>41</v>
       </c>
       <c r="H400" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="I400" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="J400" t="s">
         <v>727</v>
@@ -25012,10 +25015,10 @@
         <v>728</v>
       </c>
       <c r="L400" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="M400" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N400" t="s">
         <v>47</v>
@@ -25024,7 +25027,7 @@
         <v>48</v>
       </c>
       <c r="P400" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="Q400" t="s">
         <v>47</v>
@@ -25035,19 +25038,19 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B401" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C401" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D401" t="s">
         <v>33</v>
       </c>
       <c r="E401" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F401" t="s">
         <v>208</v>
@@ -25059,19 +25062,19 @@
         <v>189</v>
       </c>
       <c r="I401" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="J401" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="K401" t="s">
         <v>159</v>
       </c>
       <c r="L401" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="M401" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N401" t="s">
         <v>47</v>
@@ -25080,7 +25083,7 @@
         <v>48</v>
       </c>
       <c r="P401" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q401" t="s">
         <v>47</v>
@@ -25091,13 +25094,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="1">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B402" t="s" s="1">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C402" t="s" s="1">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D402" t="s" s="1">
         <v>33</v>
@@ -25147,19 +25150,19 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
+        <v>833</v>
+      </c>
+      <c r="B403" t="s">
         <v>832</v>
       </c>
-      <c r="B403" t="s">
-        <v>831</v>
-      </c>
       <c r="C403" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D403" t="s">
         <v>33</v>
       </c>
       <c r="E403" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F403" t="s">
         <v>40</v>
@@ -25168,22 +25171,22 @@
         <v>41</v>
       </c>
       <c r="H403" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="I403" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="J403" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="K403" t="s">
         <v>101</v>
       </c>
       <c r="L403" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="M403" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="N403" t="s">
         <v>47</v>
@@ -25192,7 +25195,7 @@
         <v>48</v>
       </c>
       <c r="P403" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="Q403" t="s">
         <v>47</v>
@@ -25203,13 +25206,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="1">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B404" t="s" s="1">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C404" t="s" s="1">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D404" t="s" s="1">
         <v>33</v>
@@ -25259,13 +25262,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
+        <v>841</v>
+      </c>
+      <c r="B405" t="s">
         <v>840</v>
       </c>
-      <c r="B405" t="s">
-        <v>839</v>
-      </c>
       <c r="C405" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D405" t="s">
         <v>33</v>
@@ -25280,10 +25283,10 @@
         <v>41</v>
       </c>
       <c r="H405" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="I405" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J405" t="s">
         <v>727</v>
@@ -25292,10 +25295,10 @@
         <v>45</v>
       </c>
       <c r="L405" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="M405" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="N405" t="s">
         <v>47</v>
@@ -25304,7 +25307,7 @@
         <v>48</v>
       </c>
       <c r="P405" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="Q405" t="s">
         <v>47</v>
@@ -25315,13 +25318,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="1">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B406" t="s" s="1">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C406" t="s" s="1">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D406" t="s" s="1">
         <v>33</v>
@@ -25371,19 +25374,19 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B407" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C407" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D407" t="s">
         <v>33</v>
       </c>
       <c r="E407" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F407" t="s">
         <v>40</v>
@@ -25392,22 +25395,22 @@
         <v>41</v>
       </c>
       <c r="H407" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="I407" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="J407" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="K407" t="s">
         <v>159</v>
       </c>
       <c r="L407" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="M407" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="N407" t="s">
         <v>47</v>
@@ -25416,7 +25419,7 @@
         <v>48</v>
       </c>
       <c r="P407" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="Q407" t="s">
         <v>47</v>
@@ -25427,13 +25430,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B408" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C408" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D408" t="s">
         <v>33</v>
@@ -25448,10 +25451,10 @@
         <v>41</v>
       </c>
       <c r="H408" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="I408" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J408" t="s">
         <v>727</v>
@@ -25460,10 +25463,10 @@
         <v>320</v>
       </c>
       <c r="L408" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="M408" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="N408" t="s">
         <v>47</v>
@@ -25472,7 +25475,7 @@
         <v>48</v>
       </c>
       <c r="P408" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="Q408" t="s">
         <v>47</v>
@@ -25483,13 +25486,13 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="1">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B409" t="s" s="1">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C409" t="s" s="1">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D409" t="s" s="1">
         <v>33</v>
@@ -25539,19 +25542,19 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
+        <v>859</v>
+      </c>
+      <c r="B410" t="s">
         <v>858</v>
       </c>
-      <c r="B410" t="s">
-        <v>857</v>
-      </c>
       <c r="C410" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D410" t="s">
         <v>33</v>
       </c>
       <c r="E410" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F410" t="s">
         <v>40</v>
@@ -25560,10 +25563,10 @@
         <v>41</v>
       </c>
       <c r="H410" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="I410" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J410" t="s">
         <v>727</v>
@@ -25572,10 +25575,10 @@
         <v>728</v>
       </c>
       <c r="L410" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M410" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="N410" t="s">
         <v>47</v>
@@ -25584,7 +25587,7 @@
         <v>48</v>
       </c>
       <c r="P410" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="Q410" t="s">
         <v>47</v>
@@ -25595,13 +25598,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="1">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B411" t="s" s="1">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C411" t="s" s="1">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D411" t="s" s="1">
         <v>33</v>
@@ -25651,19 +25654,19 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
+        <v>865</v>
+      </c>
+      <c r="B412" t="s">
         <v>864</v>
       </c>
-      <c r="B412" t="s">
-        <v>863</v>
-      </c>
       <c r="C412" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D412" t="s">
         <v>33</v>
       </c>
       <c r="E412" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F412" t="s">
         <v>208</v>
@@ -25672,10 +25675,10 @@
         <v>41</v>
       </c>
       <c r="H412" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="I412" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="J412" t="s">
         <v>179</v>
@@ -25684,10 +25687,10 @@
         <v>664</v>
       </c>
       <c r="L412" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M412" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N412" t="s">
         <v>47</v>
@@ -25696,7 +25699,7 @@
         <v>48</v>
       </c>
       <c r="P412" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="Q412" t="s">
         <v>47</v>
@@ -25707,7 +25710,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B413" t="s">
         <v>34</v>
@@ -25719,7 +25722,7 @@
         <v>34</v>
       </c>
       <c r="E413" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F413" t="s">
         <v>208</v>
@@ -25728,10 +25731,10 @@
         <v>41</v>
       </c>
       <c r="H413" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="I413" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="J413" t="s">
         <v>179</v>
@@ -25743,7 +25746,7 @@
         <v>34</v>
       </c>
       <c r="M413" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N413" t="s">
         <v>47</v>
@@ -25752,7 +25755,7 @@
         <v>48</v>
       </c>
       <c r="P413" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="Q413" t="s">
         <v>47</v>
@@ -25763,7 +25766,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B414" t="s">
         <v>34</v>
@@ -25775,7 +25778,7 @@
         <v>34</v>
       </c>
       <c r="E414" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F414" t="s">
         <v>208</v>
@@ -25784,10 +25787,10 @@
         <v>41</v>
       </c>
       <c r="H414" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="I414" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="J414" t="s">
         <v>179</v>
@@ -25799,7 +25802,7 @@
         <v>34</v>
       </c>
       <c r="M414" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N414" t="s">
         <v>47</v>
@@ -25808,7 +25811,7 @@
         <v>48</v>
       </c>
       <c r="P414" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="Q414" t="s">
         <v>47</v>
@@ -25819,7 +25822,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B415" t="s">
         <v>34</v>
@@ -25831,7 +25834,7 @@
         <v>34</v>
       </c>
       <c r="E415" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F415" t="s">
         <v>208</v>
@@ -25843,7 +25846,7 @@
         <v>485</v>
       </c>
       <c r="I415" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="J415" t="s">
         <v>105</v>
@@ -25852,10 +25855,10 @@
         <v>97</v>
       </c>
       <c r="L415" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="M415" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N415" t="s">
         <v>47</v>
@@ -25864,7 +25867,7 @@
         <v>48</v>
       </c>
       <c r="P415" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Q415" t="s">
         <v>47</v>
@@ -25875,7 +25878,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B416" t="s">
         <v>34</v>
@@ -25887,7 +25890,7 @@
         <v>34</v>
       </c>
       <c r="E416" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="F416" t="s">
         <v>208</v>
@@ -25896,10 +25899,10 @@
         <v>41</v>
       </c>
       <c r="H416" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="I416" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="J416" t="s">
         <v>179</v>
@@ -25908,10 +25911,10 @@
         <v>101</v>
       </c>
       <c r="L416" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="M416" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N416" t="s">
         <v>47</v>
@@ -25920,7 +25923,7 @@
         <v>48</v>
       </c>
       <c r="P416" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="Q416" t="s">
         <v>47</v>
@@ -25931,13 +25934,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="1">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B417" t="s" s="1">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C417" t="s" s="1">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D417" t="s" s="1">
         <v>33</v>
@@ -25987,13 +25990,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B418" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C418" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D418" t="s">
         <v>33</v>
@@ -26008,10 +26011,10 @@
         <v>41</v>
       </c>
       <c r="H418" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I418" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="J418" t="s">
         <v>727</v>
@@ -26020,10 +26023,10 @@
         <v>45</v>
       </c>
       <c r="L418" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="M418" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N418" t="s">
         <v>47</v>
@@ -26032,7 +26035,7 @@
         <v>48</v>
       </c>
       <c r="P418" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="Q418" t="s">
         <v>47</v>
@@ -26043,19 +26046,19 @@
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B419" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C419" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D419" t="s">
         <v>33</v>
       </c>
       <c r="E419" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F419" t="s">
         <v>40</v>
@@ -26064,22 +26067,22 @@
         <v>41</v>
       </c>
       <c r="H419" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="I419" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="J419" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="K419" t="s">
         <v>305</v>
       </c>
       <c r="L419" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="M419" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="N419" t="s">
         <v>47</v>
@@ -26088,7 +26091,7 @@
         <v>48</v>
       </c>
       <c r="P419" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="Q419" t="s">
         <v>47</v>
@@ -26099,19 +26102,19 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B420" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C420" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D420" t="s">
         <v>33</v>
       </c>
       <c r="E420" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F420" t="s">
         <v>40</v>
@@ -26120,10 +26123,10 @@
         <v>41</v>
       </c>
       <c r="H420" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="I420" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="J420" t="s">
         <v>44</v>
@@ -26132,10 +26135,10 @@
         <v>45</v>
       </c>
       <c r="L420" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="M420" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="N420" t="s">
         <v>47</v>
@@ -26144,7 +26147,7 @@
         <v>48</v>
       </c>
       <c r="P420" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="Q420" t="s">
         <v>47</v>
@@ -26155,13 +26158,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="1">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B421" t="s" s="1">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C421" t="s" s="1">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D421" t="s" s="1">
         <v>33</v>
@@ -26211,19 +26214,19 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
+        <v>902</v>
+      </c>
+      <c r="B422" t="s">
         <v>901</v>
       </c>
-      <c r="B422" t="s">
-        <v>900</v>
-      </c>
       <c r="C422" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D422" t="s">
         <v>33</v>
       </c>
       <c r="E422" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F422" t="s">
         <v>40</v>
@@ -26232,10 +26235,10 @@
         <v>41</v>
       </c>
       <c r="H422" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="I422" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="J422" t="s">
         <v>373</v>
@@ -26244,10 +26247,10 @@
         <v>45</v>
       </c>
       <c r="L422" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M422" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="N422" t="s">
         <v>47</v>
@@ -26256,7 +26259,7 @@
         <v>48</v>
       </c>
       <c r="P422" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="Q422" t="s">
         <v>47</v>
@@ -26267,7 +26270,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B423" t="s">
         <v>34</v>
@@ -26288,10 +26291,10 @@
         <v>41</v>
       </c>
       <c r="H423" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="I423" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J423" t="s">
         <v>369</v>
@@ -26300,10 +26303,10 @@
         <v>674</v>
       </c>
       <c r="L423" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="M423" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="N423" t="s">
         <v>47</v>
@@ -26312,7 +26315,7 @@
         <v>48</v>
       </c>
       <c r="P423" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="Q423" t="s">
         <v>47</v>
@@ -26323,7 +26326,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B424" t="s">
         <v>34</v>
@@ -26335,7 +26338,7 @@
         <v>34</v>
       </c>
       <c r="E424" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F424" t="s">
         <v>208</v>
@@ -26344,10 +26347,10 @@
         <v>41</v>
       </c>
       <c r="H424" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="I424" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="J424" t="s">
         <v>179</v>
@@ -26359,7 +26362,7 @@
         <v>34</v>
       </c>
       <c r="M424" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="N424" t="s">
         <v>47</v>
@@ -26368,7 +26371,7 @@
         <v>48</v>
       </c>
       <c r="P424" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="Q424" t="s">
         <v>47</v>
@@ -26379,7 +26382,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B425" t="s">
         <v>34</v>
@@ -26400,10 +26403,10 @@
         <v>41</v>
       </c>
       <c r="H425" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="I425" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="J425" t="s">
         <v>369</v>
@@ -26412,10 +26415,10 @@
         <v>45</v>
       </c>
       <c r="L425" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="M425" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="N425" t="s">
         <v>47</v>
@@ -26424,7 +26427,7 @@
         <v>48</v>
       </c>
       <c r="P425" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="Q425" t="s">
         <v>47</v>
@@ -26435,13 +26438,13 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="1">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B426" t="s" s="1">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C426" t="s" s="1">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D426" t="s" s="1">
         <v>33</v>
@@ -26491,19 +26494,19 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
+        <v>916</v>
+      </c>
+      <c r="B427" t="s">
         <v>915</v>
       </c>
-      <c r="B427" t="s">
-        <v>914</v>
-      </c>
       <c r="C427" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D427" t="s">
         <v>33</v>
       </c>
       <c r="E427" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F427" t="s">
         <v>208</v>
@@ -26512,10 +26515,10 @@
         <v>41</v>
       </c>
       <c r="H427" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="I427" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="J427" t="s">
         <v>105</v>
@@ -26524,10 +26527,10 @@
         <v>97</v>
       </c>
       <c r="L427" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="M427" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="N427" t="s">
         <v>47</v>
@@ -26536,7 +26539,7 @@
         <v>48</v>
       </c>
       <c r="P427" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="Q427" t="s">
         <v>47</v>
@@ -26547,13 +26550,13 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="1">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B428" t="s" s="1">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C428" t="s" s="1">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D428" t="s" s="1">
         <v>33</v>
@@ -26603,13 +26606,13 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
+        <v>923</v>
+      </c>
+      <c r="B429" t="s">
         <v>922</v>
       </c>
-      <c r="B429" t="s">
-        <v>921</v>
-      </c>
       <c r="C429" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D429" t="s">
         <v>33</v>
@@ -26624,10 +26627,10 @@
         <v>41</v>
       </c>
       <c r="H429" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I429" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="J429" t="s">
         <v>727</v>
@@ -26636,10 +26639,10 @@
         <v>45</v>
       </c>
       <c r="L429" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="M429" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="N429" t="s">
         <v>47</v>
@@ -26648,7 +26651,7 @@
         <v>48</v>
       </c>
       <c r="P429" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="Q429" t="s">
         <v>47</v>
@@ -26659,13 +26662,13 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="1">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B430" t="s" s="1">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C430" t="s" s="1">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D430" t="s" s="1">
         <v>33</v>
@@ -26715,13 +26718,13 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B431" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C431" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D431" t="s">
         <v>33</v>
@@ -26736,10 +26739,10 @@
         <v>41</v>
       </c>
       <c r="H431" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I431" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J431" t="s">
         <v>223</v>
@@ -26748,10 +26751,10 @@
         <v>105</v>
       </c>
       <c r="L431" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M431" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="N431" t="s">
         <v>47</v>
@@ -26760,7 +26763,7 @@
         <v>48</v>
       </c>
       <c r="P431" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="Q431" t="s">
         <v>47</v>
@@ -26771,13 +26774,13 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B432" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C432" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D432" t="s">
         <v>33</v>
@@ -26792,10 +26795,10 @@
         <v>41</v>
       </c>
       <c r="H432" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="I432" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="J432" t="s">
         <v>727</v>
@@ -26804,10 +26807,10 @@
         <v>45</v>
       </c>
       <c r="L432" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="M432" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N432" t="s">
         <v>47</v>
@@ -26816,7 +26819,7 @@
         <v>48</v>
       </c>
       <c r="P432" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="Q432" t="s">
         <v>47</v>
@@ -26827,7 +26830,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B433" t="s">
         <v>34</v>
@@ -26839,7 +26842,7 @@
         <v>34</v>
       </c>
       <c r="E433" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F433" t="s">
         <v>40</v>
@@ -26848,10 +26851,10 @@
         <v>41</v>
       </c>
       <c r="H433" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="I433" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="J433" t="s">
         <v>722</v>
@@ -26860,10 +26863,10 @@
         <v>67</v>
       </c>
       <c r="L433" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="M433" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N433" t="s">
         <v>47</v>
@@ -26872,7 +26875,7 @@
         <v>48</v>
       </c>
       <c r="P433" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="Q433" t="s">
         <v>47</v>
@@ -26883,13 +26886,13 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B434" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C434" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D434" t="s">
         <v>33</v>
@@ -26904,10 +26907,10 @@
         <v>41</v>
       </c>
       <c r="H434" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="I434" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J434" t="s">
         <v>373</v>
@@ -26916,10 +26919,10 @@
         <v>45</v>
       </c>
       <c r="L434" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="M434" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="N434" t="s">
         <v>47</v>
@@ -26928,7 +26931,7 @@
         <v>48</v>
       </c>
       <c r="P434" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="Q434" t="s">
         <v>47</v>
@@ -26939,13 +26942,13 @@
     </row>
     <row r="435">
       <c r="A435" t="s" s="1">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B435" t="s" s="1">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C435" t="s" s="1">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D435" t="s" s="1">
         <v>33</v>
@@ -26995,13 +26998,13 @@
     </row>
     <row r="436">
       <c r="A436" t="s" s="1">
+        <v>949</v>
+      </c>
+      <c r="B436" t="s" s="1">
         <v>948</v>
       </c>
-      <c r="B436" t="s" s="1">
-        <v>947</v>
-      </c>
       <c r="C436" t="s" s="1">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D436" t="s" s="1">
         <v>33</v>
@@ -27051,13 +27054,13 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B437" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C437" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D437" t="s">
         <v>33</v>
@@ -27072,10 +27075,10 @@
         <v>41</v>
       </c>
       <c r="H437" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="I437" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="J437" t="s">
         <v>293</v>
@@ -27084,10 +27087,10 @@
         <v>293</v>
       </c>
       <c r="L437" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="M437" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="N437" t="s">
         <v>47</v>
@@ -27096,7 +27099,7 @@
         <v>48</v>
       </c>
       <c r="P437" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="Q437" t="s">
         <v>47</v>
@@ -27107,13 +27110,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="1">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B438" t="s" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C438" t="s" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D438" t="s" s="1">
         <v>33</v>
@@ -27163,13 +27166,13 @@
     </row>
     <row r="439">
       <c r="A439" t="s" s="1">
+        <v>956</v>
+      </c>
+      <c r="B439" t="s" s="1">
         <v>955</v>
       </c>
-      <c r="B439" t="s" s="1">
-        <v>954</v>
-      </c>
       <c r="C439" t="s" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D439" t="s" s="1">
         <v>33</v>
@@ -27219,13 +27222,13 @@
     </row>
     <row r="440">
       <c r="A440" t="s" s="1">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B440" t="s" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C440" t="s" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D440" t="s" s="1">
         <v>33</v>
@@ -27275,19 +27278,19 @@
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B441" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C441" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D441" t="s">
         <v>33</v>
       </c>
       <c r="E441" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F441" t="s">
         <v>208</v>
@@ -27296,10 +27299,10 @@
         <v>41</v>
       </c>
       <c r="H441" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="I441" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="J441" t="s">
         <v>179</v>
@@ -27311,7 +27314,7 @@
         <v>34</v>
       </c>
       <c r="M441" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="N441" t="s">
         <v>47</v>
@@ -27320,7 +27323,7 @@
         <v>48</v>
       </c>
       <c r="P441" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="Q441" t="s">
         <v>47</v>
@@ -27331,13 +27334,13 @@
     </row>
     <row r="442">
       <c r="A442" t="s" s="1">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B442" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C442" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D442" t="s" s="1">
         <v>33</v>
@@ -27387,13 +27390,13 @@
     </row>
     <row r="443">
       <c r="A443" t="s" s="1">
+        <v>964</v>
+      </c>
+      <c r="B443" t="s" s="1">
         <v>963</v>
       </c>
-      <c r="B443" t="s" s="1">
-        <v>962</v>
-      </c>
       <c r="C443" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D443" t="s" s="1">
         <v>33</v>
@@ -27443,13 +27446,13 @@
     </row>
     <row r="444">
       <c r="A444" t="s" s="1">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B444" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C444" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D444" t="s" s="1">
         <v>33</v>
@@ -27499,13 +27502,13 @@
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B445" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C445" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D445" t="s">
         <v>33</v>
@@ -27520,10 +27523,10 @@
         <v>41</v>
       </c>
       <c r="H445" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I445" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="J445" t="s">
         <v>133</v>
@@ -27532,10 +27535,10 @@
         <v>133</v>
       </c>
       <c r="L445" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M445" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N445" t="s">
         <v>47</v>
@@ -27544,7 +27547,7 @@
         <v>145</v>
       </c>
       <c r="P445" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="Q445" t="s">
         <v>47</v>
@@ -27555,7 +27558,7 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B446" t="s">
         <v>34</v>
@@ -27576,10 +27579,10 @@
         <v>41</v>
       </c>
       <c r="H446" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I446" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="J446" t="s">
         <v>73</v>
@@ -27588,10 +27591,10 @@
         <v>73</v>
       </c>
       <c r="L446" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M446" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N446" t="s">
         <v>47</v>
@@ -27600,7 +27603,7 @@
         <v>86</v>
       </c>
       <c r="P446" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="Q446" t="s">
         <v>47</v>
@@ -27611,7 +27614,7 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B447" t="s">
         <v>34</v>
@@ -27632,10 +27635,10 @@
         <v>41</v>
       </c>
       <c r="H447" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I447" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="J447" t="s">
         <v>97</v>
@@ -27644,10 +27647,10 @@
         <v>97</v>
       </c>
       <c r="L447" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M447" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N447" t="s">
         <v>47</v>
@@ -27656,7 +27659,7 @@
         <v>98</v>
       </c>
       <c r="P447" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="Q447" t="s">
         <v>47</v>
@@ -27667,7 +27670,7 @@
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B448" t="s">
         <v>34</v>
@@ -27688,10 +27691,10 @@
         <v>41</v>
       </c>
       <c r="H448" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="I448" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="J448" t="s">
         <v>78</v>
@@ -27700,10 +27703,10 @@
         <v>78</v>
       </c>
       <c r="L448" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M448" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N448" t="s">
         <v>47</v>
@@ -27712,7 +27715,7 @@
         <v>521</v>
       </c>
       <c r="P448" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="Q448" t="s">
         <v>47</v>
@@ -27723,7 +27726,7 @@
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B449" t="s">
         <v>34</v>
@@ -27744,10 +27747,10 @@
         <v>41</v>
       </c>
       <c r="H449" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I449" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="J449" t="s">
         <v>119</v>
@@ -27756,10 +27759,10 @@
         <v>119</v>
       </c>
       <c r="L449" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M449" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N449" t="s">
         <v>47</v>
@@ -27768,7 +27771,7 @@
         <v>269</v>
       </c>
       <c r="P449" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="Q449" t="s">
         <v>47</v>
@@ -27779,7 +27782,7 @@
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B450" t="s">
         <v>34</v>
@@ -27800,10 +27803,10 @@
         <v>41</v>
       </c>
       <c r="H450" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I450" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="J450" t="s">
         <v>119</v>
@@ -27812,10 +27815,10 @@
         <v>119</v>
       </c>
       <c r="L450" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M450" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N450" t="s">
         <v>47</v>
@@ -27824,7 +27827,7 @@
         <v>149</v>
       </c>
       <c r="P450" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="Q450" t="s">
         <v>47</v>
@@ -27835,7 +27838,7 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B451" t="s">
         <v>34</v>
@@ -27856,10 +27859,10 @@
         <v>41</v>
       </c>
       <c r="H451" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I451" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="J451" t="s">
         <v>78</v>
@@ -27868,10 +27871,10 @@
         <v>78</v>
       </c>
       <c r="L451" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M451" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N451" t="s">
         <v>47</v>
@@ -27880,7 +27883,7 @@
         <v>169</v>
       </c>
       <c r="P451" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="Q451" t="s">
         <v>47</v>
@@ -27891,7 +27894,7 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B452" t="s">
         <v>34</v>
@@ -27912,10 +27915,10 @@
         <v>41</v>
       </c>
       <c r="H452" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I452" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="J452" t="s">
         <v>120</v>
@@ -27924,10 +27927,10 @@
         <v>120</v>
       </c>
       <c r="L452" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M452" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N452" t="s">
         <v>47</v>
@@ -27936,7 +27939,7 @@
         <v>152</v>
       </c>
       <c r="P452" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="Q452" t="s">
         <v>47</v>
@@ -27947,7 +27950,7 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B453" t="s">
         <v>34</v>
@@ -27968,10 +27971,10 @@
         <v>41</v>
       </c>
       <c r="H453" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I453" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="J453" t="s">
         <v>73</v>
@@ -27980,10 +27983,10 @@
         <v>73</v>
       </c>
       <c r="L453" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M453" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N453" t="s">
         <v>47</v>
@@ -27992,7 +27995,7 @@
         <v>385</v>
       </c>
       <c r="P453" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="Q453" t="s">
         <v>47</v>
@@ -28003,7 +28006,7 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B454" t="s">
         <v>34</v>
@@ -28024,10 +28027,10 @@
         <v>41</v>
       </c>
       <c r="H454" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="I454" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="J454" t="s">
         <v>73</v>
@@ -28036,10 +28039,10 @@
         <v>73</v>
       </c>
       <c r="L454" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M454" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N454" t="s">
         <v>47</v>
@@ -28048,7 +28051,7 @@
         <v>294</v>
       </c>
       <c r="P454" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="Q454" t="s">
         <v>47</v>
@@ -28059,7 +28062,7 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B455" t="s">
         <v>34</v>
@@ -28080,10 +28083,10 @@
         <v>41</v>
       </c>
       <c r="H455" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I455" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="J455" t="s">
         <v>73</v>
@@ -28092,10 +28095,10 @@
         <v>73</v>
       </c>
       <c r="L455" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M455" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N455" t="s">
         <v>47</v>
@@ -28104,7 +28107,7 @@
         <v>330</v>
       </c>
       <c r="P455" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="Q455" t="s">
         <v>47</v>
@@ -28115,7 +28118,7 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B456" t="s">
         <v>34</v>
@@ -28136,10 +28139,10 @@
         <v>41</v>
       </c>
       <c r="H456" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I456" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="J456" t="s">
         <v>68</v>
@@ -28148,10 +28151,10 @@
         <v>68</v>
       </c>
       <c r="L456" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M456" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N456" t="s">
         <v>47</v>
@@ -28160,7 +28163,7 @@
         <v>262</v>
       </c>
       <c r="P456" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="Q456" t="s">
         <v>47</v>
@@ -28171,7 +28174,7 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B457" t="s">
         <v>34</v>
@@ -28192,10 +28195,10 @@
         <v>41</v>
       </c>
       <c r="H457" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I457" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="J457" t="s">
         <v>73</v>
@@ -28204,10 +28207,10 @@
         <v>73</v>
       </c>
       <c r="L457" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M457" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N457" t="s">
         <v>47</v>
@@ -28216,7 +28219,7 @@
         <v>115</v>
       </c>
       <c r="P457" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="Q457" t="s">
         <v>47</v>
@@ -28227,7 +28230,7 @@
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B458" t="s">
         <v>34</v>
@@ -28248,10 +28251,10 @@
         <v>41</v>
       </c>
       <c r="H458" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I458" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="J458" t="s">
         <v>105</v>
@@ -28260,10 +28263,10 @@
         <v>105</v>
       </c>
       <c r="L458" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M458" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N458" t="s">
         <v>47</v>
@@ -28272,7 +28275,7 @@
         <v>112</v>
       </c>
       <c r="P458" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="Q458" t="s">
         <v>47</v>
@@ -28283,7 +28286,7 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="1">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B459" t="s" s="1">
         <v>32</v>
@@ -28339,7 +28342,7 @@
     </row>
     <row r="460">
       <c r="A460" t="s" s="1">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B460" t="s" s="1">
         <v>32</v>
@@ -28395,7 +28398,7 @@
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B461" t="s">
         <v>32</v>
@@ -28451,7 +28454,7 @@
     </row>
     <row r="462">
       <c r="A462" t="s" s="1">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B462" t="s" s="1">
         <v>57</v>
@@ -28507,7 +28510,7 @@
     </row>
     <row r="463">
       <c r="A463" t="s" s="1">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B463" t="s" s="1">
         <v>59</v>
@@ -28563,7 +28566,7 @@
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B464" t="s">
         <v>59</v>
@@ -28619,7 +28622,7 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="1">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B465" t="s" s="1">
         <v>204</v>
@@ -28675,7 +28678,7 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B466" t="s">
         <v>204</v>
@@ -28731,7 +28734,7 @@
     </row>
     <row r="467">
       <c r="A467" t="s" s="1">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B467" t="s" s="1">
         <v>216</v>
@@ -28787,7 +28790,7 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B468" t="s">
         <v>216</v>
@@ -28843,13 +28846,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s" s="1">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B469" t="s" s="1">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C469" t="s" s="1">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D469" t="s" s="1">
         <v>33</v>
@@ -28899,7 +28902,7 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="1">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B470" t="s" s="1">
         <v>238</v>
@@ -28955,7 +28958,7 @@
     </row>
     <row r="471">
       <c r="A471" t="s" s="1">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B471" t="s" s="1">
         <v>240</v>
@@ -29011,7 +29014,7 @@
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B472" t="s">
         <v>240</v>
@@ -29067,7 +29070,7 @@
     </row>
     <row r="473">
       <c r="A473" t="s" s="1">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B473" t="s" s="1">
         <v>380</v>
@@ -29123,7 +29126,7 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B474" t="s">
         <v>380</v>
@@ -29179,13 +29182,13 @@
     </row>
     <row r="475">
       <c r="A475" t="s" s="1">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B475" t="s" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C475" t="s" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D475" t="s" s="1">
         <v>33</v>
@@ -29235,13 +29238,13 @@
     </row>
     <row r="476">
       <c r="A476" t="s" s="1">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B476" t="s" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C476" t="s" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D476" t="s" s="1">
         <v>33</v>
@@ -29291,7 +29294,7 @@
     </row>
     <row r="477">
       <c r="A477" t="s" s="1">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B477" t="s" s="1">
         <v>477</v>
@@ -29347,7 +29350,7 @@
     </row>
     <row r="478">
       <c r="A478" t="s" s="1">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B478" t="s" s="1">
         <v>479</v>
@@ -29403,7 +29406,7 @@
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B479" t="s">
         <v>479</v>
@@ -29459,7 +29462,7 @@
     </row>
     <row r="480">
       <c r="A480" t="s" s="1">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B480" t="s" s="1">
         <v>624</v>
@@ -29515,7 +29518,7 @@
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B481" t="s">
         <v>624</v>
@@ -29571,7 +29574,7 @@
     </row>
     <row r="482">
       <c r="A482" t="s" s="1">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B482" t="s" s="1">
         <v>633</v>
@@ -29627,7 +29630,7 @@
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B483" t="s">
         <v>635</v>
@@ -29683,7 +29686,7 @@
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B484" t="s">
         <v>705</v>
@@ -29739,7 +29742,7 @@
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B485" t="s">
         <v>711</v>
@@ -29795,7 +29798,7 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="1">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B486" t="s" s="1">
         <v>744</v>
@@ -29851,7 +29854,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="1">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B487" t="s" s="1">
         <v>746</v>
@@ -29907,7 +29910,7 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B488" t="s">
         <v>748</v>
@@ -29963,7 +29966,7 @@
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B489" t="s">
         <v>753</v>
@@ -30019,13 +30022,13 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B490" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C490" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D490" t="s">
         <v>33</v>
@@ -30075,13 +30078,13 @@
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B491" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C491" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D491" t="s">
         <v>33</v>
@@ -30131,13 +30134,13 @@
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B492" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C492" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D492" t="s">
         <v>33</v>
@@ -30187,13 +30190,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s" s="1">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B493" t="s" s="1">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C493" t="s" s="1">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D493" t="s" s="1">
         <v>33</v>
@@ -30243,13 +30246,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B494" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C494" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D494" t="s">
         <v>33</v>
@@ -30299,13 +30302,13 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B495" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C495" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D495" t="s">
         <v>33</v>
@@ -30355,13 +30358,13 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B496" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C496" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D496" t="s">
         <v>33</v>
@@ -30411,13 +30414,13 @@
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B497" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C497" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D497" t="s">
         <v>33</v>
@@ -30467,13 +30470,13 @@
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B498" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C498" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D498" t="s">
         <v>33</v>
@@ -30523,13 +30526,13 @@
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B499" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C499" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D499" t="s">
         <v>33</v>
@@ -30579,13 +30582,13 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B500" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C500" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D500" t="s">
         <v>33</v>
@@ -30635,13 +30638,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B501" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C501" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D501" t="s">
         <v>33</v>
@@ -30691,13 +30694,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B502" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C502" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D502" t="s">
         <v>33</v>
@@ -30747,13 +30750,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B503" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C503" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D503" t="s">
         <v>33</v>
@@ -30803,13 +30806,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B504" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C504" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D504" t="s">
         <v>33</v>
@@ -30859,13 +30862,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="1">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B505" t="s" s="1">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C505" t="s" s="1">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D505" t="s" s="1">
         <v>33</v>
@@ -30915,13 +30918,13 @@
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B506" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C506" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D506" t="s">
         <v>33</v>
@@ -30971,13 +30974,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="1">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B507" t="s" s="1">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C507" t="s" s="1">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D507" t="s" s="1">
         <v>33</v>
@@ -31027,13 +31030,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="1">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B508" t="s" s="1">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C508" t="s" s="1">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D508" t="s" s="1">
         <v>33</v>
@@ -31083,13 +31086,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="1">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B509" t="s" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C509" t="s" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D509" t="s" s="1">
         <v>33</v>
@@ -31139,13 +31142,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B510" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C510" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D510" t="s">
         <v>33</v>
@@ -31195,13 +31198,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="1">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B511" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C511" t="s" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D511" t="s" s="1">
         <v>33</v>
@@ -31251,13 +31254,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B512" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C512" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D512" t="s">
         <v>33</v>
@@ -31307,13 +31310,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="1">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B513" t="s" s="1">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C513" t="s" s="1">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D513" t="s" s="1">
         <v>33</v>
@@ -31363,13 +31366,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="1">
+        <v>1044</v>
+      </c>
+      <c r="B514" t="s" s="1">
         <v>1043</v>
       </c>
-      <c r="B514" t="s" s="1">
-        <v>1042</v>
-      </c>
       <c r="C514" t="s" s="1">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D514" t="s" s="1">
         <v>33</v>
@@ -31419,13 +31422,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="1">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B515" t="s" s="1">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C515" t="s" s="1">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D515" t="s" s="1">
         <v>33</v>
@@ -31475,7 +31478,7 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="1">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B516" t="s" s="1">
         <v>57</v>
@@ -31531,13 +31534,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="1">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B517" t="s" s="1">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C517" t="s" s="1">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D517" t="s" s="1">
         <v>33</v>
@@ -31587,7 +31590,7 @@
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B518" t="s">
         <v>216</v>
@@ -31643,7 +31646,7 @@
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B519" t="s">
         <v>238</v>
@@ -31699,7 +31702,7 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B520" t="s">
         <v>477</v>
@@ -31755,13 +31758,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B521" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C521" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D521" t="s">
         <v>33</v>
@@ -31811,13 +31814,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="1">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B522" t="s" s="1">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C522" t="s" s="1">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D522" t="s" s="1">
         <v>33</v>
@@ -31867,7 +31870,7 @@
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B523" t="s">
         <v>744</v>
@@ -31923,13 +31926,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B524" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C524" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D524" t="s">
         <v>33</v>
@@ -31979,7 +31982,7 @@
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B525" t="s">
         <v>59</v>
@@ -32035,13 +32038,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B526" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C526" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D526" t="s">
         <v>33</v>
@@ -32091,13 +32094,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B527" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C527" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D527" t="s">
         <v>33</v>
@@ -32147,7 +32150,7 @@
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B528" t="s">
         <v>240</v>
@@ -32203,7 +32206,7 @@
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B529" t="s">
         <v>479</v>
@@ -32259,7 +32262,7 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B530" t="s">
         <v>746</v>
@@ -32315,13 +32318,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B531" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C531" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D531" t="s">
         <v>33</v>
@@ -32371,7 +32374,7 @@
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B532" t="s">
         <v>216</v>
@@ -32427,13 +32430,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B533" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C533" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D533" t="s">
         <v>33</v>
@@ -32483,13 +32486,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B534" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C534" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D534" t="s">
         <v>33</v>
@@ -32539,13 +32542,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="1">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B535" t="s" s="1">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C535" t="s" s="1">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D535" t="s" s="1">
         <v>33</v>
@@ -32595,16 +32598,16 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="1">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B536" t="s" s="1">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C536" t="s" s="1">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D536" t="s" s="1">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E536" t="s" s="1">
         <v>34</v>
@@ -32651,16 +32654,16 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="1">
+        <v>1074</v>
+      </c>
+      <c r="B537" t="s" s="1">
+        <v>1075</v>
+      </c>
+      <c r="C537" t="s" s="1">
+        <v>1075</v>
+      </c>
+      <c r="D537" t="s" s="1">
         <v>1073</v>
-      </c>
-      <c r="B537" t="s" s="1">
-        <v>1074</v>
-      </c>
-      <c r="C537" t="s" s="1">
-        <v>1074</v>
-      </c>
-      <c r="D537" t="s" s="1">
-        <v>1072</v>
       </c>
       <c r="E537" t="s" s="1">
         <v>34</v>
@@ -32707,16 +32710,16 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="1">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B538" t="s" s="1">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C538" t="s" s="1">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D538" t="s" s="1">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E538" t="s" s="1">
         <v>34</v>
@@ -32763,13 +32766,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B539" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C539" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D539" t="s">
         <v>33</v>
@@ -32819,19 +32822,19 @@
     </row>
     <row r="540">
       <c r="A540" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B540" t="s">
         <v>1079</v>
       </c>
-      <c r="B540" t="s">
-        <v>1078</v>
-      </c>
       <c r="C540" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D540" t="s">
         <v>33</v>
       </c>
       <c r="E540" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F540" t="s">
         <v>208</v>
@@ -32840,10 +32843,10 @@
         <v>41</v>
       </c>
       <c r="H540" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="I540" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="J540" t="s">
         <v>305</v>
@@ -32855,7 +32858,7 @@
         <v>34</v>
       </c>
       <c r="M540" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N540" t="s">
         <v>47</v>
@@ -32864,7 +32867,7 @@
         <v>48</v>
       </c>
       <c r="P540" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="Q540" t="s">
         <v>47</v>
@@ -32875,7 +32878,7 @@
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B541" t="s">
         <v>34</v>
@@ -32887,7 +32890,7 @@
         <v>34</v>
       </c>
       <c r="E541" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F541" t="s">
         <v>208</v>
@@ -32896,10 +32899,10 @@
         <v>41</v>
       </c>
       <c r="H541" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="I541" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J541" t="s">
         <v>320</v>
@@ -32908,10 +32911,10 @@
         <v>320</v>
       </c>
       <c r="L541" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="M541" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N541" t="s">
         <v>47</v>
@@ -32920,7 +32923,7 @@
         <v>48</v>
       </c>
       <c r="P541" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="Q541" t="s">
         <v>47</v>
@@ -32931,7 +32934,7 @@
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B542" t="s">
         <v>34</v>
@@ -32943,7 +32946,7 @@
         <v>34</v>
       </c>
       <c r="E542" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F542" t="s">
         <v>64</v>
@@ -32952,10 +32955,10 @@
         <v>41</v>
       </c>
       <c r="H542" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="I542" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J542" t="s">
         <v>54</v>
@@ -32964,10 +32967,10 @@
         <v>97</v>
       </c>
       <c r="L542" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="M542" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N542" t="s">
         <v>47</v>
@@ -32976,7 +32979,7 @@
         <v>48</v>
       </c>
       <c r="P542" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="Q542" t="s">
         <v>47</v>
@@ -32987,7 +32990,7 @@
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B543" t="s">
         <v>34</v>
@@ -32999,7 +33002,7 @@
         <v>34</v>
       </c>
       <c r="E543" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F543" t="s">
         <v>208</v>
@@ -33008,7 +33011,7 @@
         <v>41</v>
       </c>
       <c r="H543" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="I543" t="s">
         <v>100</v>
@@ -33020,10 +33023,10 @@
         <v>664</v>
       </c>
       <c r="L543" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="M543" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N543" t="s">
         <v>47</v>

--- a/xlsx/dre/DRE_03_2026.xlsx
+++ b/xlsx/dre/DRE_03_2026.xlsx
@@ -985,6 +985,30 @@
     <t>R$ 7.970,23</t>
   </si>
   <si>
+    <t>2/2</t>
+  </si>
+  <si>
+    <t>R$  106,63</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Mercado livre - mat aspirador</t>
+  </si>
+  <si>
+    <t>9/3</t>
+  </si>
+  <si>
+    <t>R$  91,87</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>Grapa</t>
+  </si>
+  <si>
     <t>Denny Lucas do Carmo Ferreira</t>
   </si>
   <si>
@@ -1124,30 +1148,6 @@
 </t>
   </si>
   <si>
-    <t>9/3</t>
-  </si>
-  <si>
-    <t>R$  91,87</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>Grapa</t>
-  </si>
-  <si>
-    <t>2/2</t>
-  </si>
-  <si>
-    <t>R$  106,63</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Mercado livre - mat aspirador</t>
-  </si>
-  <si>
     <t>561/1</t>
   </si>
   <si>
@@ -1172,24 +1172,234 @@
     <t>4.02.02.01.01 Fretes sobre compra de mercadorias da marca - provisão</t>
   </si>
   <si>
+    <t>67301/2</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>ENTREGADORA NOVO RUMO LTDA ME</t>
   </si>
   <si>
+    <t>R$  758,85</t>
+  </si>
+  <si>
+    <t>Título referente a Frete</t>
+  </si>
+  <si>
+    <t>67301/3</t>
+  </si>
+  <si>
+    <t>RODAG TRANSPORTES LTDA*</t>
+  </si>
+  <si>
+    <t>R$  773,11</t>
+  </si>
+  <si>
+    <t>67001/2</t>
+  </si>
+  <si>
+    <t>R$  353,67</t>
+  </si>
+  <si>
+    <t>67001/3</t>
+  </si>
+  <si>
+    <t>R$  360,12</t>
+  </si>
+  <si>
+    <t>64801/3</t>
+  </si>
+  <si>
+    <t>R$  837,11</t>
+  </si>
+  <si>
+    <t>64301/2</t>
+  </si>
+  <si>
+    <t>R$  1.916,19</t>
+  </si>
+  <si>
+    <t>R$  822,42</t>
+  </si>
+  <si>
+    <t>R$  211,55</t>
+  </si>
+  <si>
+    <t>R$  465,51</t>
+  </si>
+  <si>
+    <t>R$  124,85</t>
+  </si>
+  <si>
+    <t>R$  1.012,15</t>
+  </si>
+  <si>
+    <t>R$  881,02</t>
+  </si>
+  <si>
+    <t>67501/2</t>
+  </si>
+  <si>
+    <t>R$  944,83</t>
+  </si>
+  <si>
+    <t>70601/3</t>
+  </si>
+  <si>
+    <t>R$  592,59</t>
+  </si>
+  <si>
+    <t>69301/3</t>
+  </si>
+  <si>
+    <t>R$  890,13</t>
+  </si>
+  <si>
+    <t>R$  1.680,23</t>
+  </si>
+  <si>
+    <t>68501AMILTONF</t>
+  </si>
+  <si>
+    <t>66301/2</t>
+  </si>
+  <si>
+    <t>R$  434,55</t>
+  </si>
+  <si>
+    <t>R$  553,17</t>
+  </si>
+  <si>
+    <t>68501/2</t>
+  </si>
+  <si>
+    <t>R$  1.648,01</t>
+  </si>
+  <si>
+    <t>R$  957,86</t>
+  </si>
+  <si>
+    <t>R$  841,44</t>
+  </si>
+  <si>
+    <t>70301/3</t>
+  </si>
+  <si>
+    <t>R$  611,34</t>
+  </si>
+  <si>
+    <t>64301/3</t>
+  </si>
+  <si>
+    <t>R$  2.052,71</t>
+  </si>
+  <si>
+    <t>68201/2</t>
+  </si>
+  <si>
+    <t>R$  609,66</t>
+  </si>
+  <si>
+    <t>63701/2</t>
+  </si>
+  <si>
+    <t>R$  330,16</t>
+  </si>
+  <si>
+    <t>R$  570,68</t>
+  </si>
+  <si>
+    <t>68201/3</t>
+  </si>
+  <si>
+    <t>R$  653,09</t>
+  </si>
+  <si>
+    <t>63701/3</t>
+  </si>
+  <si>
+    <t>R$  353,68</t>
+  </si>
+  <si>
+    <t>Diferença 8,15/0</t>
+  </si>
+  <si>
+    <t>R$  227,86</t>
+  </si>
+  <si>
+    <t>1164/0</t>
+  </si>
+  <si>
+    <t>R$  279,63</t>
+  </si>
+  <si>
+    <t>CleaRH001164</t>
+  </si>
+  <si>
+    <t>R$  80,79</t>
+  </si>
+  <si>
+    <t>10/06/26</t>
+  </si>
+  <si>
+    <t>67501/0</t>
+  </si>
+  <si>
+    <t>R$  164,97</t>
+  </si>
+  <si>
+    <t>23/03/02</t>
+  </si>
+  <si>
+    <t>R$  141,69</t>
+  </si>
+  <si>
+    <t>R$  264,04</t>
+  </si>
+  <si>
+    <t>67501-/0</t>
+  </si>
+  <si>
+    <t>R$  136,00</t>
+  </si>
+  <si>
+    <t>03/07/26</t>
+  </si>
+  <si>
+    <t>63301-/0</t>
+  </si>
+  <si>
+    <t>R$  33,33</t>
+  </si>
+  <si>
+    <t>R$  50,00</t>
+  </si>
+  <si>
+    <t>R$  30,00</t>
+  </si>
+  <si>
+    <t>67501n/0</t>
+  </si>
+  <si>
+    <t>R$  198,83</t>
+  </si>
+  <si>
+    <t>66301/0</t>
+  </si>
+  <si>
+    <t>R$  11,45</t>
+  </si>
+  <si>
     <t>R$  141,50</t>
   </si>
   <si>
-    <t>68501AMILTONF</t>
-  </si>
-  <si>
     <t>63301n/0</t>
   </si>
   <si>
     <t>R$  243,97</t>
   </si>
   <si>
-    <t>RODAG TRANSPORTES LTDA*</t>
-  </si>
-  <si>
     <t>R$  11,98</t>
   </si>
   <si>
@@ -1202,9 +1412,6 @@
     <t>R$  101,41</t>
   </si>
   <si>
-    <t>67501-/0</t>
-  </si>
-  <si>
     <t>R$  95,00</t>
   </si>
   <si>
@@ -1220,9 +1427,6 @@
     <t>R$  190,00</t>
   </si>
   <si>
-    <t>R$  50,00</t>
-  </si>
-  <si>
     <t>R$  98,75</t>
   </si>
   <si>
@@ -1247,210 +1451,6 @@
     <t>R$  15,09</t>
   </si>
   <si>
-    <t>67301/2</t>
-  </si>
-  <si>
-    <t>PCP</t>
-  </si>
-  <si>
-    <t>R$  758,85</t>
-  </si>
-  <si>
-    <t>Título referente a Frete</t>
-  </si>
-  <si>
-    <t>67301/3</t>
-  </si>
-  <si>
-    <t>R$  773,11</t>
-  </si>
-  <si>
-    <t>67001/2</t>
-  </si>
-  <si>
-    <t>R$  353,67</t>
-  </si>
-  <si>
-    <t>67001/3</t>
-  </si>
-  <si>
-    <t>R$  360,12</t>
-  </si>
-  <si>
-    <t>64801/3</t>
-  </si>
-  <si>
-    <t>R$  837,11</t>
-  </si>
-  <si>
-    <t>64301/2</t>
-  </si>
-  <si>
-    <t>R$  1.916,19</t>
-  </si>
-  <si>
-    <t>R$  822,42</t>
-  </si>
-  <si>
-    <t>R$  211,55</t>
-  </si>
-  <si>
-    <t>R$  465,51</t>
-  </si>
-  <si>
-    <t>R$  124,85</t>
-  </si>
-  <si>
-    <t>R$  1.012,15</t>
-  </si>
-  <si>
-    <t>R$  881,02</t>
-  </si>
-  <si>
-    <t>67501/2</t>
-  </si>
-  <si>
-    <t>R$  944,83</t>
-  </si>
-  <si>
-    <t>70601/3</t>
-  </si>
-  <si>
-    <t>R$  592,59</t>
-  </si>
-  <si>
-    <t>69301/3</t>
-  </si>
-  <si>
-    <t>R$  890,13</t>
-  </si>
-  <si>
-    <t>R$  1.680,23</t>
-  </si>
-  <si>
-    <t>66301/2</t>
-  </si>
-  <si>
-    <t>R$  434,55</t>
-  </si>
-  <si>
-    <t>R$  553,17</t>
-  </si>
-  <si>
-    <t>68501/2</t>
-  </si>
-  <si>
-    <t>R$  1.648,01</t>
-  </si>
-  <si>
-    <t>R$  957,86</t>
-  </si>
-  <si>
-    <t>R$  841,44</t>
-  </si>
-  <si>
-    <t>70301/3</t>
-  </si>
-  <si>
-    <t>R$  611,34</t>
-  </si>
-  <si>
-    <t>64301/3</t>
-  </si>
-  <si>
-    <t>R$  2.052,71</t>
-  </si>
-  <si>
-    <t>68201/2</t>
-  </si>
-  <si>
-    <t>R$  609,66</t>
-  </si>
-  <si>
-    <t>63701/2</t>
-  </si>
-  <si>
-    <t>R$  330,16</t>
-  </si>
-  <si>
-    <t>R$  570,68</t>
-  </si>
-  <si>
-    <t>68201/3</t>
-  </si>
-  <si>
-    <t>R$  653,09</t>
-  </si>
-  <si>
-    <t>63701/3</t>
-  </si>
-  <si>
-    <t>R$  353,68</t>
-  </si>
-  <si>
-    <t>Diferença 8,15/0</t>
-  </si>
-  <si>
-    <t>R$  227,86</t>
-  </si>
-  <si>
-    <t>1164/0</t>
-  </si>
-  <si>
-    <t>R$  279,63</t>
-  </si>
-  <si>
-    <t>CleaRH001164</t>
-  </si>
-  <si>
-    <t>R$  80,79</t>
-  </si>
-  <si>
-    <t>10/06/26</t>
-  </si>
-  <si>
-    <t>67501/0</t>
-  </si>
-  <si>
-    <t>R$  164,97</t>
-  </si>
-  <si>
-    <t>23/03/02</t>
-  </si>
-  <si>
-    <t>R$  141,69</t>
-  </si>
-  <si>
-    <t>R$  264,04</t>
-  </si>
-  <si>
-    <t>R$  136,00</t>
-  </si>
-  <si>
-    <t>03/07/26</t>
-  </si>
-  <si>
-    <t>63301-/0</t>
-  </si>
-  <si>
-    <t>R$  33,33</t>
-  </si>
-  <si>
-    <t>R$  30,00</t>
-  </si>
-  <si>
-    <t>67501n/0</t>
-  </si>
-  <si>
-    <t>R$  198,83</t>
-  </si>
-  <si>
-    <t>66301/0</t>
-  </si>
-  <si>
-    <t>R$  11,45</t>
-  </si>
-  <si>
     <t>4.03 DESPESAS DE VENDAS</t>
   </si>
   <si>
@@ -1718,39 +1718,57 @@
     <t>R$ 6.206,47</t>
   </si>
   <si>
+    <t>69801/2</t>
+  </si>
+  <si>
+    <t>70101/2</t>
+  </si>
+  <si>
+    <t>71701/2</t>
+  </si>
+  <si>
+    <t>R$  2,40</t>
+  </si>
+  <si>
     <t>FERNANDA DOCHVAT SILVA</t>
   </si>
   <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>05/08/26</t>
+  </si>
+  <si>
+    <t>R$  188,04</t>
+  </si>
+  <si>
+    <t>01/07/26</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>David Alves</t>
+  </si>
+  <si>
+    <t>01/06/26</t>
+  </si>
+  <si>
+    <t>R$  1.035,56</t>
+  </si>
+  <si>
     <t>05/05/26</t>
   </si>
   <si>
-    <t>R$  1.035,56</t>
-  </si>
-  <si>
-    <t>01/06/26</t>
-  </si>
-  <si>
-    <t>David Alves</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>01/07/26</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>R$  188,04</t>
-  </si>
-  <si>
-    <t>05/08/26</t>
-  </si>
-  <si>
     <t>R$  304,96</t>
   </si>
   <si>
+    <t>71601/2</t>
+  </si>
+  <si>
+    <t>R$  44,10</t>
+  </si>
+  <si>
     <t>19203/1</t>
   </si>
   <si>
@@ -1761,24 +1779,6 @@
   </si>
   <si>
     <t>R$  442,63</t>
-  </si>
-  <si>
-    <t>71601/2</t>
-  </si>
-  <si>
-    <t>R$  44,10</t>
-  </si>
-  <si>
-    <t>69801/2</t>
-  </si>
-  <si>
-    <t>70101/2</t>
-  </si>
-  <si>
-    <t>71701/2</t>
-  </si>
-  <si>
-    <t>R$  2,40</t>
   </si>
   <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
@@ -2301,97 +2301,97 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Leandro Henrique Simoes Campos</t>
+  </si>
+  <si>
+    <t>R$  2.000,00</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos Fixo 2026</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>R$  1.819,86</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>R$  2.071,82</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.020,07</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.405,07</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  2.071,98</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  1.900,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  7.800,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>R$  2.219,99</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
     <t>603/1</t>
-  </si>
-  <si>
-    <t>R$  2.219,99</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  1.900,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>R$  2.071,98</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos</t>
-  </si>
-  <si>
-    <t>R$  2.000,00</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos Fixo 2026</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.020,07</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  7.800,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.405,07</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>R$  1.819,86</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>R$  2.071,82</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -2945,28 +2945,28 @@
     <t>Título referente a Valor da Taxa Financeira</t>
   </si>
   <si>
+    <t>R$  1.165,41</t>
+  </si>
+  <si>
+    <t>PAGSEGURO</t>
+  </si>
+  <si>
+    <t>R$  192,00</t>
+  </si>
+  <si>
+    <t>R$  4.169,46</t>
+  </si>
+  <si>
+    <t>R$  907,60</t>
+  </si>
+  <si>
+    <t>R$  405,24</t>
+  </si>
+  <si>
+    <t>R$  501,61</t>
+  </si>
+  <si>
     <t>R$  2.789,71</t>
-  </si>
-  <si>
-    <t>R$  1.165,41</t>
-  </si>
-  <si>
-    <t>PAGSEGURO</t>
-  </si>
-  <si>
-    <t>R$  192,00</t>
-  </si>
-  <si>
-    <t>R$  4.169,46</t>
-  </si>
-  <si>
-    <t>R$  907,60</t>
-  </si>
-  <si>
-    <t>R$  405,24</t>
-  </si>
-  <si>
-    <t>R$  501,61</t>
   </si>
   <si>
     <t>R$  1.206,97</t>
@@ -8754,28 +8754,28 @@
         <v>33</v>
       </c>
       <c r="E110" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="F110" t="s">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="G110" t="s">
         <v>41</v>
       </c>
       <c r="H110" t="s">
-        <v>323</v>
+        <v>52</v>
       </c>
       <c r="I110" t="s">
         <v>324</v>
       </c>
       <c r="J110" t="s">
-        <v>119</v>
+        <v>325</v>
       </c>
       <c r="K110" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="L110" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="M110" t="s">
         <v>321</v>
@@ -8784,7 +8784,7 @@
         <v>47</v>
       </c>
       <c r="O110" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="P110" t="s">
         <v>324</v>
@@ -8810,28 +8810,28 @@
         <v>34</v>
       </c>
       <c r="E111" t="s">
-        <v>250</v>
+        <v>327</v>
       </c>
       <c r="F111" t="s">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="G111" t="s">
         <v>41</v>
       </c>
       <c r="H111" t="s">
-        <v>325</v>
+        <v>52</v>
       </c>
       <c r="I111" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J111" t="s">
-        <v>105</v>
+        <v>329</v>
       </c>
       <c r="K111" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="L111" t="s">
-        <v>34</v>
+        <v>330</v>
       </c>
       <c r="M111" t="s">
         <v>321</v>
@@ -8840,10 +8840,10 @@
         <v>47</v>
       </c>
       <c r="O111" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="P111" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q111" t="s">
         <v>47</v>
@@ -8866,7 +8866,7 @@
         <v>34</v>
       </c>
       <c r="E112" t="s">
-        <v>327</v>
+        <v>263</v>
       </c>
       <c r="F112" t="s">
         <v>208</v>
@@ -8875,19 +8875,19 @@
         <v>41</v>
       </c>
       <c r="H112" t="s">
-        <v>52</v>
+        <v>331</v>
       </c>
       <c r="I112" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="J112" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="K112" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="L112" t="s">
-        <v>329</v>
+        <v>34</v>
       </c>
       <c r="M112" t="s">
         <v>321</v>
@@ -8896,10 +8896,10 @@
         <v>47</v>
       </c>
       <c r="O112" t="s">
-        <v>330</v>
+        <v>149</v>
       </c>
       <c r="P112" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q112" t="s">
         <v>47</v>
@@ -8922,7 +8922,7 @@
         <v>34</v>
       </c>
       <c r="E113" t="s">
-        <v>331</v>
+        <v>250</v>
       </c>
       <c r="F113" t="s">
         <v>208</v>
@@ -8931,19 +8931,19 @@
         <v>41</v>
       </c>
       <c r="H113" t="s">
-        <v>52</v>
+        <v>333</v>
       </c>
       <c r="I113" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="J113" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="K113" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="L113" t="s">
-        <v>332</v>
+        <v>34</v>
       </c>
       <c r="M113" t="s">
         <v>321</v>
@@ -8952,10 +8952,10 @@
         <v>47</v>
       </c>
       <c r="O113" t="s">
-        <v>330</v>
+        <v>112</v>
       </c>
       <c r="P113" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="Q113" t="s">
         <v>47</v>
@@ -8978,7 +8978,7 @@
         <v>34</v>
       </c>
       <c r="E114" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F114" t="s">
         <v>208</v>
@@ -8990,7 +8990,7 @@
         <v>52</v>
       </c>
       <c r="I114" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="J114" t="s">
         <v>67</v>
@@ -8999,7 +8999,7 @@
         <v>67</v>
       </c>
       <c r="L114" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M114" t="s">
         <v>321</v>
@@ -9008,10 +9008,10 @@
         <v>47</v>
       </c>
       <c r="O114" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="P114" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="Q114" t="s">
         <v>47</v>
@@ -9034,7 +9034,7 @@
         <v>34</v>
       </c>
       <c r="E115" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F115" t="s">
         <v>208</v>
@@ -9043,19 +9043,19 @@
         <v>41</v>
       </c>
       <c r="H115" t="s">
+        <v>52</v>
+      </c>
+      <c r="I115" t="s">
         <v>336</v>
       </c>
-      <c r="I115" t="s">
-        <v>337</v>
-      </c>
       <c r="J115" t="s">
-        <v>338</v>
+        <v>67</v>
       </c>
       <c r="K115" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L115" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M115" t="s">
         <v>321</v>
@@ -9064,10 +9064,10 @@
         <v>47</v>
       </c>
       <c r="O115" t="s">
-        <v>48</v>
+        <v>338</v>
       </c>
       <c r="P115" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q115" t="s">
         <v>47</v>
@@ -9090,7 +9090,7 @@
         <v>34</v>
       </c>
       <c r="E116" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F116" t="s">
         <v>208</v>
@@ -9102,13 +9102,13 @@
         <v>52</v>
       </c>
       <c r="I116" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="J116" t="s">
-        <v>179</v>
+        <v>67</v>
       </c>
       <c r="K116" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L116" t="s">
         <v>342</v>
@@ -9120,10 +9120,10 @@
         <v>47</v>
       </c>
       <c r="O116" t="s">
-        <v>48</v>
+        <v>338</v>
       </c>
       <c r="P116" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="Q116" t="s">
         <v>47</v>
@@ -9155,19 +9155,19 @@
         <v>41</v>
       </c>
       <c r="H117" t="s">
-        <v>52</v>
+        <v>344</v>
       </c>
       <c r="I117" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J117" t="s">
-        <v>179</v>
+        <v>346</v>
       </c>
       <c r="K117" t="s">
         <v>105</v>
       </c>
       <c r="L117" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M117" t="s">
         <v>321</v>
@@ -9179,7 +9179,7 @@
         <v>48</v>
       </c>
       <c r="P117" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q117" t="s">
         <v>47</v>
@@ -9202,7 +9202,7 @@
         <v>34</v>
       </c>
       <c r="E118" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F118" t="s">
         <v>208</v>
@@ -9211,19 +9211,19 @@
         <v>41</v>
       </c>
       <c r="H118" t="s">
-        <v>336</v>
+        <v>52</v>
       </c>
       <c r="I118" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J118" t="s">
-        <v>348</v>
+        <v>179</v>
       </c>
       <c r="K118" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="L118" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="M118" t="s">
         <v>321</v>
@@ -9235,7 +9235,7 @@
         <v>48</v>
       </c>
       <c r="P118" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q118" t="s">
         <v>47</v>
@@ -9258,7 +9258,7 @@
         <v>34</v>
       </c>
       <c r="E119" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F119" t="s">
         <v>208</v>
@@ -9267,19 +9267,19 @@
         <v>41</v>
       </c>
       <c r="H119" t="s">
-        <v>336</v>
+        <v>52</v>
       </c>
       <c r="I119" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J119" t="s">
         <v>179</v>
       </c>
       <c r="K119" t="s">
-        <v>351</v>
+        <v>105</v>
       </c>
       <c r="L119" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="M119" t="s">
         <v>321</v>
@@ -9291,7 +9291,7 @@
         <v>48</v>
       </c>
       <c r="P119" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q119" t="s">
         <v>47</v>
@@ -9314,7 +9314,7 @@
         <v>34</v>
       </c>
       <c r="E120" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F120" t="s">
         <v>208</v>
@@ -9323,19 +9323,19 @@
         <v>41</v>
       </c>
       <c r="H120" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="I120" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J120" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K120" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="L120" t="s">
-        <v>34</v>
+        <v>347</v>
       </c>
       <c r="M120" t="s">
         <v>321</v>
@@ -9347,7 +9347,7 @@
         <v>48</v>
       </c>
       <c r="P120" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q120" t="s">
         <v>47</v>
@@ -9370,7 +9370,7 @@
         <v>34</v>
       </c>
       <c r="E121" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F121" t="s">
         <v>208</v>
@@ -9379,19 +9379,19 @@
         <v>41</v>
       </c>
       <c r="H121" t="s">
-        <v>52</v>
+        <v>344</v>
       </c>
       <c r="I121" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="J121" t="s">
         <v>179</v>
       </c>
       <c r="K121" t="s">
-        <v>67</v>
+        <v>359</v>
       </c>
       <c r="L121" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="M121" t="s">
         <v>321</v>
@@ -9400,10 +9400,10 @@
         <v>47</v>
       </c>
       <c r="O121" t="s">
-        <v>330</v>
+        <v>48</v>
       </c>
       <c r="P121" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="Q121" t="s">
         <v>47</v>
@@ -9426,7 +9426,7 @@
         <v>34</v>
       </c>
       <c r="E122" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F122" t="s">
         <v>208</v>
@@ -9435,16 +9435,16 @@
         <v>41</v>
       </c>
       <c r="H122" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="I122" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J122" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K122" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L122" t="s">
         <v>34</v>
@@ -9459,7 +9459,7 @@
         <v>48</v>
       </c>
       <c r="P122" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q122" t="s">
         <v>47</v>
@@ -9482,7 +9482,7 @@
         <v>34</v>
       </c>
       <c r="E123" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F123" t="s">
         <v>208</v>
@@ -9491,19 +9491,19 @@
         <v>41</v>
       </c>
       <c r="H123" t="s">
+        <v>52</v>
+      </c>
+      <c r="I123" t="s">
         <v>336</v>
       </c>
-      <c r="I123" t="s">
-        <v>361</v>
-      </c>
       <c r="J123" t="s">
-        <v>362</v>
+        <v>179</v>
       </c>
       <c r="K123" t="s">
         <v>67</v>
       </c>
       <c r="L123" t="s">
-        <v>34</v>
+        <v>364</v>
       </c>
       <c r="M123" t="s">
         <v>321</v>
@@ -9512,10 +9512,10 @@
         <v>47</v>
       </c>
       <c r="O123" t="s">
-        <v>48</v>
+        <v>338</v>
       </c>
       <c r="P123" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="Q123" t="s">
         <v>47</v>
@@ -9538,7 +9538,7 @@
         <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F124" t="s">
         <v>208</v>
@@ -9547,19 +9547,19 @@
         <v>41</v>
       </c>
       <c r="H124" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="I124" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J124" t="s">
-        <v>179</v>
+        <v>367</v>
       </c>
       <c r="K124" t="s">
         <v>105</v>
       </c>
       <c r="L124" t="s">
-        <v>366</v>
+        <v>34</v>
       </c>
       <c r="M124" t="s">
         <v>321</v>
@@ -9571,7 +9571,7 @@
         <v>48</v>
       </c>
       <c r="P124" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q124" t="s">
         <v>47</v>
@@ -9594,28 +9594,28 @@
         <v>34</v>
       </c>
       <c r="E125" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F125" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G125" t="s">
         <v>41</v>
       </c>
       <c r="H125" t="s">
-        <v>52</v>
+        <v>344</v>
       </c>
       <c r="I125" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J125" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K125" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="L125" t="s">
-        <v>370</v>
+        <v>34</v>
       </c>
       <c r="M125" t="s">
         <v>321</v>
@@ -9627,7 +9627,7 @@
         <v>48</v>
       </c>
       <c r="P125" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q125" t="s">
         <v>47</v>
@@ -9653,22 +9653,22 @@
         <v>371</v>
       </c>
       <c r="F126" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G126" t="s">
         <v>41</v>
       </c>
       <c r="H126" t="s">
-        <v>52</v>
+        <v>372</v>
       </c>
       <c r="I126" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J126" t="s">
-        <v>373</v>
+        <v>179</v>
       </c>
       <c r="K126" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="L126" t="s">
         <v>374</v>
@@ -9683,7 +9683,7 @@
         <v>48</v>
       </c>
       <c r="P126" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q126" t="s">
         <v>47</v>
@@ -9874,19 +9874,19 @@
         <v>33</v>
       </c>
       <c r="E130" t="s">
-        <v>87</v>
+        <v>383</v>
       </c>
       <c r="F130" t="s">
-        <v>208</v>
+        <v>384</v>
       </c>
       <c r="G130" t="s">
         <v>41</v>
       </c>
       <c r="H130" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I130" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J130" t="s">
         <v>73</v>
@@ -9895,7 +9895,7 @@
         <v>73</v>
       </c>
       <c r="L130" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M130" t="s">
         <v>382</v>
@@ -9904,13 +9904,13 @@
         <v>47</v>
       </c>
       <c r="O130" t="s">
-        <v>385</v>
+        <v>34</v>
       </c>
       <c r="P130" t="s">
-        <v>384</v>
+        <v>34</v>
       </c>
       <c r="Q130" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R130" t="s">
         <v>34</v>
@@ -9930,28 +9930,28 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F131" t="s">
-        <v>208</v>
+        <v>384</v>
       </c>
       <c r="G131" t="s">
         <v>41</v>
       </c>
       <c r="H131" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I131" t="s">
+        <v>390</v>
+      </c>
+      <c r="J131" t="s">
+        <v>73</v>
+      </c>
+      <c r="K131" t="s">
+        <v>73</v>
+      </c>
+      <c r="L131" t="s">
         <v>387</v>
-      </c>
-      <c r="J131" t="s">
-        <v>97</v>
-      </c>
-      <c r="K131" t="s">
-        <v>97</v>
-      </c>
-      <c r="L131" t="s">
-        <v>34</v>
       </c>
       <c r="M131" t="s">
         <v>382</v>
@@ -9960,13 +9960,13 @@
         <v>47</v>
       </c>
       <c r="O131" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="P131" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="Q131" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R131" t="s">
         <v>34</v>
@@ -9986,28 +9986,28 @@
         <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>113</v>
+        <v>391</v>
       </c>
       <c r="F132" t="s">
-        <v>208</v>
+        <v>384</v>
       </c>
       <c r="G132" t="s">
         <v>41</v>
       </c>
       <c r="H132" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I132" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J132" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="K132" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="L132" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M132" t="s">
         <v>382</v>
@@ -10016,13 +10016,13 @@
         <v>47</v>
       </c>
       <c r="O132" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="P132" t="s">
-        <v>389</v>
+        <v>34</v>
       </c>
       <c r="Q132" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R132" t="s">
         <v>34</v>
@@ -10042,28 +10042,28 @@
         <v>34</v>
       </c>
       <c r="E133" t="s">
-        <v>113</v>
+        <v>393</v>
       </c>
       <c r="F133" t="s">
-        <v>208</v>
+        <v>384</v>
       </c>
       <c r="G133" t="s">
         <v>41</v>
       </c>
       <c r="H133" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I133" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="J133" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="K133" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="L133" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M133" t="s">
         <v>382</v>
@@ -10072,13 +10072,13 @@
         <v>47</v>
       </c>
       <c r="O133" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="P133" t="s">
-        <v>390</v>
+        <v>34</v>
       </c>
       <c r="Q133" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R133" t="s">
         <v>34</v>
@@ -10098,28 +10098,28 @@
         <v>34</v>
       </c>
       <c r="E134" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F134" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G134" t="s">
         <v>41</v>
       </c>
       <c r="H134" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I134" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="J134" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K134" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L134" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M134" t="s">
         <v>382</v>
@@ -10128,10 +10128,10 @@
         <v>47</v>
       </c>
       <c r="O134" t="s">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="P134" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="Q134" t="s">
         <v>47</v>
@@ -10154,28 +10154,28 @@
         <v>34</v>
       </c>
       <c r="E135" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F135" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G135" t="s">
         <v>41</v>
       </c>
       <c r="H135" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I135" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="J135" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="K135" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L135" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M135" t="s">
         <v>382</v>
@@ -10184,10 +10184,10 @@
         <v>47</v>
       </c>
       <c r="O135" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="P135" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="Q135" t="s">
         <v>47</v>
@@ -10210,28 +10210,28 @@
         <v>34</v>
       </c>
       <c r="E136" t="s">
-        <v>395</v>
+        <v>300</v>
       </c>
       <c r="F136" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G136" t="s">
         <v>41</v>
       </c>
       <c r="H136" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I136" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J136" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K136" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L136" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M136" t="s">
         <v>382</v>
@@ -10240,10 +10240,10 @@
         <v>47</v>
       </c>
       <c r="O136" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="P136" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Q136" t="s">
         <v>47</v>
@@ -10266,28 +10266,28 @@
         <v>34</v>
       </c>
       <c r="E137" t="s">
-        <v>396</v>
+        <v>341</v>
       </c>
       <c r="F137" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G137" t="s">
         <v>41</v>
       </c>
       <c r="H137" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I137" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="J137" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K137" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L137" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M137" t="s">
         <v>382</v>
@@ -10296,10 +10296,10 @@
         <v>47</v>
       </c>
       <c r="O137" t="s">
-        <v>262</v>
+        <v>338</v>
       </c>
       <c r="P137" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="Q137" t="s">
         <v>47</v>
@@ -10322,28 +10322,28 @@
         <v>34</v>
       </c>
       <c r="E138" t="s">
-        <v>397</v>
+        <v>285</v>
       </c>
       <c r="F138" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G138" t="s">
         <v>41</v>
       </c>
       <c r="H138" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I138" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J138" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K138" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L138" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M138" t="s">
         <v>382</v>
@@ -10352,10 +10352,10 @@
         <v>47</v>
       </c>
       <c r="O138" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
       <c r="P138" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q138" t="s">
         <v>47</v>
@@ -10378,28 +10378,28 @@
         <v>34</v>
       </c>
       <c r="E139" t="s">
-        <v>150</v>
+        <v>339</v>
       </c>
       <c r="F139" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G139" t="s">
         <v>41</v>
       </c>
       <c r="H139" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I139" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J139" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="K139" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="L139" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M139" t="s">
         <v>382</v>
@@ -10408,10 +10408,10 @@
         <v>47</v>
       </c>
       <c r="O139" t="s">
-        <v>152</v>
+        <v>338</v>
       </c>
       <c r="P139" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q139" t="s">
         <v>47</v>
@@ -10434,28 +10434,28 @@
         <v>34</v>
       </c>
       <c r="E140" t="s">
-        <v>110</v>
+        <v>308</v>
       </c>
       <c r="F140" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G140" t="s">
         <v>41</v>
       </c>
       <c r="H140" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I140" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="J140" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="K140" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="L140" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M140" t="s">
         <v>382</v>
@@ -10464,10 +10464,10 @@
         <v>47</v>
       </c>
       <c r="O140" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="P140" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q140" t="s">
         <v>47</v>
@@ -10490,28 +10490,28 @@
         <v>34</v>
       </c>
       <c r="E141" t="s">
-        <v>401</v>
+        <v>306</v>
       </c>
       <c r="F141" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G141" t="s">
         <v>41</v>
       </c>
       <c r="H141" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I141" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J141" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="K141" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L141" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M141" t="s">
         <v>382</v>
@@ -10520,10 +10520,10 @@
         <v>47</v>
       </c>
       <c r="O141" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="P141" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q141" t="s">
         <v>47</v>
@@ -10546,28 +10546,28 @@
         <v>34</v>
       </c>
       <c r="E142" t="s">
-        <v>150</v>
+        <v>405</v>
       </c>
       <c r="F142" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G142" t="s">
         <v>41</v>
       </c>
       <c r="H142" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I142" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="J142" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K142" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L142" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M142" t="s">
         <v>382</v>
@@ -10576,10 +10576,10 @@
         <v>47</v>
       </c>
       <c r="O142" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="P142" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="Q142" t="s">
         <v>47</v>
@@ -10602,28 +10602,28 @@
         <v>34</v>
       </c>
       <c r="E143" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F143" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G143" t="s">
         <v>41</v>
       </c>
       <c r="H143" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I143" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="J143" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K143" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L143" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M143" t="s">
         <v>382</v>
@@ -10632,10 +10632,10 @@
         <v>47</v>
       </c>
       <c r="O143" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="Q143" t="s">
         <v>47</v>
@@ -10658,28 +10658,28 @@
         <v>34</v>
       </c>
       <c r="E144" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F144" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G144" t="s">
         <v>41</v>
       </c>
       <c r="H144" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="J144" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="K144" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L144" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M144" t="s">
         <v>382</v>
@@ -10688,10 +10688,10 @@
         <v>47</v>
       </c>
       <c r="O144" t="s">
-        <v>294</v>
+        <v>149</v>
       </c>
       <c r="P144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="Q144" t="s">
         <v>47</v>
@@ -10714,19 +10714,19 @@
         <v>34</v>
       </c>
       <c r="E145" t="s">
-        <v>405</v>
+        <v>312</v>
       </c>
       <c r="F145" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G145" t="s">
         <v>41</v>
       </c>
       <c r="H145" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="J145" t="s">
         <v>73</v>
@@ -10735,7 +10735,7 @@
         <v>73</v>
       </c>
       <c r="L145" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="M145" t="s">
         <v>382</v>
@@ -10744,10 +10744,10 @@
         <v>47</v>
       </c>
       <c r="O145" t="s">
-        <v>294</v>
+        <v>412</v>
       </c>
       <c r="P145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="Q145" t="s">
         <v>47</v>
@@ -10770,28 +10770,28 @@
         <v>34</v>
       </c>
       <c r="E146" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F146" t="s">
-        <v>409</v>
+        <v>247</v>
       </c>
       <c r="G146" t="s">
         <v>41</v>
       </c>
       <c r="H146" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I146" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="J146" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K146" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L146" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M146" t="s">
         <v>382</v>
@@ -10800,13 +10800,13 @@
         <v>47</v>
       </c>
       <c r="O146" t="s">
-        <v>34</v>
+        <v>262</v>
       </c>
       <c r="P146" t="s">
-        <v>34</v>
+        <v>414</v>
       </c>
       <c r="Q146" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R146" t="s">
         <v>34</v>
@@ -10826,28 +10826,28 @@
         <v>34</v>
       </c>
       <c r="E147" t="s">
-        <v>412</v>
+        <v>276</v>
       </c>
       <c r="F147" t="s">
-        <v>409</v>
+        <v>247</v>
       </c>
       <c r="G147" t="s">
         <v>41</v>
       </c>
       <c r="H147" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I147" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J147" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K147" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L147" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M147" t="s">
         <v>382</v>
@@ -10856,13 +10856,13 @@
         <v>47</v>
       </c>
       <c r="O147" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="P147" t="s">
-        <v>34</v>
+        <v>415</v>
       </c>
       <c r="Q147" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R147" t="s">
         <v>34</v>
@@ -10882,28 +10882,28 @@
         <v>34</v>
       </c>
       <c r="E148" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F148" t="s">
-        <v>409</v>
+        <v>247</v>
       </c>
       <c r="G148" t="s">
         <v>41</v>
       </c>
       <c r="H148" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I148" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J148" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="K148" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="L148" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M148" t="s">
         <v>382</v>
@@ -10912,13 +10912,13 @@
         <v>47</v>
       </c>
       <c r="O148" t="s">
-        <v>34</v>
+        <v>412</v>
       </c>
       <c r="P148" t="s">
-        <v>34</v>
+        <v>417</v>
       </c>
       <c r="Q148" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R148" t="s">
         <v>34</v>
@@ -10938,28 +10938,28 @@
         <v>34</v>
       </c>
       <c r="E149" t="s">
-        <v>416</v>
+        <v>303</v>
       </c>
       <c r="F149" t="s">
-        <v>409</v>
+        <v>247</v>
       </c>
       <c r="G149" t="s">
         <v>41</v>
       </c>
       <c r="H149" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I149" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J149" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="K149" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="L149" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M149" t="s">
         <v>382</v>
@@ -10968,13 +10968,13 @@
         <v>47</v>
       </c>
       <c r="O149" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="P149" t="s">
-        <v>34</v>
+        <v>418</v>
       </c>
       <c r="Q149" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R149" t="s">
         <v>34</v>
@@ -10994,7 +10994,7 @@
         <v>34</v>
       </c>
       <c r="E150" t="s">
-        <v>418</v>
+        <v>298</v>
       </c>
       <c r="F150" t="s">
         <v>247</v>
@@ -11003,7 +11003,7 @@
         <v>41</v>
       </c>
       <c r="H150" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I150" t="s">
         <v>419</v>
@@ -11015,7 +11015,7 @@
         <v>73</v>
       </c>
       <c r="L150" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M150" t="s">
         <v>382</v>
@@ -11059,19 +11059,19 @@
         <v>41</v>
       </c>
       <c r="H151" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I151" t="s">
         <v>421</v>
       </c>
       <c r="J151" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="K151" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L151" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M151" t="s">
         <v>382</v>
@@ -11080,7 +11080,7 @@
         <v>47</v>
       </c>
       <c r="O151" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="P151" t="s">
         <v>421</v>
@@ -11106,7 +11106,7 @@
         <v>34</v>
       </c>
       <c r="E152" t="s">
-        <v>300</v>
+        <v>422</v>
       </c>
       <c r="F152" t="s">
         <v>247</v>
@@ -11115,19 +11115,19 @@
         <v>41</v>
       </c>
       <c r="H152" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I152" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J152" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K152" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="L152" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M152" t="s">
         <v>382</v>
@@ -11136,10 +11136,10 @@
         <v>47</v>
       </c>
       <c r="O152" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="P152" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q152" t="s">
         <v>47</v>
@@ -11162,7 +11162,7 @@
         <v>34</v>
       </c>
       <c r="E153" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="F153" t="s">
         <v>247</v>
@@ -11171,19 +11171,19 @@
         <v>41</v>
       </c>
       <c r="H153" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I153" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J153" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="K153" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="L153" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M153" t="s">
         <v>382</v>
@@ -11192,10 +11192,10 @@
         <v>47</v>
       </c>
       <c r="O153" t="s">
-        <v>330</v>
+        <v>152</v>
       </c>
       <c r="P153" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q153" t="s">
         <v>47</v>
@@ -11218,7 +11218,7 @@
         <v>34</v>
       </c>
       <c r="E154" t="s">
-        <v>285</v>
+        <v>426</v>
       </c>
       <c r="F154" t="s">
         <v>247</v>
@@ -11227,19 +11227,19 @@
         <v>41</v>
       </c>
       <c r="H154" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I154" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="J154" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K154" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L154" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M154" t="s">
         <v>382</v>
@@ -11248,10 +11248,10 @@
         <v>47</v>
       </c>
       <c r="O154" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="P154" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Q154" t="s">
         <v>47</v>
@@ -11274,7 +11274,7 @@
         <v>34</v>
       </c>
       <c r="E155" t="s">
-        <v>331</v>
+        <v>280</v>
       </c>
       <c r="F155" t="s">
         <v>247</v>
@@ -11283,19 +11283,19 @@
         <v>41</v>
       </c>
       <c r="H155" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I155" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="J155" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="K155" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="L155" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M155" t="s">
         <v>382</v>
@@ -11304,10 +11304,10 @@
         <v>47</v>
       </c>
       <c r="O155" t="s">
-        <v>330</v>
+        <v>145</v>
       </c>
       <c r="P155" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="Q155" t="s">
         <v>47</v>
@@ -11330,7 +11330,7 @@
         <v>34</v>
       </c>
       <c r="E156" t="s">
-        <v>308</v>
+        <v>429</v>
       </c>
       <c r="F156" t="s">
         <v>247</v>
@@ -11339,19 +11339,19 @@
         <v>41</v>
       </c>
       <c r="H156" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I156" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="J156" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K156" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L156" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M156" t="s">
         <v>382</v>
@@ -11360,10 +11360,10 @@
         <v>47</v>
       </c>
       <c r="O156" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="P156" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="Q156" t="s">
         <v>47</v>
@@ -11386,7 +11386,7 @@
         <v>34</v>
       </c>
       <c r="E157" t="s">
-        <v>306</v>
+        <v>431</v>
       </c>
       <c r="F157" t="s">
         <v>247</v>
@@ -11395,19 +11395,19 @@
         <v>41</v>
       </c>
       <c r="H157" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I157" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="J157" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="K157" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L157" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="M157" t="s">
         <v>382</v>
@@ -11416,10 +11416,10 @@
         <v>47</v>
       </c>
       <c r="O157" t="s">
-        <v>98</v>
+        <v>294</v>
       </c>
       <c r="P157" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="Q157" t="s">
         <v>47</v>
@@ -11442,28 +11442,28 @@
         <v>34</v>
       </c>
       <c r="E158" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F158" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G158" t="s">
         <v>41</v>
       </c>
       <c r="H158" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I158" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="J158" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="K158" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="L158" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M158" t="s">
         <v>382</v>
@@ -11472,10 +11472,10 @@
         <v>47</v>
       </c>
       <c r="O158" t="s">
-        <v>269</v>
+        <v>48</v>
       </c>
       <c r="P158" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="Q158" t="s">
         <v>47</v>
@@ -11498,28 +11498,28 @@
         <v>34</v>
       </c>
       <c r="E159" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F159" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G159" t="s">
         <v>41</v>
       </c>
       <c r="H159" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I159" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="J159" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="K159" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="L159" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M159" t="s">
         <v>382</v>
@@ -11528,10 +11528,10 @@
         <v>47</v>
       </c>
       <c r="O159" t="s">
-        <v>169</v>
+        <v>437</v>
       </c>
       <c r="P159" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="Q159" t="s">
         <v>47</v>
@@ -11554,28 +11554,28 @@
         <v>34</v>
       </c>
       <c r="E160" t="s">
-        <v>432</v>
+        <v>94</v>
       </c>
       <c r="F160" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G160" t="s">
         <v>41</v>
       </c>
       <c r="H160" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I160" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="J160" t="s">
-        <v>119</v>
+        <v>439</v>
       </c>
       <c r="K160" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="L160" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M160" t="s">
         <v>382</v>
@@ -11584,10 +11584,10 @@
         <v>47</v>
       </c>
       <c r="O160" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="P160" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q160" t="s">
         <v>47</v>
@@ -11610,28 +11610,28 @@
         <v>34</v>
       </c>
       <c r="E161" t="s">
-        <v>312</v>
+        <v>440</v>
       </c>
       <c r="F161" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G161" t="s">
         <v>41</v>
       </c>
       <c r="H161" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I161" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="J161" t="s">
-        <v>73</v>
+        <v>442</v>
       </c>
       <c r="K161" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L161" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M161" t="s">
         <v>382</v>
@@ -11640,10 +11640,10 @@
         <v>47</v>
       </c>
       <c r="O161" t="s">
-        <v>385</v>
+        <v>269</v>
       </c>
       <c r="P161" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="Q161" t="s">
         <v>47</v>
@@ -11666,28 +11666,28 @@
         <v>34</v>
       </c>
       <c r="E162" t="s">
-        <v>435</v>
+        <v>94</v>
       </c>
       <c r="F162" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G162" t="s">
         <v>41</v>
       </c>
       <c r="H162" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I162" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="J162" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="K162" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="L162" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M162" t="s">
         <v>382</v>
@@ -11696,10 +11696,10 @@
         <v>47</v>
       </c>
       <c r="O162" t="s">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="P162" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="Q162" t="s">
         <v>47</v>
@@ -11722,28 +11722,28 @@
         <v>34</v>
       </c>
       <c r="E163" t="s">
-        <v>276</v>
+        <v>440</v>
       </c>
       <c r="F163" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G163" t="s">
         <v>41</v>
       </c>
       <c r="H163" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I163" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="J163" t="s">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="K163" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="L163" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M163" t="s">
         <v>382</v>
@@ -11752,10 +11752,10 @@
         <v>47</v>
       </c>
       <c r="O163" t="s">
-        <v>169</v>
+        <v>269</v>
       </c>
       <c r="P163" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="Q163" t="s">
         <v>47</v>
@@ -11778,28 +11778,28 @@
         <v>34</v>
       </c>
       <c r="E164" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="F164" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G164" t="s">
         <v>41</v>
       </c>
       <c r="H164" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I164" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="J164" t="s">
-        <v>73</v>
+        <v>447</v>
       </c>
       <c r="K164" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L164" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M164" t="s">
         <v>382</v>
@@ -11808,10 +11808,10 @@
         <v>47</v>
       </c>
       <c r="O164" t="s">
-        <v>385</v>
+        <v>269</v>
       </c>
       <c r="P164" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="Q164" t="s">
         <v>47</v>
@@ -11834,28 +11834,28 @@
         <v>34</v>
       </c>
       <c r="E165" t="s">
-        <v>303</v>
+        <v>448</v>
       </c>
       <c r="F165" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G165" t="s">
         <v>41</v>
       </c>
       <c r="H165" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I165" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="J165" t="s">
-        <v>119</v>
+        <v>447</v>
       </c>
       <c r="K165" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="L165" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M165" t="s">
         <v>382</v>
@@ -11864,10 +11864,10 @@
         <v>47</v>
       </c>
       <c r="O165" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="P165" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="Q165" t="s">
         <v>47</v>
@@ -11890,28 +11890,28 @@
         <v>34</v>
       </c>
       <c r="E166" t="s">
-        <v>298</v>
+        <v>87</v>
       </c>
       <c r="F166" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G166" t="s">
         <v>41</v>
       </c>
       <c r="H166" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I166" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="J166" t="s">
-        <v>73</v>
+        <v>447</v>
       </c>
       <c r="K166" t="s">
         <v>73</v>
       </c>
       <c r="L166" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M166" t="s">
         <v>382</v>
@@ -11920,10 +11920,10 @@
         <v>47</v>
       </c>
       <c r="O166" t="s">
-        <v>115</v>
+        <v>412</v>
       </c>
       <c r="P166" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="Q166" t="s">
         <v>47</v>
@@ -11946,28 +11946,28 @@
         <v>34</v>
       </c>
       <c r="E167" t="s">
-        <v>442</v>
+        <v>166</v>
       </c>
       <c r="F167" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G167" t="s">
         <v>41</v>
       </c>
       <c r="H167" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I167" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="J167" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="K167" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="L167" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M167" t="s">
         <v>382</v>
@@ -11976,10 +11976,10 @@
         <v>47</v>
       </c>
       <c r="O167" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="P167" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="Q167" t="s">
         <v>47</v>
@@ -12002,28 +12002,28 @@
         <v>34</v>
       </c>
       <c r="E168" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="F168" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G168" t="s">
         <v>41</v>
       </c>
       <c r="H168" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I168" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="J168" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="K168" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="L168" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M168" t="s">
         <v>382</v>
@@ -12032,10 +12032,10 @@
         <v>47</v>
       </c>
       <c r="O168" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="P168" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="Q168" t="s">
         <v>47</v>
@@ -12058,28 +12058,28 @@
         <v>34</v>
       </c>
       <c r="E169" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="F169" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G169" t="s">
         <v>41</v>
       </c>
       <c r="H169" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I169" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="J169" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="K169" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="L169" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M169" t="s">
         <v>382</v>
@@ -12088,10 +12088,10 @@
         <v>47</v>
       </c>
       <c r="O169" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="P169" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="Q169" t="s">
         <v>47</v>
@@ -12114,19 +12114,19 @@
         <v>34</v>
       </c>
       <c r="E170" t="s">
-        <v>448</v>
+        <v>87</v>
       </c>
       <c r="F170" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G170" t="s">
         <v>41</v>
       </c>
       <c r="H170" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I170" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="J170" t="s">
         <v>73</v>
@@ -12135,7 +12135,7 @@
         <v>73</v>
       </c>
       <c r="L170" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M170" t="s">
         <v>382</v>
@@ -12144,10 +12144,10 @@
         <v>47</v>
       </c>
       <c r="O170" t="s">
-        <v>294</v>
+        <v>412</v>
       </c>
       <c r="P170" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="Q170" t="s">
         <v>47</v>
@@ -12170,28 +12170,28 @@
         <v>34</v>
       </c>
       <c r="E171" t="s">
-        <v>280</v>
+        <v>457</v>
       </c>
       <c r="F171" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G171" t="s">
         <v>41</v>
       </c>
       <c r="H171" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I171" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="J171" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="K171" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="L171" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M171" t="s">
         <v>382</v>
@@ -12200,10 +12200,10 @@
         <v>47</v>
       </c>
       <c r="O171" t="s">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="Q171" t="s">
         <v>47</v>
@@ -12226,28 +12226,28 @@
         <v>34</v>
       </c>
       <c r="E172" t="s">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="F172" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G172" t="s">
         <v>41</v>
       </c>
       <c r="H172" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I172" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="J172" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="K172" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="L172" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M172" t="s">
         <v>382</v>
@@ -12256,10 +12256,10 @@
         <v>47</v>
       </c>
       <c r="O172" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="P172" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="Q172" t="s">
         <v>47</v>
@@ -12282,19 +12282,19 @@
         <v>34</v>
       </c>
       <c r="E173" t="s">
-        <v>453</v>
+        <v>113</v>
       </c>
       <c r="F173" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G173" t="s">
         <v>41</v>
       </c>
       <c r="H173" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I173" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="J173" t="s">
         <v>73</v>
@@ -12303,7 +12303,7 @@
         <v>73</v>
       </c>
       <c r="L173" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="M173" t="s">
         <v>382</v>
@@ -12312,10 +12312,10 @@
         <v>47</v>
       </c>
       <c r="O173" t="s">
-        <v>294</v>
+        <v>115</v>
       </c>
       <c r="P173" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="Q173" t="s">
         <v>47</v>
@@ -12338,7 +12338,7 @@
         <v>34</v>
       </c>
       <c r="E174" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F174" t="s">
         <v>208</v>
@@ -12347,16 +12347,16 @@
         <v>41</v>
       </c>
       <c r="H174" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I174" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="J174" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="K174" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="L174" t="s">
         <v>34</v>
@@ -12368,10 +12368,10 @@
         <v>47</v>
       </c>
       <c r="O174" t="s">
-        <v>48</v>
+        <v>262</v>
       </c>
       <c r="P174" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="Q174" t="s">
         <v>47</v>
@@ -12394,7 +12394,7 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="F175" t="s">
         <v>208</v>
@@ -12403,16 +12403,16 @@
         <v>41</v>
       </c>
       <c r="H175" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I175" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="J175" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="K175" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="L175" t="s">
         <v>34</v>
@@ -12424,10 +12424,10 @@
         <v>47</v>
       </c>
       <c r="O175" t="s">
-        <v>459</v>
+        <v>269</v>
       </c>
       <c r="P175" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="Q175" t="s">
         <v>47</v>
@@ -12450,7 +12450,7 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>94</v>
+        <v>464</v>
       </c>
       <c r="F176" t="s">
         <v>208</v>
@@ -12459,16 +12459,16 @@
         <v>41</v>
       </c>
       <c r="H176" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I176" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="J176" t="s">
-        <v>461</v>
+        <v>78</v>
       </c>
       <c r="K176" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L176" t="s">
         <v>34</v>
@@ -12480,10 +12480,10 @@
         <v>47</v>
       </c>
       <c r="O176" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="P176" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="Q176" t="s">
         <v>47</v>
@@ -12506,7 +12506,7 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F177" t="s">
         <v>208</v>
@@ -12515,16 +12515,16 @@
         <v>41</v>
       </c>
       <c r="H177" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I177" t="s">
         <v>463</v>
       </c>
       <c r="J177" t="s">
-        <v>464</v>
+        <v>68</v>
       </c>
       <c r="K177" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="L177" t="s">
         <v>34</v>
@@ -12536,7 +12536,7 @@
         <v>47</v>
       </c>
       <c r="O177" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="P177" t="s">
         <v>463</v>
@@ -12562,7 +12562,7 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>94</v>
+        <v>466</v>
       </c>
       <c r="F178" t="s">
         <v>208</v>
@@ -12571,16 +12571,16 @@
         <v>41</v>
       </c>
       <c r="H178" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I178" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J178" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="K178" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L178" t="s">
         <v>34</v>
@@ -12592,10 +12592,10 @@
         <v>47</v>
       </c>
       <c r="O178" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="P178" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="Q178" t="s">
         <v>47</v>
@@ -12618,7 +12618,7 @@
         <v>34</v>
       </c>
       <c r="E179" t="s">
-        <v>462</v>
+        <v>150</v>
       </c>
       <c r="F179" t="s">
         <v>208</v>
@@ -12627,16 +12627,16 @@
         <v>41</v>
       </c>
       <c r="H179" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I179" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="J179" t="s">
-        <v>461</v>
+        <v>120</v>
       </c>
       <c r="K179" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L179" t="s">
         <v>34</v>
@@ -12648,10 +12648,10 @@
         <v>47</v>
       </c>
       <c r="O179" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="P179" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="Q179" t="s">
         <v>47</v>
@@ -12674,7 +12674,7 @@
         <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>393</v>
+        <v>110</v>
       </c>
       <c r="F180" t="s">
         <v>208</v>
@@ -12683,16 +12683,16 @@
         <v>41</v>
       </c>
       <c r="H180" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I180" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J180" t="s">
-        <v>468</v>
+        <v>105</v>
       </c>
       <c r="K180" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L180" t="s">
         <v>34</v>
@@ -12704,10 +12704,10 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="P180" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q180" t="s">
         <v>47</v>
@@ -12739,16 +12739,16 @@
         <v>41</v>
       </c>
       <c r="H181" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I181" t="s">
         <v>470</v>
       </c>
       <c r="J181" t="s">
-        <v>468</v>
+        <v>73</v>
       </c>
       <c r="K181" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L181" t="s">
         <v>34</v>
@@ -12760,7 +12760,7 @@
         <v>47</v>
       </c>
       <c r="O181" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="P181" t="s">
         <v>470</v>
@@ -12786,7 +12786,7 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="F182" t="s">
         <v>208</v>
@@ -12795,16 +12795,16 @@
         <v>41</v>
       </c>
       <c r="H182" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I182" t="s">
-        <v>399</v>
+        <v>463</v>
       </c>
       <c r="J182" t="s">
-        <v>468</v>
+        <v>120</v>
       </c>
       <c r="K182" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="L182" t="s">
         <v>34</v>
@@ -12816,10 +12816,10 @@
         <v>47</v>
       </c>
       <c r="O182" t="s">
-        <v>385</v>
+        <v>152</v>
       </c>
       <c r="P182" t="s">
-        <v>399</v>
+        <v>463</v>
       </c>
       <c r="Q182" t="s">
         <v>47</v>
@@ -12842,7 +12842,7 @@
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>166</v>
+        <v>471</v>
       </c>
       <c r="F183" t="s">
         <v>208</v>
@@ -12851,16 +12851,16 @@
         <v>41</v>
       </c>
       <c r="H183" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I183" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J183" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K183" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L183" t="s">
         <v>34</v>
@@ -12872,10 +12872,10 @@
         <v>47</v>
       </c>
       <c r="O183" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="P183" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Q183" t="s">
         <v>47</v>
@@ -12898,7 +12898,7 @@
         <v>34</v>
       </c>
       <c r="E184" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F184" t="s">
         <v>208</v>
@@ -12907,16 +12907,16 @@
         <v>41</v>
       </c>
       <c r="H184" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I184" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J184" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="K184" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L184" t="s">
         <v>34</v>
@@ -12928,10 +12928,10 @@
         <v>47</v>
       </c>
       <c r="O184" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="P184" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q184" t="s">
         <v>47</v>
@@ -12954,7 +12954,7 @@
         <v>34</v>
       </c>
       <c r="E185" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F185" t="s">
         <v>208</v>
@@ -12963,16 +12963,16 @@
         <v>41</v>
       </c>
       <c r="H185" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I185" t="s">
         <v>475</v>
       </c>
       <c r="J185" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K185" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L185" t="s">
         <v>34</v>
@@ -12984,7 +12984,7 @@
         <v>47</v>
       </c>
       <c r="O185" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="P185" t="s">
         <v>475</v>
@@ -14048,7 +14048,7 @@
         <v>47</v>
       </c>
       <c r="O204" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="P204" t="s">
         <v>501</v>
@@ -14832,7 +14832,7 @@
         <v>47</v>
       </c>
       <c r="O218" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="P218" t="s">
         <v>523</v>
@@ -15392,7 +15392,7 @@
         <v>47</v>
       </c>
       <c r="O228" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="P228" t="s">
         <v>501</v>
@@ -16120,7 +16120,7 @@
         <v>47</v>
       </c>
       <c r="O241" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="P241" t="s">
         <v>535</v>
@@ -17490,25 +17490,25 @@
         <v>33</v>
       </c>
       <c r="E266" t="s">
-        <v>263</v>
+        <v>565</v>
       </c>
       <c r="F266" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
       <c r="G266" t="s">
         <v>41</v>
       </c>
       <c r="H266" t="s">
-        <v>565</v>
+        <v>192</v>
       </c>
       <c r="I266" t="s">
-        <v>491</v>
+        <v>550</v>
       </c>
       <c r="J266" t="s">
-        <v>566</v>
+        <v>124</v>
       </c>
       <c r="K266" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L266" t="s">
         <v>34</v>
@@ -17520,13 +17520,13 @@
         <v>47</v>
       </c>
       <c r="O266" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="P266" t="s">
-        <v>491</v>
+        <v>34</v>
       </c>
       <c r="Q266" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R266" t="s">
         <v>34</v>
@@ -17546,25 +17546,25 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>250</v>
+        <v>391</v>
       </c>
       <c r="F267" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
       <c r="G267" t="s">
         <v>41</v>
       </c>
       <c r="H267" t="s">
-        <v>565</v>
+        <v>192</v>
       </c>
       <c r="I267" t="s">
-        <v>567</v>
+        <v>494</v>
       </c>
       <c r="J267" t="s">
-        <v>568</v>
+        <v>165</v>
       </c>
       <c r="K267" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="L267" t="s">
         <v>34</v>
@@ -17576,13 +17576,13 @@
         <v>47</v>
       </c>
       <c r="O267" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="P267" t="s">
-        <v>567</v>
+        <v>34</v>
       </c>
       <c r="Q267" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R267" t="s">
         <v>34</v>
@@ -17602,25 +17602,25 @@
         <v>34</v>
       </c>
       <c r="E268" t="s">
-        <v>258</v>
+        <v>566</v>
       </c>
       <c r="F268" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
       <c r="G268" t="s">
         <v>41</v>
       </c>
       <c r="H268" t="s">
-        <v>569</v>
+        <v>192</v>
       </c>
       <c r="I268" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="J268" t="s">
-        <v>568</v>
+        <v>119</v>
       </c>
       <c r="K268" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L268" t="s">
         <v>34</v>
@@ -17632,13 +17632,13 @@
         <v>47</v>
       </c>
       <c r="O268" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="P268" t="s">
-        <v>502</v>
+        <v>34</v>
       </c>
       <c r="Q268" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R268" t="s">
         <v>34</v>
@@ -17658,25 +17658,25 @@
         <v>34</v>
       </c>
       <c r="E269" t="s">
-        <v>265</v>
+        <v>567</v>
       </c>
       <c r="F269" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
       <c r="G269" t="s">
         <v>41</v>
       </c>
       <c r="H269" t="s">
-        <v>570</v>
+        <v>192</v>
       </c>
       <c r="I269" t="s">
-        <v>497</v>
+        <v>568</v>
       </c>
       <c r="J269" t="s">
-        <v>571</v>
+        <v>78</v>
       </c>
       <c r="K269" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="L269" t="s">
         <v>34</v>
@@ -17688,13 +17688,13 @@
         <v>47</v>
       </c>
       <c r="O269" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="P269" t="s">
-        <v>497</v>
+        <v>34</v>
       </c>
       <c r="Q269" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R269" t="s">
         <v>34</v>
@@ -17714,22 +17714,22 @@
         <v>34</v>
       </c>
       <c r="E270" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="F270" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
       <c r="G270" t="s">
         <v>41</v>
       </c>
       <c r="H270" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="I270" t="s">
-        <v>573</v>
+        <v>501</v>
       </c>
       <c r="J270" t="s">
-        <v>571</v>
+        <v>73</v>
       </c>
       <c r="K270" t="s">
         <v>73</v>
@@ -17744,13 +17744,13 @@
         <v>47</v>
       </c>
       <c r="O270" t="s">
-        <v>294</v>
+        <v>34</v>
       </c>
       <c r="P270" t="s">
-        <v>573</v>
+        <v>34</v>
       </c>
       <c r="Q270" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R270" t="s">
         <v>34</v>
@@ -17779,13 +17779,13 @@
         <v>41</v>
       </c>
       <c r="H271" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="I271" t="s">
         <v>495</v>
       </c>
       <c r="J271" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="K271" t="s">
         <v>133</v>
@@ -17826,7 +17826,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="F272" t="s">
         <v>247</v>
@@ -17835,16 +17835,16 @@
         <v>41</v>
       </c>
       <c r="H272" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="I272" t="s">
-        <v>498</v>
+        <v>572</v>
       </c>
       <c r="J272" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="K272" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L272" t="s">
         <v>34</v>
@@ -17856,10 +17856,10 @@
         <v>47</v>
       </c>
       <c r="O272" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="P272" t="s">
-        <v>498</v>
+        <v>572</v>
       </c>
       <c r="Q272" t="s">
         <v>47</v>
@@ -17882,7 +17882,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="F273" t="s">
         <v>247</v>
@@ -17891,16 +17891,16 @@
         <v>41</v>
       </c>
       <c r="H273" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="I273" t="s">
-        <v>575</v>
+        <v>497</v>
       </c>
       <c r="J273" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="K273" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="L273" t="s">
         <v>34</v>
@@ -17912,10 +17912,10 @@
         <v>47</v>
       </c>
       <c r="O273" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="P273" t="s">
-        <v>575</v>
+        <v>497</v>
       </c>
       <c r="Q273" t="s">
         <v>47</v>
@@ -17938,7 +17938,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="F274" t="s">
         <v>247</v>
@@ -17947,16 +17947,16 @@
         <v>41</v>
       </c>
       <c r="H274" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="I274" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="J274" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="K274" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L274" t="s">
         <v>34</v>
@@ -17968,10 +17968,10 @@
         <v>47</v>
       </c>
       <c r="O274" t="s">
-        <v>269</v>
+        <v>115</v>
       </c>
       <c r="P274" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="Q274" t="s">
         <v>47</v>
@@ -17994,7 +17994,7 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F275" t="s">
         <v>247</v>
@@ -18003,16 +18003,16 @@
         <v>41</v>
       </c>
       <c r="H275" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="I275" t="s">
-        <v>500</v>
+        <v>577</v>
       </c>
       <c r="J275" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="K275" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="L275" t="s">
         <v>34</v>
@@ -18024,10 +18024,10 @@
         <v>47</v>
       </c>
       <c r="O275" t="s">
-        <v>385</v>
+        <v>112</v>
       </c>
       <c r="P275" t="s">
-        <v>500</v>
+        <v>577</v>
       </c>
       <c r="Q275" t="s">
         <v>47</v>
@@ -18050,7 +18050,7 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="F276" t="s">
         <v>247</v>
@@ -18059,16 +18059,16 @@
         <v>41</v>
       </c>
       <c r="H276" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="I276" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="J276" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="K276" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L276" t="s">
         <v>34</v>
@@ -18080,10 +18080,10 @@
         <v>47</v>
       </c>
       <c r="O276" t="s">
-        <v>86</v>
+        <v>149</v>
       </c>
       <c r="P276" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="Q276" t="s">
         <v>47</v>
@@ -18106,7 +18106,7 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
-        <v>576</v>
+        <v>260</v>
       </c>
       <c r="F277" t="s">
         <v>247</v>
@@ -18115,16 +18115,16 @@
         <v>41</v>
       </c>
       <c r="H277" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="I277" t="s">
-        <v>577</v>
+        <v>498</v>
       </c>
       <c r="J277" t="s">
-        <v>182</v>
+        <v>578</v>
       </c>
       <c r="K277" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="L277" t="s">
         <v>34</v>
@@ -18136,10 +18136,10 @@
         <v>47</v>
       </c>
       <c r="O277" t="s">
-        <v>578</v>
+        <v>262</v>
       </c>
       <c r="P277" t="s">
-        <v>577</v>
+        <v>498</v>
       </c>
       <c r="Q277" t="s">
         <v>47</v>
@@ -18162,7 +18162,7 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="F278" t="s">
         <v>247</v>
@@ -18171,16 +18171,16 @@
         <v>41</v>
       </c>
       <c r="H278" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="I278" t="s">
         <v>579</v>
       </c>
       <c r="J278" t="s">
-        <v>182</v>
+        <v>578</v>
       </c>
       <c r="K278" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L278" t="s">
         <v>34</v>
@@ -18192,7 +18192,7 @@
         <v>47</v>
       </c>
       <c r="O278" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="P278" t="s">
         <v>579</v>
@@ -18218,25 +18218,25 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>580</v>
+        <v>267</v>
       </c>
       <c r="F279" t="s">
-        <v>484</v>
+        <v>247</v>
       </c>
       <c r="G279" t="s">
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>192</v>
+        <v>570</v>
       </c>
       <c r="I279" t="s">
-        <v>581</v>
+        <v>496</v>
       </c>
       <c r="J279" t="s">
-        <v>78</v>
+        <v>578</v>
       </c>
       <c r="K279" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="L279" t="s">
         <v>34</v>
@@ -18248,13 +18248,13 @@
         <v>47</v>
       </c>
       <c r="O279" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="P279" t="s">
-        <v>34</v>
+        <v>496</v>
       </c>
       <c r="Q279" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R279" t="s">
         <v>34</v>
@@ -18274,7 +18274,7 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>414</v>
+        <v>580</v>
       </c>
       <c r="F280" t="s">
         <v>484</v>
@@ -18286,13 +18286,13 @@
         <v>192</v>
       </c>
       <c r="I280" t="s">
-        <v>494</v>
+        <v>581</v>
       </c>
       <c r="J280" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="K280" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="L280" t="s">
         <v>34</v>
@@ -18330,25 +18330,25 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
-        <v>582</v>
+        <v>246</v>
       </c>
       <c r="F281" t="s">
-        <v>484</v>
+        <v>247</v>
       </c>
       <c r="G281" t="s">
         <v>41</v>
       </c>
       <c r="H281" t="s">
-        <v>192</v>
+        <v>570</v>
       </c>
       <c r="I281" t="s">
-        <v>550</v>
+        <v>503</v>
       </c>
       <c r="J281" t="s">
-        <v>124</v>
+        <v>578</v>
       </c>
       <c r="K281" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="L281" t="s">
         <v>34</v>
@@ -18360,13 +18360,13 @@
         <v>47</v>
       </c>
       <c r="O281" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="P281" t="s">
-        <v>34</v>
+        <v>503</v>
       </c>
       <c r="Q281" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R281" t="s">
         <v>34</v>
@@ -18386,25 +18386,25 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
+        <v>582</v>
+      </c>
+      <c r="F282" t="s">
+        <v>247</v>
+      </c>
+      <c r="G282" t="s">
+        <v>41</v>
+      </c>
+      <c r="H282" t="s">
+        <v>569</v>
+      </c>
+      <c r="I282" t="s">
         <v>583</v>
       </c>
-      <c r="F282" t="s">
-        <v>484</v>
-      </c>
-      <c r="G282" t="s">
-        <v>41</v>
-      </c>
-      <c r="H282" t="s">
-        <v>192</v>
-      </c>
-      <c r="I282" t="s">
-        <v>489</v>
-      </c>
       <c r="J282" t="s">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="K282" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="L282" t="s">
         <v>34</v>
@@ -18416,13 +18416,13 @@
         <v>47</v>
       </c>
       <c r="O282" t="s">
-        <v>34</v>
+        <v>584</v>
       </c>
       <c r="P282" t="s">
-        <v>34</v>
+        <v>583</v>
       </c>
       <c r="Q282" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R282" t="s">
         <v>34</v>
@@ -18442,25 +18442,25 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>333</v>
+        <v>254</v>
       </c>
       <c r="F283" t="s">
-        <v>484</v>
+        <v>247</v>
       </c>
       <c r="G283" t="s">
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="I283" t="s">
-        <v>501</v>
+        <v>585</v>
       </c>
       <c r="J283" t="s">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="K283" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L283" t="s">
         <v>34</v>
@@ -18472,13 +18472,13 @@
         <v>47</v>
       </c>
       <c r="O283" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="P283" t="s">
-        <v>34</v>
+        <v>585</v>
       </c>
       <c r="Q283" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R283" t="s">
         <v>34</v>
@@ -18498,25 +18498,25 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>584</v>
+        <v>256</v>
       </c>
       <c r="F284" t="s">
-        <v>484</v>
+        <v>247</v>
       </c>
       <c r="G284" t="s">
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>192</v>
+        <v>570</v>
       </c>
       <c r="I284" t="s">
-        <v>585</v>
+        <v>500</v>
       </c>
       <c r="J284" t="s">
-        <v>78</v>
+        <v>578</v>
       </c>
       <c r="K284" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L284" t="s">
         <v>34</v>
@@ -18528,13 +18528,13 @@
         <v>47</v>
       </c>
       <c r="O284" t="s">
-        <v>34</v>
+        <v>412</v>
       </c>
       <c r="P284" t="s">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="Q284" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R284" t="s">
         <v>34</v>
@@ -18834,7 +18834,7 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>405</v>
+        <v>473</v>
       </c>
       <c r="F290" t="s">
         <v>208</v>
@@ -19114,7 +19114,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="F295" t="s">
         <v>208</v>
@@ -19170,7 +19170,7 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="F296" t="s">
         <v>208</v>
@@ -19312,7 +19312,7 @@
         <v>47</v>
       </c>
       <c r="O298" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="P298" t="s">
         <v>608</v>
@@ -19536,7 +19536,7 @@
         <v>47</v>
       </c>
       <c r="O302" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="P302" t="s">
         <v>608</v>
@@ -20246,7 +20246,7 @@
         <v>638</v>
       </c>
       <c r="I315" t="s">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="J315" t="s">
         <v>105</v>
@@ -20267,7 +20267,7 @@
         <v>112</v>
       </c>
       <c r="P315" t="s">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="Q315" t="s">
         <v>47</v>
@@ -20290,7 +20290,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>405</v>
+        <v>473</v>
       </c>
       <c r="F316" t="s">
         <v>208</v>
@@ -20402,7 +20402,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="F318" t="s">
         <v>208</v>
@@ -20529,7 +20529,7 @@
         <v>650</v>
       </c>
       <c r="J320" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="K320" t="s">
         <v>73</v>
@@ -20585,7 +20585,7 @@
         <v>651</v>
       </c>
       <c r="J321" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="K321" t="s">
         <v>105</v>
@@ -20962,7 +20962,7 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="F328" t="s">
         <v>208</v>
@@ -23049,7 +23049,7 @@
         <v>731</v>
       </c>
       <c r="J365" t="s">
-        <v>369</v>
+        <v>329</v>
       </c>
       <c r="K365" t="s">
         <v>45</v>
@@ -23538,28 +23538,28 @@
         <v>33</v>
       </c>
       <c r="E374" t="s">
+        <v>724</v>
+      </c>
+      <c r="F374" t="s">
+        <v>40</v>
+      </c>
+      <c r="G374" t="s">
+        <v>41</v>
+      </c>
+      <c r="H374" t="s">
         <v>757</v>
       </c>
-      <c r="F374" t="s">
-        <v>208</v>
-      </c>
-      <c r="G374" t="s">
-        <v>41</v>
-      </c>
-      <c r="H374" t="s">
-        <v>572</v>
-      </c>
       <c r="I374" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="J374" t="s">
-        <v>530</v>
+        <v>329</v>
       </c>
       <c r="K374" t="s">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="L374" t="s">
-        <v>34</v>
+        <v>759</v>
       </c>
       <c r="M374" t="s">
         <v>756</v>
@@ -23571,7 +23571,7 @@
         <v>48</v>
       </c>
       <c r="P374" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="Q374" t="s">
         <v>47</v>
@@ -23594,7 +23594,7 @@
         <v>34</v>
       </c>
       <c r="E375" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="F375" t="s">
         <v>40</v>
@@ -23603,19 +23603,19 @@
         <v>41</v>
       </c>
       <c r="H375" t="s">
-        <v>485</v>
+        <v>760</v>
       </c>
       <c r="I375" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="J375" t="s">
-        <v>67</v>
+        <v>727</v>
       </c>
       <c r="K375" t="s">
         <v>45</v>
       </c>
       <c r="L375" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="M375" t="s">
         <v>756</v>
@@ -23627,7 +23627,7 @@
         <v>48</v>
       </c>
       <c r="P375" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="Q375" t="s">
         <v>47</v>
@@ -23659,10 +23659,10 @@
         <v>41</v>
       </c>
       <c r="H376" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="I376" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="J376" t="s">
         <v>727</v>
@@ -23671,7 +23671,7 @@
         <v>45</v>
       </c>
       <c r="L376" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="M376" t="s">
         <v>756</v>
@@ -23683,7 +23683,7 @@
         <v>48</v>
       </c>
       <c r="P376" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="Q376" t="s">
         <v>47</v>
@@ -23706,7 +23706,7 @@
         <v>34</v>
       </c>
       <c r="E377" t="s">
-        <v>724</v>
+        <v>227</v>
       </c>
       <c r="F377" t="s">
         <v>40</v>
@@ -23715,19 +23715,19 @@
         <v>41</v>
       </c>
       <c r="H377" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="I377" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
       <c r="J377" t="s">
-        <v>727</v>
+        <v>767</v>
       </c>
       <c r="K377" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="L377" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="M377" t="s">
         <v>756</v>
@@ -23739,7 +23739,7 @@
         <v>48</v>
       </c>
       <c r="P377" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
       <c r="Q377" t="s">
         <v>47</v>
@@ -23762,7 +23762,7 @@
         <v>34</v>
       </c>
       <c r="E378" t="s">
-        <v>227</v>
+        <v>724</v>
       </c>
       <c r="F378" t="s">
         <v>40</v>
@@ -23771,19 +23771,19 @@
         <v>41</v>
       </c>
       <c r="H378" t="s">
-        <v>508</v>
+        <v>769</v>
       </c>
       <c r="I378" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="J378" t="s">
-        <v>766</v>
+        <v>727</v>
       </c>
       <c r="K378" t="s">
         <v>45</v>
       </c>
       <c r="L378" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="M378" t="s">
         <v>756</v>
@@ -23795,7 +23795,7 @@
         <v>48</v>
       </c>
       <c r="P378" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="Q378" t="s">
         <v>47</v>
@@ -23827,19 +23827,19 @@
         <v>41</v>
       </c>
       <c r="H379" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="I379" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="J379" t="s">
-        <v>369</v>
+        <v>727</v>
       </c>
       <c r="K379" t="s">
         <v>45</v>
       </c>
       <c r="L379" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="M379" t="s">
         <v>756</v>
@@ -23851,7 +23851,7 @@
         <v>48</v>
       </c>
       <c r="P379" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="Q379" t="s">
         <v>47</v>
@@ -23883,19 +23883,19 @@
         <v>41</v>
       </c>
       <c r="H380" t="s">
-        <v>565</v>
+        <v>508</v>
       </c>
       <c r="I380" t="s">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="J380" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="K380" t="s">
         <v>45</v>
       </c>
       <c r="L380" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="M380" t="s">
         <v>756</v>
@@ -23907,7 +23907,7 @@
         <v>48</v>
       </c>
       <c r="P380" t="s">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="Q380" t="s">
         <v>47</v>
@@ -23939,10 +23939,10 @@
         <v>41</v>
       </c>
       <c r="H381" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="I381" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="J381" t="s">
         <v>727</v>
@@ -23951,7 +23951,7 @@
         <v>45</v>
       </c>
       <c r="L381" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="M381" t="s">
         <v>756</v>
@@ -23963,7 +23963,7 @@
         <v>48</v>
       </c>
       <c r="P381" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="Q381" t="s">
         <v>47</v>
@@ -23986,7 +23986,7 @@
         <v>34</v>
       </c>
       <c r="E382" t="s">
-        <v>724</v>
+        <v>227</v>
       </c>
       <c r="F382" t="s">
         <v>40</v>
@@ -23995,19 +23995,19 @@
         <v>41</v>
       </c>
       <c r="H382" t="s">
-        <v>776</v>
+        <v>569</v>
       </c>
       <c r="I382" t="s">
-        <v>777</v>
+        <v>750</v>
       </c>
       <c r="J382" t="s">
-        <v>727</v>
+        <v>780</v>
       </c>
       <c r="K382" t="s">
         <v>45</v>
       </c>
       <c r="L382" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="M382" t="s">
         <v>756</v>
@@ -24019,7 +24019,7 @@
         <v>48</v>
       </c>
       <c r="P382" t="s">
-        <v>777</v>
+        <v>750</v>
       </c>
       <c r="Q382" t="s">
         <v>47</v>
@@ -24051,10 +24051,10 @@
         <v>41</v>
       </c>
       <c r="H383" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="I383" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="J383" t="s">
         <v>727</v>
@@ -24063,7 +24063,7 @@
         <v>45</v>
       </c>
       <c r="L383" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="M383" t="s">
         <v>756</v>
@@ -24075,7 +24075,7 @@
         <v>48</v>
       </c>
       <c r="P383" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="Q383" t="s">
         <v>47</v>
@@ -24098,7 +24098,7 @@
         <v>34</v>
       </c>
       <c r="E384" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="F384" t="s">
         <v>40</v>
@@ -24107,19 +24107,19 @@
         <v>41</v>
       </c>
       <c r="H384" t="s">
-        <v>782</v>
+        <v>485</v>
       </c>
       <c r="I384" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="J384" t="s">
-        <v>727</v>
+        <v>67</v>
       </c>
       <c r="K384" t="s">
         <v>45</v>
       </c>
       <c r="L384" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="M384" t="s">
         <v>756</v>
@@ -24131,7 +24131,7 @@
         <v>48</v>
       </c>
       <c r="P384" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="Q384" t="s">
         <v>47</v>
@@ -24154,28 +24154,28 @@
         <v>34</v>
       </c>
       <c r="E385" t="s">
-        <v>227</v>
+        <v>787</v>
       </c>
       <c r="F385" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G385" t="s">
         <v>41</v>
       </c>
       <c r="H385" t="s">
-        <v>785</v>
+        <v>570</v>
       </c>
       <c r="I385" t="s">
-        <v>786</v>
+        <v>750</v>
       </c>
       <c r="J385" t="s">
-        <v>766</v>
+        <v>530</v>
       </c>
       <c r="K385" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="L385" t="s">
-        <v>787</v>
+        <v>34</v>
       </c>
       <c r="M385" t="s">
         <v>756</v>
@@ -24187,7 +24187,7 @@
         <v>48</v>
       </c>
       <c r="P385" t="s">
-        <v>786</v>
+        <v>750</v>
       </c>
       <c r="Q385" t="s">
         <v>47</v>
@@ -26241,7 +26241,7 @@
         <v>904</v>
       </c>
       <c r="J422" t="s">
-        <v>373</v>
+        <v>325</v>
       </c>
       <c r="K422" t="s">
         <v>45</v>
@@ -26297,7 +26297,7 @@
         <v>906</v>
       </c>
       <c r="J423" t="s">
-        <v>369</v>
+        <v>329</v>
       </c>
       <c r="K423" t="s">
         <v>674</v>
@@ -26409,7 +26409,7 @@
         <v>912</v>
       </c>
       <c r="J425" t="s">
-        <v>369</v>
+        <v>329</v>
       </c>
       <c r="K425" t="s">
         <v>45</v>
@@ -26913,7 +26913,7 @@
         <v>945</v>
       </c>
       <c r="J434" t="s">
-        <v>373</v>
+        <v>325</v>
       </c>
       <c r="K434" t="s">
         <v>45</v>
@@ -27570,7 +27570,7 @@
         <v>34</v>
       </c>
       <c r="E446" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="F446" t="s">
         <v>247</v>
@@ -27585,10 +27585,10 @@
         <v>970</v>
       </c>
       <c r="J446" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="K446" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L446" t="s">
         <v>969</v>
@@ -27600,7 +27600,7 @@
         <v>47</v>
       </c>
       <c r="O446" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="P446" t="s">
         <v>970</v>
@@ -27626,7 +27626,7 @@
         <v>34</v>
       </c>
       <c r="E447" t="s">
-        <v>254</v>
+        <v>518</v>
       </c>
       <c r="F447" t="s">
         <v>247</v>
@@ -27635,16 +27635,16 @@
         <v>41</v>
       </c>
       <c r="H447" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="I447" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="J447" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="K447" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L447" t="s">
         <v>969</v>
@@ -27656,10 +27656,10 @@
         <v>47</v>
       </c>
       <c r="O447" t="s">
-        <v>98</v>
+        <v>521</v>
       </c>
       <c r="P447" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="Q447" t="s">
         <v>47</v>
@@ -27682,7 +27682,7 @@
         <v>34</v>
       </c>
       <c r="E448" t="s">
-        <v>518</v>
+        <v>267</v>
       </c>
       <c r="F448" t="s">
         <v>247</v>
@@ -27691,16 +27691,16 @@
         <v>41</v>
       </c>
       <c r="H448" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="I448" t="s">
         <v>973</v>
       </c>
       <c r="J448" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="K448" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="L448" t="s">
         <v>969</v>
@@ -27712,7 +27712,7 @@
         <v>47</v>
       </c>
       <c r="O448" t="s">
-        <v>521</v>
+        <v>269</v>
       </c>
       <c r="P448" t="s">
         <v>973</v>
@@ -27738,7 +27738,7 @@
         <v>34</v>
       </c>
       <c r="E449" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F449" t="s">
         <v>247</v>
@@ -27768,7 +27768,7 @@
         <v>47</v>
       </c>
       <c r="O449" t="s">
-        <v>269</v>
+        <v>149</v>
       </c>
       <c r="P449" t="s">
         <v>974</v>
@@ -27794,7 +27794,7 @@
         <v>34</v>
       </c>
       <c r="E450" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="F450" t="s">
         <v>247</v>
@@ -27809,10 +27809,10 @@
         <v>975</v>
       </c>
       <c r="J450" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="K450" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="L450" t="s">
         <v>969</v>
@@ -27824,7 +27824,7 @@
         <v>47</v>
       </c>
       <c r="O450" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="P450" t="s">
         <v>975</v>
@@ -27850,7 +27850,7 @@
         <v>34</v>
       </c>
       <c r="E451" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="F451" t="s">
         <v>247</v>
@@ -27865,10 +27865,10 @@
         <v>976</v>
       </c>
       <c r="J451" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="K451" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="L451" t="s">
         <v>969</v>
@@ -27880,7 +27880,7 @@
         <v>47</v>
       </c>
       <c r="O451" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="P451" t="s">
         <v>976</v>
@@ -27906,7 +27906,7 @@
         <v>34</v>
       </c>
       <c r="E452" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="F452" t="s">
         <v>247</v>
@@ -27921,10 +27921,10 @@
         <v>977</v>
       </c>
       <c r="J452" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="K452" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="L452" t="s">
         <v>969</v>
@@ -27936,7 +27936,7 @@
         <v>47</v>
       </c>
       <c r="O452" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="P452" t="s">
         <v>977</v>
@@ -27962,7 +27962,7 @@
         <v>34</v>
       </c>
       <c r="E453" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="F453" t="s">
         <v>247</v>
@@ -27971,10 +27971,10 @@
         <v>41</v>
       </c>
       <c r="H453" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="I453" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="J453" t="s">
         <v>73</v>
@@ -27992,10 +27992,10 @@
         <v>47</v>
       </c>
       <c r="O453" t="s">
-        <v>385</v>
+        <v>294</v>
       </c>
       <c r="P453" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="Q453" t="s">
         <v>47</v>
@@ -28018,7 +28018,7 @@
         <v>34</v>
       </c>
       <c r="E454" t="s">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="F454" t="s">
         <v>247</v>
@@ -28027,10 +28027,10 @@
         <v>41</v>
       </c>
       <c r="H454" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="I454" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="J454" t="s">
         <v>73</v>
@@ -28048,10 +28048,10 @@
         <v>47</v>
       </c>
       <c r="O454" t="s">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="P454" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="Q454" t="s">
         <v>47</v>
@@ -28074,7 +28074,7 @@
         <v>34</v>
       </c>
       <c r="E455" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="F455" t="s">
         <v>247</v>
@@ -28086,13 +28086,13 @@
         <v>967</v>
       </c>
       <c r="I455" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="J455" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K455" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L455" t="s">
         <v>969</v>
@@ -28104,10 +28104,10 @@
         <v>47</v>
       </c>
       <c r="O455" t="s">
-        <v>330</v>
+        <v>262</v>
       </c>
       <c r="P455" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="Q455" t="s">
         <v>47</v>
@@ -28130,7 +28130,7 @@
         <v>34</v>
       </c>
       <c r="E456" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F456" t="s">
         <v>247</v>
@@ -28142,13 +28142,13 @@
         <v>967</v>
       </c>
       <c r="I456" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="J456" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K456" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L456" t="s">
         <v>969</v>
@@ -28160,10 +28160,10 @@
         <v>47</v>
       </c>
       <c r="O456" t="s">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="P456" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="Q456" t="s">
         <v>47</v>
@@ -28186,7 +28186,7 @@
         <v>34</v>
       </c>
       <c r="E457" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="F457" t="s">
         <v>247</v>
@@ -28198,13 +28198,13 @@
         <v>967</v>
       </c>
       <c r="I457" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="J457" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="K457" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="L457" t="s">
         <v>969</v>
@@ -28216,10 +28216,10 @@
         <v>47</v>
       </c>
       <c r="O457" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P457" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="Q457" t="s">
         <v>47</v>
@@ -28242,7 +28242,7 @@
         <v>34</v>
       </c>
       <c r="E458" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F458" t="s">
         <v>247</v>
@@ -28254,13 +28254,13 @@
         <v>967</v>
       </c>
       <c r="I458" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="J458" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="K458" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="L458" t="s">
         <v>969</v>
@@ -28272,10 +28272,10 @@
         <v>47</v>
       </c>
       <c r="O458" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="P458" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="Q458" t="s">
         <v>47</v>

--- a/xlsx/dre/DRE_03_2026.xlsx
+++ b/xlsx/dre/DRE_03_2026.xlsx
@@ -588,6 +588,21 @@
     <t>R$  4.689,29</t>
   </si>
   <si>
+    <t>12/1</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  736,71</t>
+  </si>
+  <si>
+    <t>23/04/26</t>
+  </si>
+  <si>
+    <t>Digisac</t>
+  </si>
+  <si>
     <t>5/1</t>
   </si>
   <si>
@@ -599,21 +614,6 @@
   <si>
     <t xml:space="preserve">Reembolso Pushing
 </t>
-  </si>
-  <si>
-    <t>12/1</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  736,71</t>
-  </si>
-  <si>
-    <t>23/04/26</t>
-  </si>
-  <si>
-    <t>Digisac</t>
   </si>
   <si>
     <t>9/1</t>
@@ -2190,6 +2190,48 @@
     <t>R$ 9.161,99</t>
   </si>
   <si>
+    <t>12/3</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>01/03/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
+    <t>1/1</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>R$  3.750,00</t>
+  </si>
+  <si>
+    <t>30/03/26</t>
+  </si>
+  <si>
+    <t>Facebook 2026</t>
+  </si>
+  <si>
     <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
   </si>
   <si>
@@ -2202,48 +2244,6 @@
     <t>Webgiga 2026</t>
   </si>
   <si>
-    <t>12/3</t>
-  </si>
-  <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>01/03/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
-    <t>1/1</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>R$  3.750,00</t>
-  </si>
-  <si>
-    <t>30/03/26</t>
-  </si>
-  <si>
-    <t>Facebook 2026</t>
-  </si>
-  <si>
     <t>4.03.03.09.06 Marketing - outros gastos (CV)</t>
   </si>
   <si>
@@ -2628,6 +2628,24 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
+    <t>593/1</t>
+  </si>
+  <si>
+    <t>Pão de Açúcar</t>
+  </si>
+  <si>
+    <t>R$  98,44</t>
+  </si>
+  <si>
+    <t>594/1</t>
+  </si>
+  <si>
+    <t>Marinete</t>
+  </si>
+  <si>
+    <t>R$  19,98</t>
+  </si>
+  <si>
     <t>595/1</t>
   </si>
   <si>
@@ -2638,24 +2656,6 @@
   </si>
   <si>
     <t>Cafés loja</t>
-  </si>
-  <si>
-    <t>593/1</t>
-  </si>
-  <si>
-    <t>Pão de Açúcar</t>
-  </si>
-  <si>
-    <t>R$  98,44</t>
-  </si>
-  <si>
-    <t>594/1</t>
-  </si>
-  <si>
-    <t>Marinete</t>
-  </si>
-  <si>
-    <t>R$  19,98</t>
   </si>
   <si>
     <t>569/1</t>
@@ -2744,6 +2744,30 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>592/1</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>R$  198,99</t>
+  </si>
+  <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>3/2</t>
   </si>
   <si>
@@ -2753,30 +2777,6 @@
     <t>Promob 2026/2</t>
   </si>
   <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>592/1</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>R$  198,99</t>
-  </si>
-  <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
   </si>
   <si>
@@ -2843,6 +2843,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>VERISURE</t>
+  </si>
+  <si>
+    <t>R$  250,33</t>
+  </si>
+  <si>
+    <t>Verisure - Alarme 2026</t>
+  </si>
+  <si>
     <t>Jackson Fernando de Araujo</t>
   </si>
   <si>
@@ -2850,15 +2859,6 @@
   </si>
   <si>
     <t>Segurança 2026</t>
-  </si>
-  <si>
-    <t>VERISURE</t>
-  </si>
-  <si>
-    <t>R$  250,33</t>
-  </si>
-  <si>
-    <t>Verisure - Alarme 2026</t>
   </si>
   <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
@@ -6025,13 +6025,13 @@
         <v>193</v>
       </c>
       <c r="J61" t="s">
-        <v>83</v>
+        <v>194</v>
       </c>
       <c r="K61" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="L61" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M61" t="s">
         <v>183</v>
@@ -6066,7 +6066,7 @@
         <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F62" t="s">
         <v>64</v>
@@ -6075,16 +6075,16 @@
         <v>41</v>
       </c>
       <c r="H62" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I62" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J62" t="s">
-        <v>198</v>
+        <v>83</v>
       </c>
       <c r="K62" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="L62" t="s">
         <v>199</v>
@@ -6099,7 +6099,7 @@
         <v>48</v>
       </c>
       <c r="P62" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q62" t="s">
         <v>47</v>
@@ -6131,7 +6131,7 @@
         <v>41</v>
       </c>
       <c r="H63" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I63" t="s">
         <v>201</v>
@@ -6305,7 +6305,7 @@
         <v>210</v>
       </c>
       <c r="J66" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K66" t="s">
         <v>159</v>
@@ -17499,7 +17499,7 @@
         <v>41</v>
       </c>
       <c r="H266" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I266" t="s">
         <v>550</v>
@@ -17555,7 +17555,7 @@
         <v>41</v>
       </c>
       <c r="H267" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I267" t="s">
         <v>494</v>
@@ -17611,7 +17611,7 @@
         <v>41</v>
       </c>
       <c r="H268" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I268" t="s">
         <v>489</v>
@@ -17667,7 +17667,7 @@
         <v>41</v>
       </c>
       <c r="H269" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I269" t="s">
         <v>568</v>
@@ -18283,7 +18283,7 @@
         <v>41</v>
       </c>
       <c r="H280" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I280" t="s">
         <v>581</v>
@@ -18563,7 +18563,7 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I285" t="s">
         <v>588</v>
@@ -18619,7 +18619,7 @@
         <v>41</v>
       </c>
       <c r="H286" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I286" t="s">
         <v>589</v>
@@ -18675,7 +18675,7 @@
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I287" t="s">
         <v>590</v>
@@ -18731,7 +18731,7 @@
         <v>41</v>
       </c>
       <c r="H288" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I288" t="s">
         <v>591</v>
@@ -19403,7 +19403,7 @@
         <v>41</v>
       </c>
       <c r="H300" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I300" t="s">
         <v>612</v>
@@ -21970,7 +21970,7 @@
         <v>33</v>
       </c>
       <c r="E346" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="F346" t="s">
         <v>40</v>
@@ -21985,10 +21985,10 @@
         <v>92</v>
       </c>
       <c r="J346" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="K346" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="L346" t="s">
         <v>34</v>
@@ -22000,7 +22000,7 @@
         <v>47</v>
       </c>
       <c r="O346" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="P346" t="s">
         <v>92</v>
@@ -22026,7 +22026,7 @@
         <v>34</v>
       </c>
       <c r="E347" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="F347" t="s">
         <v>40</v>
@@ -22056,7 +22056,7 @@
         <v>47</v>
       </c>
       <c r="O347" t="s">
-        <v>115</v>
+        <v>294</v>
       </c>
       <c r="P347" t="s">
         <v>92</v>
@@ -22138,10 +22138,10 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>531</v>
+        <v>250</v>
       </c>
       <c r="F349" t="s">
-        <v>709</v>
+        <v>40</v>
       </c>
       <c r="G349" t="s">
         <v>41</v>
@@ -22153,10 +22153,10 @@
         <v>92</v>
       </c>
       <c r="J349" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="K349" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="L349" t="s">
         <v>34</v>
@@ -22168,13 +22168,13 @@
         <v>47</v>
       </c>
       <c r="O349" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="P349" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="Q349" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R349" t="s">
         <v>34</v>
@@ -22194,7 +22194,7 @@
         <v>34</v>
       </c>
       <c r="E350" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="F350" t="s">
         <v>40</v>
@@ -22209,10 +22209,10 @@
         <v>92</v>
       </c>
       <c r="J350" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K350" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L350" t="s">
         <v>34</v>
@@ -22224,7 +22224,7 @@
         <v>47</v>
       </c>
       <c r="O350" t="s">
-        <v>294</v>
+        <v>169</v>
       </c>
       <c r="P350" t="s">
         <v>92</v>
@@ -22250,7 +22250,7 @@
         <v>34</v>
       </c>
       <c r="E351" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F351" t="s">
         <v>40</v>
@@ -22265,10 +22265,10 @@
         <v>92</v>
       </c>
       <c r="J351" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="K351" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L351" t="s">
         <v>34</v>
@@ -22280,7 +22280,7 @@
         <v>47</v>
       </c>
       <c r="O351" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="P351" t="s">
         <v>92</v>
@@ -22306,7 +22306,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="F352" t="s">
         <v>40</v>
@@ -22321,10 +22321,10 @@
         <v>92</v>
       </c>
       <c r="J352" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="K352" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L352" t="s">
         <v>34</v>
@@ -22336,7 +22336,7 @@
         <v>47</v>
       </c>
       <c r="O352" t="s">
-        <v>269</v>
+        <v>88</v>
       </c>
       <c r="P352" t="s">
         <v>92</v>
@@ -22418,7 +22418,7 @@
         <v>34</v>
       </c>
       <c r="E354" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="F354" t="s">
         <v>40</v>
@@ -22433,10 +22433,10 @@
         <v>92</v>
       </c>
       <c r="J354" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K354" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L354" t="s">
         <v>34</v>
@@ -22448,7 +22448,7 @@
         <v>47</v>
       </c>
       <c r="O354" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="P354" t="s">
         <v>92</v>
@@ -22474,10 +22474,10 @@
         <v>34</v>
       </c>
       <c r="E355" t="s">
-        <v>272</v>
+        <v>531</v>
       </c>
       <c r="F355" t="s">
-        <v>40</v>
+        <v>709</v>
       </c>
       <c r="G355" t="s">
         <v>41</v>
@@ -22489,10 +22489,10 @@
         <v>92</v>
       </c>
       <c r="J355" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="K355" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="L355" t="s">
         <v>34</v>
@@ -22504,13 +22504,13 @@
         <v>47</v>
       </c>
       <c r="O355" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="P355" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="Q355" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R355" t="s">
         <v>34</v>
@@ -22530,7 +22530,7 @@
         <v>34</v>
       </c>
       <c r="E356" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F356" t="s">
         <v>40</v>
@@ -22545,10 +22545,10 @@
         <v>92</v>
       </c>
       <c r="J356" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="K356" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L356" t="s">
         <v>34</v>
@@ -22560,7 +22560,7 @@
         <v>47</v>
       </c>
       <c r="O356" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="P356" t="s">
         <v>92</v>
@@ -22642,7 +22642,7 @@
         <v>34</v>
       </c>
       <c r="E358" t="s">
-        <v>487</v>
+        <v>260</v>
       </c>
       <c r="F358" t="s">
         <v>40</v>
@@ -22657,10 +22657,10 @@
         <v>92</v>
       </c>
       <c r="J358" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K358" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="L358" t="s">
         <v>34</v>
@@ -22672,7 +22672,7 @@
         <v>47</v>
       </c>
       <c r="O358" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="P358" t="s">
         <v>92</v>
@@ -22698,7 +22698,7 @@
         <v>34</v>
       </c>
       <c r="E359" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="F359" t="s">
         <v>40</v>
@@ -22713,10 +22713,10 @@
         <v>92</v>
       </c>
       <c r="J359" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="K359" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L359" t="s">
         <v>34</v>
@@ -22728,7 +22728,7 @@
         <v>47</v>
       </c>
       <c r="O359" t="s">
-        <v>98</v>
+        <v>269</v>
       </c>
       <c r="P359" t="s">
         <v>92</v>
@@ -22754,7 +22754,7 @@
         <v>34</v>
       </c>
       <c r="E360" t="s">
-        <v>260</v>
+        <v>487</v>
       </c>
       <c r="F360" t="s">
         <v>40</v>
@@ -22769,10 +22769,10 @@
         <v>92</v>
       </c>
       <c r="J360" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K360" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="L360" t="s">
         <v>34</v>
@@ -22784,7 +22784,7 @@
         <v>47</v>
       </c>
       <c r="O360" t="s">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="P360" t="s">
         <v>92</v>
@@ -22922,7 +22922,7 @@
         <v>33</v>
       </c>
       <c r="E363" t="s">
-        <v>227</v>
+        <v>720</v>
       </c>
       <c r="F363" t="s">
         <v>40</v>
@@ -22931,16 +22931,16 @@
         <v>41</v>
       </c>
       <c r="H363" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I363" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J363" t="s">
-        <v>722</v>
+        <v>329</v>
       </c>
       <c r="K363" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="L363" t="s">
         <v>723</v>
@@ -22955,7 +22955,7 @@
         <v>48</v>
       </c>
       <c r="P363" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="Q363" t="s">
         <v>47</v>
@@ -22978,7 +22978,7 @@
         <v>34</v>
       </c>
       <c r="E364" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F364" t="s">
         <v>40</v>
@@ -22987,19 +22987,19 @@
         <v>41</v>
       </c>
       <c r="H364" t="s">
+        <v>724</v>
+      </c>
+      <c r="I364" t="s">
         <v>725</v>
       </c>
-      <c r="I364" t="s">
+      <c r="J364" t="s">
         <v>726</v>
       </c>
-      <c r="J364" t="s">
+      <c r="K364" t="s">
         <v>727</v>
       </c>
-      <c r="K364" t="s">
+      <c r="L364" t="s">
         <v>728</v>
-      </c>
-      <c r="L364" t="s">
-        <v>729</v>
       </c>
       <c r="M364" t="s">
         <v>718</v>
@@ -23011,7 +23011,7 @@
         <v>48</v>
       </c>
       <c r="P364" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="Q364" t="s">
         <v>47</v>
@@ -23034,7 +23034,7 @@
         <v>34</v>
       </c>
       <c r="E365" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="F365" t="s">
         <v>40</v>
@@ -23049,13 +23049,13 @@
         <v>731</v>
       </c>
       <c r="J365" t="s">
-        <v>329</v>
+        <v>230</v>
       </c>
       <c r="K365" t="s">
-        <v>45</v>
+        <v>732</v>
       </c>
       <c r="L365" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M365" t="s">
         <v>718</v>
@@ -23090,7 +23090,7 @@
         <v>34</v>
       </c>
       <c r="E366" t="s">
-        <v>733</v>
+        <v>227</v>
       </c>
       <c r="F366" t="s">
         <v>40</v>
@@ -23105,10 +23105,10 @@
         <v>735</v>
       </c>
       <c r="J366" t="s">
-        <v>230</v>
+        <v>736</v>
       </c>
       <c r="K366" t="s">
-        <v>736</v>
+        <v>67</v>
       </c>
       <c r="L366" t="s">
         <v>737</v>
@@ -23370,7 +23370,7 @@
         <v>33</v>
       </c>
       <c r="E371" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F371" t="s">
         <v>40</v>
@@ -23385,7 +23385,7 @@
         <v>750</v>
       </c>
       <c r="J371" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K371" t="s">
         <v>45</v>
@@ -23538,7 +23538,7 @@
         <v>33</v>
       </c>
       <c r="E374" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F374" t="s">
         <v>40</v>
@@ -23594,7 +23594,7 @@
         <v>34</v>
       </c>
       <c r="E375" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F375" t="s">
         <v>40</v>
@@ -23609,7 +23609,7 @@
         <v>750</v>
       </c>
       <c r="J375" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K375" t="s">
         <v>45</v>
@@ -23650,7 +23650,7 @@
         <v>34</v>
       </c>
       <c r="E376" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F376" t="s">
         <v>40</v>
@@ -23665,7 +23665,7 @@
         <v>763</v>
       </c>
       <c r="J376" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K376" t="s">
         <v>45</v>
@@ -23762,7 +23762,7 @@
         <v>34</v>
       </c>
       <c r="E378" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F378" t="s">
         <v>40</v>
@@ -23777,7 +23777,7 @@
         <v>770</v>
       </c>
       <c r="J378" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K378" t="s">
         <v>45</v>
@@ -23818,7 +23818,7 @@
         <v>34</v>
       </c>
       <c r="E379" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F379" t="s">
         <v>40</v>
@@ -23833,7 +23833,7 @@
         <v>773</v>
       </c>
       <c r="J379" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K379" t="s">
         <v>45</v>
@@ -23930,7 +23930,7 @@
         <v>34</v>
       </c>
       <c r="E381" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F381" t="s">
         <v>40</v>
@@ -23945,7 +23945,7 @@
         <v>778</v>
       </c>
       <c r="J381" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K381" t="s">
         <v>45</v>
@@ -24042,7 +24042,7 @@
         <v>34</v>
       </c>
       <c r="E383" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F383" t="s">
         <v>40</v>
@@ -24057,7 +24057,7 @@
         <v>783</v>
       </c>
       <c r="J383" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K383" t="s">
         <v>45</v>
@@ -24098,7 +24098,7 @@
         <v>34</v>
       </c>
       <c r="E384" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="F384" t="s">
         <v>40</v>
@@ -24611,7 +24611,7 @@
         <v>41</v>
       </c>
       <c r="H393" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I393" t="s">
         <v>805</v>
@@ -24841,7 +24841,7 @@
         <v>814</v>
       </c>
       <c r="J397" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
       <c r="K397" t="s">
         <v>68</v>
@@ -25009,10 +25009,10 @@
         <v>823</v>
       </c>
       <c r="J400" t="s">
+        <v>726</v>
+      </c>
+      <c r="K400" t="s">
         <v>727</v>
-      </c>
-      <c r="K400" t="s">
-        <v>728</v>
       </c>
       <c r="L400" t="s">
         <v>824</v>
@@ -25274,7 +25274,7 @@
         <v>33</v>
       </c>
       <c r="E405" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F405" t="s">
         <v>40</v>
@@ -25289,7 +25289,7 @@
         <v>843</v>
       </c>
       <c r="J405" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K405" t="s">
         <v>45</v>
@@ -25442,7 +25442,7 @@
         <v>33</v>
       </c>
       <c r="E408" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F408" t="s">
         <v>40</v>
@@ -25457,7 +25457,7 @@
         <v>855</v>
       </c>
       <c r="J408" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K408" t="s">
         <v>320</v>
@@ -25569,10 +25569,10 @@
         <v>861</v>
       </c>
       <c r="J410" t="s">
+        <v>726</v>
+      </c>
+      <c r="K410" t="s">
         <v>727</v>
-      </c>
-      <c r="K410" t="s">
-        <v>728</v>
       </c>
       <c r="L410" t="s">
         <v>862</v>
@@ -25684,10 +25684,10 @@
         <v>179</v>
       </c>
       <c r="K412" t="s">
-        <v>664</v>
+        <v>293</v>
       </c>
       <c r="L412" t="s">
-        <v>869</v>
+        <v>34</v>
       </c>
       <c r="M412" t="s">
         <v>865</v>
@@ -25722,7 +25722,7 @@
         <v>34</v>
       </c>
       <c r="E413" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F413" t="s">
         <v>208</v>
@@ -25731,16 +25731,16 @@
         <v>41</v>
       </c>
       <c r="H413" t="s">
+        <v>870</v>
+      </c>
+      <c r="I413" t="s">
         <v>871</v>
-      </c>
-      <c r="I413" t="s">
-        <v>872</v>
       </c>
       <c r="J413" t="s">
         <v>179</v>
       </c>
       <c r="K413" t="s">
-        <v>293</v>
+        <v>109</v>
       </c>
       <c r="L413" t="s">
         <v>34</v>
@@ -25755,7 +25755,7 @@
         <v>48</v>
       </c>
       <c r="P413" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="Q413" t="s">
         <v>47</v>
@@ -25778,7 +25778,7 @@
         <v>34</v>
       </c>
       <c r="E414" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F414" t="s">
         <v>208</v>
@@ -25787,19 +25787,19 @@
         <v>41</v>
       </c>
       <c r="H414" t="s">
+        <v>873</v>
+      </c>
+      <c r="I414" t="s">
         <v>874</v>
-      </c>
-      <c r="I414" t="s">
-        <v>875</v>
       </c>
       <c r="J414" t="s">
         <v>179</v>
       </c>
       <c r="K414" t="s">
-        <v>109</v>
+        <v>664</v>
       </c>
       <c r="L414" t="s">
-        <v>34</v>
+        <v>875</v>
       </c>
       <c r="M414" t="s">
         <v>865</v>
@@ -25811,7 +25811,7 @@
         <v>48</v>
       </c>
       <c r="P414" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="Q414" t="s">
         <v>47</v>
@@ -26002,7 +26002,7 @@
         <v>33</v>
       </c>
       <c r="E418" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F418" t="s">
         <v>40</v>
@@ -26017,7 +26017,7 @@
         <v>888</v>
       </c>
       <c r="J418" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K418" t="s">
         <v>45</v>
@@ -26229,25 +26229,25 @@
         <v>903</v>
       </c>
       <c r="F422" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G422" t="s">
         <v>41</v>
       </c>
       <c r="H422" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="I422" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="J422" t="s">
-        <v>325</v>
+        <v>179</v>
       </c>
       <c r="K422" t="s">
-        <v>45</v>
+        <v>293</v>
       </c>
       <c r="L422" t="s">
-        <v>905</v>
+        <v>34</v>
       </c>
       <c r="M422" t="s">
         <v>902</v>
@@ -26259,7 +26259,7 @@
         <v>48</v>
       </c>
       <c r="P422" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="Q422" t="s">
         <v>47</v>
@@ -26282,7 +26282,7 @@
         <v>34</v>
       </c>
       <c r="E423" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F423" t="s">
         <v>40</v>
@@ -26291,19 +26291,19 @@
         <v>41</v>
       </c>
       <c r="H423" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="I423" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="J423" t="s">
         <v>329</v>
       </c>
       <c r="K423" t="s">
-        <v>674</v>
+        <v>45</v>
       </c>
       <c r="L423" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="M423" t="s">
         <v>902</v>
@@ -26315,7 +26315,7 @@
         <v>48</v>
       </c>
       <c r="P423" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="Q423" t="s">
         <v>47</v>
@@ -26338,28 +26338,28 @@
         <v>34</v>
       </c>
       <c r="E424" t="s">
-        <v>908</v>
+        <v>720</v>
       </c>
       <c r="F424" t="s">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="G424" t="s">
         <v>41</v>
       </c>
       <c r="H424" t="s">
+        <v>898</v>
+      </c>
+      <c r="I424" t="s">
         <v>909</v>
       </c>
-      <c r="I424" t="s">
+      <c r="J424" t="s">
+        <v>329</v>
+      </c>
+      <c r="K424" t="s">
+        <v>674</v>
+      </c>
+      <c r="L424" t="s">
         <v>910</v>
-      </c>
-      <c r="J424" t="s">
-        <v>179</v>
-      </c>
-      <c r="K424" t="s">
-        <v>293</v>
-      </c>
-      <c r="L424" t="s">
-        <v>34</v>
       </c>
       <c r="M424" t="s">
         <v>902</v>
@@ -26371,7 +26371,7 @@
         <v>48</v>
       </c>
       <c r="P424" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="Q424" t="s">
         <v>47</v>
@@ -26394,7 +26394,7 @@
         <v>34</v>
       </c>
       <c r="E425" t="s">
-        <v>724</v>
+        <v>911</v>
       </c>
       <c r="F425" t="s">
         <v>40</v>
@@ -26403,13 +26403,13 @@
         <v>41</v>
       </c>
       <c r="H425" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
       <c r="I425" t="s">
         <v>912</v>
       </c>
       <c r="J425" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="K425" t="s">
         <v>45</v>
@@ -26618,7 +26618,7 @@
         <v>33</v>
       </c>
       <c r="E429" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F429" t="s">
         <v>40</v>
@@ -26633,7 +26633,7 @@
         <v>925</v>
       </c>
       <c r="J429" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K429" t="s">
         <v>45</v>
@@ -26786,7 +26786,7 @@
         <v>33</v>
       </c>
       <c r="E432" t="s">
-        <v>724</v>
+        <v>821</v>
       </c>
       <c r="F432" t="s">
         <v>40</v>
@@ -26801,10 +26801,10 @@
         <v>937</v>
       </c>
       <c r="J432" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="K432" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="L432" t="s">
         <v>938</v>
@@ -26842,7 +26842,7 @@
         <v>34</v>
       </c>
       <c r="E433" t="s">
-        <v>821</v>
+        <v>720</v>
       </c>
       <c r="F433" t="s">
         <v>40</v>
@@ -26857,10 +26857,10 @@
         <v>940</v>
       </c>
       <c r="J433" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="K433" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="L433" t="s">
         <v>941</v>
@@ -27066,7 +27066,7 @@
         <v>33</v>
       </c>
       <c r="E437" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="F437" t="s">
         <v>40</v>

--- a/xlsx/dre/DRE_03_2026.xlsx
+++ b/xlsx/dre/DRE_03_2026.xlsx
@@ -588,21 +588,6 @@
     <t>R$  4.689,29</t>
   </si>
   <si>
-    <t>12/1</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  736,71</t>
-  </si>
-  <si>
-    <t>23/04/26</t>
-  </si>
-  <si>
-    <t>Digisac</t>
-  </si>
-  <si>
     <t>5/1</t>
   </si>
   <si>
@@ -616,6 +601,21 @@
 </t>
   </si>
   <si>
+    <t>12/1</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  736,71</t>
+  </si>
+  <si>
+    <t>23/04/26</t>
+  </si>
+  <si>
+    <t>Digisac</t>
+  </si>
+  <si>
     <t>9/1</t>
   </si>
   <si>
@@ -983,30 +983,6 @@
   </si>
   <si>
     <t>R$ 7.970,23</t>
-  </si>
-  <si>
-    <t>2/2</t>
-  </si>
-  <si>
-    <t>R$  106,63</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Mercado livre - mat aspirador</t>
-  </si>
-  <si>
-    <t>9/3</t>
-  </si>
-  <si>
-    <t>R$  91,87</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>Grapa</t>
   </si>
   <si>
     <t>Denny Lucas do Carmo Ferreira</t>
@@ -1148,6 +1124,30 @@
 </t>
   </si>
   <si>
+    <t>9/3</t>
+  </si>
+  <si>
+    <t>R$  91,87</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>Grapa</t>
+  </si>
+  <si>
+    <t>2/2</t>
+  </si>
+  <si>
+    <t>R$  106,63</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Mercado livre - mat aspirador</t>
+  </si>
+  <si>
     <t>561/1</t>
   </si>
   <si>
@@ -1172,15 +1172,87 @@
     <t>4.02.02.01.01 Fretes sobre compra de mercadorias da marca - provisão</t>
   </si>
   <si>
+    <t>ENTREGADORA NOVO RUMO LTDA ME</t>
+  </si>
+  <si>
+    <t>R$  141,50</t>
+  </si>
+  <si>
+    <t>68501AMILTONF</t>
+  </si>
+  <si>
+    <t>63301n/0</t>
+  </si>
+  <si>
+    <t>R$  243,97</t>
+  </si>
+  <si>
+    <t>RODAG TRANSPORTES LTDA*</t>
+  </si>
+  <si>
+    <t>R$  11,98</t>
+  </si>
+  <si>
+    <t>R$  11,18</t>
+  </si>
+  <si>
+    <t>66301-/0</t>
+  </si>
+  <si>
+    <t>R$  101,41</t>
+  </si>
+  <si>
+    <t>67501-/0</t>
+  </si>
+  <si>
+    <t>R$  95,00</t>
+  </si>
+  <si>
+    <t>70601-/0</t>
+  </si>
+  <si>
+    <t>66301n/0</t>
+  </si>
+  <si>
+    <t>64801n/0</t>
+  </si>
+  <si>
+    <t>R$  190,00</t>
+  </si>
+  <si>
+    <t>R$  50,00</t>
+  </si>
+  <si>
+    <t>R$  98,75</t>
+  </si>
+  <si>
+    <t>64801R/0</t>
+  </si>
+  <si>
+    <t>R$  12,95</t>
+  </si>
+  <si>
+    <t>64801N/0</t>
+  </si>
+  <si>
+    <t>R$  12,09</t>
+  </si>
+  <si>
+    <t>63701/0</t>
+  </si>
+  <si>
+    <t>R$  14,09</t>
+  </si>
+  <si>
+    <t>R$  15,09</t>
+  </si>
+  <si>
     <t>67301/2</t>
   </si>
   <si>
     <t>PCP</t>
   </si>
   <si>
-    <t>ENTREGADORA NOVO RUMO LTDA ME</t>
-  </si>
-  <si>
     <t>R$  758,85</t>
   </si>
   <si>
@@ -1190,9 +1262,6 @@
     <t>67301/3</t>
   </si>
   <si>
-    <t>RODAG TRANSPORTES LTDA*</t>
-  </si>
-  <si>
     <t>R$  773,11</t>
   </si>
   <si>
@@ -1259,9 +1328,6 @@
     <t>R$  1.680,23</t>
   </si>
   <si>
-    <t>68501AMILTONF</t>
-  </si>
-  <si>
     <t>66301/2</t>
   </si>
   <si>
@@ -1358,9 +1424,6 @@
     <t>R$  264,04</t>
   </si>
   <si>
-    <t>67501-/0</t>
-  </si>
-  <si>
     <t>R$  136,00</t>
   </si>
   <si>
@@ -1373,9 +1436,6 @@
     <t>R$  33,33</t>
   </si>
   <si>
-    <t>R$  50,00</t>
-  </si>
-  <si>
     <t>R$  30,00</t>
   </si>
   <si>
@@ -1391,66 +1451,6 @@
     <t>R$  11,45</t>
   </si>
   <si>
-    <t>R$  141,50</t>
-  </si>
-  <si>
-    <t>63301n/0</t>
-  </si>
-  <si>
-    <t>R$  243,97</t>
-  </si>
-  <si>
-    <t>R$  11,98</t>
-  </si>
-  <si>
-    <t>R$  11,18</t>
-  </si>
-  <si>
-    <t>66301-/0</t>
-  </si>
-  <si>
-    <t>R$  101,41</t>
-  </si>
-  <si>
-    <t>R$  95,00</t>
-  </si>
-  <si>
-    <t>70601-/0</t>
-  </si>
-  <si>
-    <t>66301n/0</t>
-  </si>
-  <si>
-    <t>64801n/0</t>
-  </si>
-  <si>
-    <t>R$  190,00</t>
-  </si>
-  <si>
-    <t>R$  98,75</t>
-  </si>
-  <si>
-    <t>64801R/0</t>
-  </si>
-  <si>
-    <t>R$  12,95</t>
-  </si>
-  <si>
-    <t>64801N/0</t>
-  </si>
-  <si>
-    <t>R$  12,09</t>
-  </si>
-  <si>
-    <t>63701/0</t>
-  </si>
-  <si>
-    <t>R$  14,09</t>
-  </si>
-  <si>
-    <t>R$  15,09</t>
-  </si>
-  <si>
     <t>4.03 DESPESAS DE VENDAS</t>
   </si>
   <si>
@@ -1718,6 +1718,57 @@
     <t>R$ 6.206,47</t>
   </si>
   <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>05/05/26</t>
+  </si>
+  <si>
+    <t>R$  1.035,56</t>
+  </si>
+  <si>
+    <t>01/06/26</t>
+  </si>
+  <si>
+    <t>David Alves</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>01/07/26</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>R$  188,04</t>
+  </si>
+  <si>
+    <t>05/08/26</t>
+  </si>
+  <si>
+    <t>R$  304,96</t>
+  </si>
+  <si>
+    <t>19203/1</t>
+  </si>
+  <si>
+    <t>R$  558,00</t>
+  </si>
+  <si>
+    <t>19203RobertoTK</t>
+  </si>
+  <si>
+    <t>R$  442,63</t>
+  </si>
+  <si>
+    <t>71601/2</t>
+  </si>
+  <si>
+    <t>R$  44,10</t>
+  </si>
+  <si>
     <t>69801/2</t>
   </si>
   <si>
@@ -1728,57 +1779,6 @@
   </si>
   <si>
     <t>R$  2,40</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>05/08/26</t>
-  </si>
-  <si>
-    <t>R$  188,04</t>
-  </si>
-  <si>
-    <t>01/07/26</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>David Alves</t>
-  </si>
-  <si>
-    <t>01/06/26</t>
-  </si>
-  <si>
-    <t>R$  1.035,56</t>
-  </si>
-  <si>
-    <t>05/05/26</t>
-  </si>
-  <si>
-    <t>R$  304,96</t>
-  </si>
-  <si>
-    <t>71601/2</t>
-  </si>
-  <si>
-    <t>R$  44,10</t>
-  </si>
-  <si>
-    <t>19203/1</t>
-  </si>
-  <si>
-    <t>R$  558,00</t>
-  </si>
-  <si>
-    <t>19203RobertoTK</t>
-  </si>
-  <si>
-    <t>R$  442,63</t>
   </si>
   <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
@@ -2190,9 +2190,36 @@
     <t>R$ 9.161,99</t>
   </si>
   <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.588,50</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
     <t>12/3</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>01/03/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
@@ -2202,21 +2229,6 @@
     <t>Google 2026</t>
   </si>
   <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>01/03/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
     <t>1/1</t>
   </si>
   <si>
@@ -2232,18 +2244,6 @@
     <t>Facebook 2026</t>
   </si>
   <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.588,50</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
     <t>4.03.03.09.06 Marketing - outros gastos (CV)</t>
   </si>
   <si>
@@ -2301,6 +2301,39 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>603/1</t>
+  </si>
+  <si>
+    <t>R$  2.219,99</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  1.900,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>R$  2.071,98</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
     <t>Leandro Henrique Simoes Campos</t>
   </si>
   <si>
@@ -2310,10 +2343,37 @@
     <t>Leandro Henrique Simoes Campos Fixo 2026</t>
   </si>
   <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.020,07</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  7.800,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.405,07</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
     <t>CARINA PEREIRA</t>
@@ -2331,69 +2391,9 @@
     <t>R$  2.071,82</t>
   </si>
   <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
     <t>Salário Fixo -Eric Serpa 2026</t>
   </si>
   <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.020,07</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.405,07</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  2.071,98</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  1.900,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  7.800,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>R$  2.219,99</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>603/1</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -2628,6 +2628,18 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
+    <t>595/1</t>
+  </si>
+  <si>
+    <t>Oxxo</t>
+  </si>
+  <si>
+    <t>R$  110,94</t>
+  </si>
+  <si>
+    <t>Cafés loja</t>
+  </si>
+  <si>
     <t>593/1</t>
   </si>
   <si>
@@ -2644,18 +2656,6 @@
   </si>
   <si>
     <t>R$  19,98</t>
-  </si>
-  <si>
-    <t>595/1</t>
-  </si>
-  <si>
-    <t>Oxxo</t>
-  </si>
-  <si>
-    <t>R$  110,94</t>
-  </si>
-  <si>
-    <t>Cafés loja</t>
   </si>
   <si>
     <t>569/1</t>
@@ -2744,6 +2744,21 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>3/2</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>592/1</t>
   </si>
   <si>
@@ -2762,21 +2777,6 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>3/2</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
-  </si>
-  <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
   </si>
   <si>
@@ -2843,6 +2843,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
+    <t>R$  150,00</t>
+  </si>
+  <si>
+    <t>Segurança 2026</t>
+  </si>
+  <si>
     <t>VERISURE</t>
   </si>
   <si>
@@ -2852,15 +2861,6 @@
     <t>Verisure - Alarme 2026</t>
   </si>
   <si>
-    <t>Jackson Fernando de Araujo</t>
-  </si>
-  <si>
-    <t>R$  150,00</t>
-  </si>
-  <si>
-    <t>Segurança 2026</t>
-  </si>
-  <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
   </si>
   <si>
@@ -2945,6 +2945,9 @@
     <t>Título referente a Valor da Taxa Financeira</t>
   </si>
   <si>
+    <t>R$  2.789,71</t>
+  </si>
+  <si>
     <t>R$  1.165,41</t>
   </si>
   <si>
@@ -2964,9 +2967,6 @@
   </si>
   <si>
     <t>R$  501,61</t>
-  </si>
-  <si>
-    <t>R$  2.789,71</t>
   </si>
   <si>
     <t>R$  1.206,97</t>
@@ -6025,13 +6025,13 @@
         <v>193</v>
       </c>
       <c r="J61" t="s">
+        <v>83</v>
+      </c>
+      <c r="K61" t="s">
+        <v>67</v>
+      </c>
+      <c r="L61" t="s">
         <v>194</v>
-      </c>
-      <c r="K61" t="s">
-        <v>133</v>
-      </c>
-      <c r="L61" t="s">
-        <v>195</v>
       </c>
       <c r="M61" t="s">
         <v>183</v>
@@ -6066,7 +6066,7 @@
         <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F62" t="s">
         <v>64</v>
@@ -6075,16 +6075,16 @@
         <v>41</v>
       </c>
       <c r="H62" t="s">
+        <v>196</v>
+      </c>
+      <c r="I62" t="s">
         <v>197</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>198</v>
       </c>
-      <c r="J62" t="s">
-        <v>83</v>
-      </c>
       <c r="K62" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="L62" t="s">
         <v>199</v>
@@ -6099,7 +6099,7 @@
         <v>48</v>
       </c>
       <c r="P62" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q62" t="s">
         <v>47</v>
@@ -6131,7 +6131,7 @@
         <v>41</v>
       </c>
       <c r="H63" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I63" t="s">
         <v>201</v>
@@ -6305,7 +6305,7 @@
         <v>210</v>
       </c>
       <c r="J66" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K66" t="s">
         <v>159</v>
@@ -8754,28 +8754,28 @@
         <v>33</v>
       </c>
       <c r="E110" t="s">
+        <v>263</v>
+      </c>
+      <c r="F110" t="s">
+        <v>208</v>
+      </c>
+      <c r="G110" t="s">
+        <v>41</v>
+      </c>
+      <c r="H110" t="s">
         <v>323</v>
-      </c>
-      <c r="F110" t="s">
-        <v>40</v>
-      </c>
-      <c r="G110" t="s">
-        <v>41</v>
-      </c>
-      <c r="H110" t="s">
-        <v>52</v>
       </c>
       <c r="I110" t="s">
         <v>324</v>
       </c>
       <c r="J110" t="s">
-        <v>325</v>
+        <v>119</v>
       </c>
       <c r="K110" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="L110" t="s">
-        <v>326</v>
+        <v>34</v>
       </c>
       <c r="M110" t="s">
         <v>321</v>
@@ -8784,7 +8784,7 @@
         <v>47</v>
       </c>
       <c r="O110" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="P110" t="s">
         <v>324</v>
@@ -8810,28 +8810,28 @@
         <v>34</v>
       </c>
       <c r="E111" t="s">
-        <v>327</v>
+        <v>250</v>
       </c>
       <c r="F111" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G111" t="s">
         <v>41</v>
       </c>
       <c r="H111" t="s">
-        <v>52</v>
+        <v>325</v>
       </c>
       <c r="I111" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J111" t="s">
-        <v>329</v>
+        <v>105</v>
       </c>
       <c r="K111" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="L111" t="s">
-        <v>330</v>
+        <v>34</v>
       </c>
       <c r="M111" t="s">
         <v>321</v>
@@ -8840,10 +8840,10 @@
         <v>47</v>
       </c>
       <c r="O111" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="P111" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Q111" t="s">
         <v>47</v>
@@ -8866,7 +8866,7 @@
         <v>34</v>
       </c>
       <c r="E112" t="s">
-        <v>263</v>
+        <v>327</v>
       </c>
       <c r="F112" t="s">
         <v>208</v>
@@ -8875,19 +8875,19 @@
         <v>41</v>
       </c>
       <c r="H112" t="s">
-        <v>331</v>
+        <v>52</v>
       </c>
       <c r="I112" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="J112" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="K112" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="L112" t="s">
-        <v>34</v>
+        <v>329</v>
       </c>
       <c r="M112" t="s">
         <v>321</v>
@@ -8896,10 +8896,10 @@
         <v>47</v>
       </c>
       <c r="O112" t="s">
-        <v>149</v>
+        <v>330</v>
       </c>
       <c r="P112" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="Q112" t="s">
         <v>47</v>
@@ -8922,7 +8922,7 @@
         <v>34</v>
       </c>
       <c r="E113" t="s">
-        <v>250</v>
+        <v>331</v>
       </c>
       <c r="F113" t="s">
         <v>208</v>
@@ -8931,19 +8931,19 @@
         <v>41</v>
       </c>
       <c r="H113" t="s">
-        <v>333</v>
+        <v>52</v>
       </c>
       <c r="I113" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="J113" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="K113" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L113" t="s">
-        <v>34</v>
+        <v>332</v>
       </c>
       <c r="M113" t="s">
         <v>321</v>
@@ -8952,10 +8952,10 @@
         <v>47</v>
       </c>
       <c r="O113" t="s">
-        <v>112</v>
+        <v>330</v>
       </c>
       <c r="P113" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="Q113" t="s">
         <v>47</v>
@@ -8978,7 +8978,7 @@
         <v>34</v>
       </c>
       <c r="E114" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F114" t="s">
         <v>208</v>
@@ -8990,7 +8990,7 @@
         <v>52</v>
       </c>
       <c r="I114" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="J114" t="s">
         <v>67</v>
@@ -8999,7 +8999,7 @@
         <v>67</v>
       </c>
       <c r="L114" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="M114" t="s">
         <v>321</v>
@@ -9008,10 +9008,10 @@
         <v>47</v>
       </c>
       <c r="O114" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="P114" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="Q114" t="s">
         <v>47</v>
@@ -9034,7 +9034,7 @@
         <v>34</v>
       </c>
       <c r="E115" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F115" t="s">
         <v>208</v>
@@ -9043,19 +9043,19 @@
         <v>41</v>
       </c>
       <c r="H115" t="s">
-        <v>52</v>
+        <v>336</v>
       </c>
       <c r="I115" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J115" t="s">
-        <v>67</v>
+        <v>338</v>
       </c>
       <c r="K115" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="L115" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M115" t="s">
         <v>321</v>
@@ -9064,10 +9064,10 @@
         <v>47</v>
       </c>
       <c r="O115" t="s">
-        <v>338</v>
+        <v>48</v>
       </c>
       <c r="P115" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q115" t="s">
         <v>47</v>
@@ -9090,7 +9090,7 @@
         <v>34</v>
       </c>
       <c r="E116" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F116" t="s">
         <v>208</v>
@@ -9102,13 +9102,13 @@
         <v>52</v>
       </c>
       <c r="I116" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J116" t="s">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="K116" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="L116" t="s">
         <v>342</v>
@@ -9120,10 +9120,10 @@
         <v>47</v>
       </c>
       <c r="O116" t="s">
-        <v>338</v>
+        <v>48</v>
       </c>
       <c r="P116" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q116" t="s">
         <v>47</v>
@@ -9155,19 +9155,19 @@
         <v>41</v>
       </c>
       <c r="H117" t="s">
+        <v>52</v>
+      </c>
+      <c r="I117" t="s">
         <v>344</v>
       </c>
-      <c r="I117" t="s">
-        <v>345</v>
-      </c>
       <c r="J117" t="s">
-        <v>346</v>
+        <v>179</v>
       </c>
       <c r="K117" t="s">
         <v>105</v>
       </c>
       <c r="L117" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M117" t="s">
         <v>321</v>
@@ -9179,7 +9179,7 @@
         <v>48</v>
       </c>
       <c r="P117" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q117" t="s">
         <v>47</v>
@@ -9202,7 +9202,7 @@
         <v>34</v>
       </c>
       <c r="E118" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F118" t="s">
         <v>208</v>
@@ -9211,19 +9211,19 @@
         <v>41</v>
       </c>
       <c r="H118" t="s">
-        <v>52</v>
+        <v>336</v>
       </c>
       <c r="I118" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J118" t="s">
-        <v>179</v>
+        <v>348</v>
       </c>
       <c r="K118" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L118" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="M118" t="s">
         <v>321</v>
@@ -9235,7 +9235,7 @@
         <v>48</v>
       </c>
       <c r="P118" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Q118" t="s">
         <v>47</v>
@@ -9258,7 +9258,7 @@
         <v>34</v>
       </c>
       <c r="E119" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F119" t="s">
         <v>208</v>
@@ -9267,19 +9267,19 @@
         <v>41</v>
       </c>
       <c r="H119" t="s">
-        <v>52</v>
+        <v>336</v>
       </c>
       <c r="I119" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J119" t="s">
         <v>179</v>
       </c>
       <c r="K119" t="s">
-        <v>105</v>
+        <v>351</v>
       </c>
       <c r="L119" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="M119" t="s">
         <v>321</v>
@@ -9291,7 +9291,7 @@
         <v>48</v>
       </c>
       <c r="P119" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="Q119" t="s">
         <v>47</v>
@@ -9314,7 +9314,7 @@
         <v>34</v>
       </c>
       <c r="E120" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F120" t="s">
         <v>208</v>
@@ -9323,19 +9323,19 @@
         <v>41</v>
       </c>
       <c r="H120" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="I120" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J120" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K120" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="L120" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="M120" t="s">
         <v>321</v>
@@ -9347,7 +9347,7 @@
         <v>48</v>
       </c>
       <c r="P120" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q120" t="s">
         <v>47</v>
@@ -9370,7 +9370,7 @@
         <v>34</v>
       </c>
       <c r="E121" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F121" t="s">
         <v>208</v>
@@ -9379,19 +9379,19 @@
         <v>41</v>
       </c>
       <c r="H121" t="s">
-        <v>344</v>
+        <v>52</v>
       </c>
       <c r="I121" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="J121" t="s">
         <v>179</v>
       </c>
       <c r="K121" t="s">
-        <v>359</v>
+        <v>67</v>
       </c>
       <c r="L121" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="M121" t="s">
         <v>321</v>
@@ -9400,10 +9400,10 @@
         <v>47</v>
       </c>
       <c r="O121" t="s">
-        <v>48</v>
+        <v>330</v>
       </c>
       <c r="P121" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="Q121" t="s">
         <v>47</v>
@@ -9426,7 +9426,7 @@
         <v>34</v>
       </c>
       <c r="E122" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F122" t="s">
         <v>208</v>
@@ -9435,16 +9435,16 @@
         <v>41</v>
       </c>
       <c r="H122" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="I122" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="J122" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="K122" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="L122" t="s">
         <v>34</v>
@@ -9459,7 +9459,7 @@
         <v>48</v>
       </c>
       <c r="P122" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="Q122" t="s">
         <v>47</v>
@@ -9482,7 +9482,7 @@
         <v>34</v>
       </c>
       <c r="E123" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F123" t="s">
         <v>208</v>
@@ -9491,19 +9491,19 @@
         <v>41</v>
       </c>
       <c r="H123" t="s">
-        <v>52</v>
+        <v>336</v>
       </c>
       <c r="I123" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="J123" t="s">
-        <v>179</v>
+        <v>362</v>
       </c>
       <c r="K123" t="s">
         <v>67</v>
       </c>
       <c r="L123" t="s">
-        <v>364</v>
+        <v>34</v>
       </c>
       <c r="M123" t="s">
         <v>321</v>
@@ -9512,10 +9512,10 @@
         <v>47</v>
       </c>
       <c r="O123" t="s">
-        <v>338</v>
+        <v>48</v>
       </c>
       <c r="P123" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="Q123" t="s">
         <v>47</v>
@@ -9538,7 +9538,7 @@
         <v>34</v>
       </c>
       <c r="E124" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F124" t="s">
         <v>208</v>
@@ -9547,19 +9547,19 @@
         <v>41</v>
       </c>
       <c r="H124" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="I124" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J124" t="s">
-        <v>367</v>
+        <v>179</v>
       </c>
       <c r="K124" t="s">
         <v>105</v>
       </c>
       <c r="L124" t="s">
-        <v>34</v>
+        <v>366</v>
       </c>
       <c r="M124" t="s">
         <v>321</v>
@@ -9571,7 +9571,7 @@
         <v>48</v>
       </c>
       <c r="P124" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q124" t="s">
         <v>47</v>
@@ -9594,28 +9594,28 @@
         <v>34</v>
       </c>
       <c r="E125" t="s">
+        <v>367</v>
+      </c>
+      <c r="F125" t="s">
+        <v>40</v>
+      </c>
+      <c r="G125" t="s">
+        <v>41</v>
+      </c>
+      <c r="H125" t="s">
+        <v>52</v>
+      </c>
+      <c r="I125" t="s">
         <v>368</v>
       </c>
-      <c r="F125" t="s">
-        <v>208</v>
-      </c>
-      <c r="G125" t="s">
-        <v>41</v>
-      </c>
-      <c r="H125" t="s">
-        <v>344</v>
-      </c>
-      <c r="I125" t="s">
+      <c r="J125" t="s">
         <v>369</v>
       </c>
-      <c r="J125" t="s">
+      <c r="K125" t="s">
+        <v>45</v>
+      </c>
+      <c r="L125" t="s">
         <v>370</v>
-      </c>
-      <c r="K125" t="s">
-        <v>67</v>
-      </c>
-      <c r="L125" t="s">
-        <v>34</v>
       </c>
       <c r="M125" t="s">
         <v>321</v>
@@ -9627,7 +9627,7 @@
         <v>48</v>
       </c>
       <c r="P125" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q125" t="s">
         <v>47</v>
@@ -9653,22 +9653,22 @@
         <v>371</v>
       </c>
       <c r="F126" t="s">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="G126" t="s">
         <v>41</v>
       </c>
       <c r="H126" t="s">
+        <v>52</v>
+      </c>
+      <c r="I126" t="s">
         <v>372</v>
       </c>
-      <c r="I126" t="s">
+      <c r="J126" t="s">
         <v>373</v>
       </c>
-      <c r="J126" t="s">
-        <v>179</v>
-      </c>
       <c r="K126" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="L126" t="s">
         <v>374</v>
@@ -9683,7 +9683,7 @@
         <v>48</v>
       </c>
       <c r="P126" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q126" t="s">
         <v>47</v>
@@ -9874,19 +9874,19 @@
         <v>33</v>
       </c>
       <c r="E130" t="s">
+        <v>87</v>
+      </c>
+      <c r="F130" t="s">
+        <v>208</v>
+      </c>
+      <c r="G130" t="s">
+        <v>41</v>
+      </c>
+      <c r="H130" t="s">
         <v>383</v>
       </c>
-      <c r="F130" t="s">
+      <c r="I130" t="s">
         <v>384</v>
-      </c>
-      <c r="G130" t="s">
-        <v>41</v>
-      </c>
-      <c r="H130" t="s">
-        <v>385</v>
-      </c>
-      <c r="I130" t="s">
-        <v>386</v>
       </c>
       <c r="J130" t="s">
         <v>73</v>
@@ -9895,7 +9895,7 @@
         <v>73</v>
       </c>
       <c r="L130" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M130" t="s">
         <v>382</v>
@@ -9904,13 +9904,13 @@
         <v>47</v>
       </c>
       <c r="O130" t="s">
-        <v>34</v>
+        <v>385</v>
       </c>
       <c r="P130" t="s">
-        <v>34</v>
+        <v>384</v>
       </c>
       <c r="Q130" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R130" t="s">
         <v>34</v>
@@ -9930,28 +9930,28 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F131" t="s">
-        <v>384</v>
+        <v>208</v>
       </c>
       <c r="G131" t="s">
         <v>41</v>
       </c>
       <c r="H131" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I131" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="J131" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="K131" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L131" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M131" t="s">
         <v>382</v>
@@ -9960,13 +9960,13 @@
         <v>47</v>
       </c>
       <c r="O131" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="P131" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="Q131" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R131" t="s">
         <v>34</v>
@@ -9986,28 +9986,28 @@
         <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>391</v>
+        <v>113</v>
       </c>
       <c r="F132" t="s">
-        <v>384</v>
+        <v>208</v>
       </c>
       <c r="G132" t="s">
         <v>41</v>
       </c>
       <c r="H132" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I132" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J132" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="K132" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="L132" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M132" t="s">
         <v>382</v>
@@ -10016,13 +10016,13 @@
         <v>47</v>
       </c>
       <c r="O132" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="P132" t="s">
-        <v>34</v>
+        <v>389</v>
       </c>
       <c r="Q132" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R132" t="s">
         <v>34</v>
@@ -10042,28 +10042,28 @@
         <v>34</v>
       </c>
       <c r="E133" t="s">
-        <v>393</v>
+        <v>113</v>
       </c>
       <c r="F133" t="s">
-        <v>384</v>
+        <v>208</v>
       </c>
       <c r="G133" t="s">
         <v>41</v>
       </c>
       <c r="H133" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I133" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="J133" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="K133" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="L133" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M133" t="s">
         <v>382</v>
@@ -10072,13 +10072,13 @@
         <v>47</v>
       </c>
       <c r="O133" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="P133" t="s">
-        <v>34</v>
+        <v>390</v>
       </c>
       <c r="Q133" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R133" t="s">
         <v>34</v>
@@ -10098,28 +10098,28 @@
         <v>34</v>
       </c>
       <c r="E134" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F134" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G134" t="s">
         <v>41</v>
       </c>
       <c r="H134" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I134" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="J134" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K134" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L134" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M134" t="s">
         <v>382</v>
@@ -10128,10 +10128,10 @@
         <v>47</v>
       </c>
       <c r="O134" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
       <c r="P134" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="Q134" t="s">
         <v>47</v>
@@ -10154,28 +10154,28 @@
         <v>34</v>
       </c>
       <c r="E135" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F135" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G135" t="s">
         <v>41</v>
       </c>
       <c r="H135" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I135" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="J135" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="K135" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="L135" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M135" t="s">
         <v>382</v>
@@ -10184,10 +10184,10 @@
         <v>47</v>
       </c>
       <c r="O135" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="P135" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="Q135" t="s">
         <v>47</v>
@@ -10210,28 +10210,28 @@
         <v>34</v>
       </c>
       <c r="E136" t="s">
-        <v>300</v>
+        <v>395</v>
       </c>
       <c r="F136" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G136" t="s">
         <v>41</v>
       </c>
       <c r="H136" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I136" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="J136" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="K136" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L136" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M136" t="s">
         <v>382</v>
@@ -10240,10 +10240,10 @@
         <v>47</v>
       </c>
       <c r="O136" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="P136" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="Q136" t="s">
         <v>47</v>
@@ -10266,28 +10266,28 @@
         <v>34</v>
       </c>
       <c r="E137" t="s">
-        <v>341</v>
+        <v>396</v>
       </c>
       <c r="F137" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G137" t="s">
         <v>41</v>
       </c>
       <c r="H137" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I137" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="J137" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K137" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L137" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M137" t="s">
         <v>382</v>
@@ -10296,10 +10296,10 @@
         <v>47</v>
       </c>
       <c r="O137" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="P137" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="Q137" t="s">
         <v>47</v>
@@ -10322,28 +10322,28 @@
         <v>34</v>
       </c>
       <c r="E138" t="s">
-        <v>285</v>
+        <v>397</v>
       </c>
       <c r="F138" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G138" t="s">
         <v>41</v>
       </c>
       <c r="H138" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I138" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J138" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K138" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L138" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M138" t="s">
         <v>382</v>
@@ -10352,10 +10352,10 @@
         <v>47</v>
       </c>
       <c r="O138" t="s">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="P138" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="Q138" t="s">
         <v>47</v>
@@ -10378,28 +10378,28 @@
         <v>34</v>
       </c>
       <c r="E139" t="s">
-        <v>339</v>
+        <v>150</v>
       </c>
       <c r="F139" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G139" t="s">
         <v>41</v>
       </c>
       <c r="H139" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I139" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J139" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="K139" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="L139" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M139" t="s">
         <v>382</v>
@@ -10408,10 +10408,10 @@
         <v>47</v>
       </c>
       <c r="O139" t="s">
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="P139" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="Q139" t="s">
         <v>47</v>
@@ -10434,28 +10434,28 @@
         <v>34</v>
       </c>
       <c r="E140" t="s">
-        <v>308</v>
+        <v>110</v>
       </c>
       <c r="F140" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G140" t="s">
         <v>41</v>
       </c>
       <c r="H140" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I140" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J140" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="K140" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L140" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M140" t="s">
         <v>382</v>
@@ -10464,10 +10464,10 @@
         <v>47</v>
       </c>
       <c r="O140" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="P140" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="Q140" t="s">
         <v>47</v>
@@ -10490,28 +10490,28 @@
         <v>34</v>
       </c>
       <c r="E141" t="s">
-        <v>306</v>
+        <v>401</v>
       </c>
       <c r="F141" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G141" t="s">
         <v>41</v>
       </c>
       <c r="H141" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I141" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J141" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="K141" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L141" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M141" t="s">
         <v>382</v>
@@ -10520,10 +10520,10 @@
         <v>47</v>
       </c>
       <c r="O141" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="P141" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Q141" t="s">
         <v>47</v>
@@ -10546,28 +10546,28 @@
         <v>34</v>
       </c>
       <c r="E142" t="s">
-        <v>405</v>
+        <v>150</v>
       </c>
       <c r="F142" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G142" t="s">
         <v>41</v>
       </c>
       <c r="H142" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I142" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="J142" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K142" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L142" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M142" t="s">
         <v>382</v>
@@ -10576,10 +10576,10 @@
         <v>47</v>
       </c>
       <c r="O142" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="P142" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="Q142" t="s">
         <v>47</v>
@@ -10602,28 +10602,28 @@
         <v>34</v>
       </c>
       <c r="E143" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F143" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G143" t="s">
         <v>41</v>
       </c>
       <c r="H143" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I143" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="J143" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K143" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L143" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M143" t="s">
         <v>382</v>
@@ -10632,10 +10632,10 @@
         <v>47</v>
       </c>
       <c r="O143" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="P143" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="Q143" t="s">
         <v>47</v>
@@ -10658,28 +10658,28 @@
         <v>34</v>
       </c>
       <c r="E144" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F144" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G144" t="s">
         <v>41</v>
       </c>
       <c r="H144" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I144" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="J144" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="K144" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L144" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M144" t="s">
         <v>382</v>
@@ -10688,10 +10688,10 @@
         <v>47</v>
       </c>
       <c r="O144" t="s">
-        <v>149</v>
+        <v>294</v>
       </c>
       <c r="P144" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="Q144" t="s">
         <v>47</v>
@@ -10714,19 +10714,19 @@
         <v>34</v>
       </c>
       <c r="E145" t="s">
-        <v>312</v>
+        <v>405</v>
       </c>
       <c r="F145" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G145" t="s">
         <v>41</v>
       </c>
       <c r="H145" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I145" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="J145" t="s">
         <v>73</v>
@@ -10735,7 +10735,7 @@
         <v>73</v>
       </c>
       <c r="L145" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M145" t="s">
         <v>382</v>
@@ -10744,10 +10744,10 @@
         <v>47</v>
       </c>
       <c r="O145" t="s">
-        <v>412</v>
+        <v>294</v>
       </c>
       <c r="P145" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="Q145" t="s">
         <v>47</v>
@@ -10770,28 +10770,28 @@
         <v>34</v>
       </c>
       <c r="E146" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F146" t="s">
-        <v>247</v>
+        <v>409</v>
       </c>
       <c r="G146" t="s">
         <v>41</v>
       </c>
       <c r="H146" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I146" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="J146" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K146" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L146" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M146" t="s">
         <v>382</v>
@@ -10800,13 +10800,13 @@
         <v>47</v>
       </c>
       <c r="O146" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="P146" t="s">
-        <v>414</v>
+        <v>34</v>
       </c>
       <c r="Q146" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R146" t="s">
         <v>34</v>
@@ -10826,28 +10826,28 @@
         <v>34</v>
       </c>
       <c r="E147" t="s">
-        <v>276</v>
+        <v>412</v>
       </c>
       <c r="F147" t="s">
-        <v>247</v>
+        <v>409</v>
       </c>
       <c r="G147" t="s">
         <v>41</v>
       </c>
       <c r="H147" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I147" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J147" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K147" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L147" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M147" t="s">
         <v>382</v>
@@ -10856,13 +10856,13 @@
         <v>47</v>
       </c>
       <c r="O147" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="P147" t="s">
-        <v>415</v>
+        <v>34</v>
       </c>
       <c r="Q147" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R147" t="s">
         <v>34</v>
@@ -10882,28 +10882,28 @@
         <v>34</v>
       </c>
       <c r="E148" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F148" t="s">
-        <v>247</v>
+        <v>409</v>
       </c>
       <c r="G148" t="s">
         <v>41</v>
       </c>
       <c r="H148" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I148" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J148" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="K148" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="L148" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M148" t="s">
         <v>382</v>
@@ -10912,13 +10912,13 @@
         <v>47</v>
       </c>
       <c r="O148" t="s">
-        <v>412</v>
+        <v>34</v>
       </c>
       <c r="P148" t="s">
-        <v>417</v>
+        <v>34</v>
       </c>
       <c r="Q148" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R148" t="s">
         <v>34</v>
@@ -10938,28 +10938,28 @@
         <v>34</v>
       </c>
       <c r="E149" t="s">
-        <v>303</v>
+        <v>416</v>
       </c>
       <c r="F149" t="s">
-        <v>247</v>
+        <v>409</v>
       </c>
       <c r="G149" t="s">
         <v>41</v>
       </c>
       <c r="H149" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I149" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J149" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="K149" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="L149" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M149" t="s">
         <v>382</v>
@@ -10968,13 +10968,13 @@
         <v>47</v>
       </c>
       <c r="O149" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="P149" t="s">
-        <v>418</v>
+        <v>34</v>
       </c>
       <c r="Q149" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R149" t="s">
         <v>34</v>
@@ -10994,7 +10994,7 @@
         <v>34</v>
       </c>
       <c r="E150" t="s">
-        <v>298</v>
+        <v>418</v>
       </c>
       <c r="F150" t="s">
         <v>247</v>
@@ -11003,7 +11003,7 @@
         <v>41</v>
       </c>
       <c r="H150" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I150" t="s">
         <v>419</v>
@@ -11015,7 +11015,7 @@
         <v>73</v>
       </c>
       <c r="L150" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M150" t="s">
         <v>382</v>
@@ -11059,19 +11059,19 @@
         <v>41</v>
       </c>
       <c r="H151" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I151" t="s">
         <v>421</v>
       </c>
       <c r="J151" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="K151" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L151" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M151" t="s">
         <v>382</v>
@@ -11080,7 +11080,7 @@
         <v>47</v>
       </c>
       <c r="O151" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="P151" t="s">
         <v>421</v>
@@ -11106,7 +11106,7 @@
         <v>34</v>
       </c>
       <c r="E152" t="s">
-        <v>422</v>
+        <v>300</v>
       </c>
       <c r="F152" t="s">
         <v>247</v>
@@ -11115,19 +11115,19 @@
         <v>41</v>
       </c>
       <c r="H152" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I152" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J152" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="K152" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L152" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M152" t="s">
         <v>382</v>
@@ -11136,10 +11136,10 @@
         <v>47</v>
       </c>
       <c r="O152" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="P152" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q152" t="s">
         <v>47</v>
@@ -11162,7 +11162,7 @@
         <v>34</v>
       </c>
       <c r="E153" t="s">
-        <v>424</v>
+        <v>333</v>
       </c>
       <c r="F153" t="s">
         <v>247</v>
@@ -11171,19 +11171,19 @@
         <v>41</v>
       </c>
       <c r="H153" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I153" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J153" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="K153" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="L153" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M153" t="s">
         <v>382</v>
@@ -11192,10 +11192,10 @@
         <v>47</v>
       </c>
       <c r="O153" t="s">
-        <v>152</v>
+        <v>330</v>
       </c>
       <c r="P153" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q153" t="s">
         <v>47</v>
@@ -11218,7 +11218,7 @@
         <v>34</v>
       </c>
       <c r="E154" t="s">
-        <v>426</v>
+        <v>285</v>
       </c>
       <c r="F154" t="s">
         <v>247</v>
@@ -11227,19 +11227,19 @@
         <v>41</v>
       </c>
       <c r="H154" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I154" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J154" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K154" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L154" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M154" t="s">
         <v>382</v>
@@ -11248,10 +11248,10 @@
         <v>47</v>
       </c>
       <c r="O154" t="s">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="P154" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="Q154" t="s">
         <v>47</v>
@@ -11274,7 +11274,7 @@
         <v>34</v>
       </c>
       <c r="E155" t="s">
-        <v>280</v>
+        <v>331</v>
       </c>
       <c r="F155" t="s">
         <v>247</v>
@@ -11283,19 +11283,19 @@
         <v>41</v>
       </c>
       <c r="H155" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I155" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J155" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="K155" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="L155" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M155" t="s">
         <v>382</v>
@@ -11304,10 +11304,10 @@
         <v>47</v>
       </c>
       <c r="O155" t="s">
-        <v>145</v>
+        <v>330</v>
       </c>
       <c r="P155" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="Q155" t="s">
         <v>47</v>
@@ -11330,7 +11330,7 @@
         <v>34</v>
       </c>
       <c r="E156" t="s">
-        <v>429</v>
+        <v>308</v>
       </c>
       <c r="F156" t="s">
         <v>247</v>
@@ -11339,19 +11339,19 @@
         <v>41</v>
       </c>
       <c r="H156" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I156" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="J156" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K156" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L156" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M156" t="s">
         <v>382</v>
@@ -11360,10 +11360,10 @@
         <v>47</v>
       </c>
       <c r="O156" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="P156" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="Q156" t="s">
         <v>47</v>
@@ -11386,7 +11386,7 @@
         <v>34</v>
       </c>
       <c r="E157" t="s">
-        <v>431</v>
+        <v>306</v>
       </c>
       <c r="F157" t="s">
         <v>247</v>
@@ -11395,19 +11395,19 @@
         <v>41</v>
       </c>
       <c r="H157" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I157" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="J157" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="K157" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L157" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M157" t="s">
         <v>382</v>
@@ -11416,10 +11416,10 @@
         <v>47</v>
       </c>
       <c r="O157" t="s">
-        <v>294</v>
+        <v>98</v>
       </c>
       <c r="P157" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="Q157" t="s">
         <v>47</v>
@@ -11442,28 +11442,28 @@
         <v>34</v>
       </c>
       <c r="E158" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="F158" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G158" t="s">
         <v>41</v>
       </c>
       <c r="H158" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I158" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J158" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="K158" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="L158" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M158" t="s">
         <v>382</v>
@@ -11472,10 +11472,10 @@
         <v>47</v>
       </c>
       <c r="O158" t="s">
-        <v>48</v>
+        <v>269</v>
       </c>
       <c r="P158" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="Q158" t="s">
         <v>47</v>
@@ -11498,28 +11498,28 @@
         <v>34</v>
       </c>
       <c r="E159" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F159" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G159" t="s">
         <v>41</v>
       </c>
       <c r="H159" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I159" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="J159" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="K159" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="L159" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M159" t="s">
         <v>382</v>
@@ -11528,10 +11528,10 @@
         <v>47</v>
       </c>
       <c r="O159" t="s">
-        <v>437</v>
+        <v>169</v>
       </c>
       <c r="P159" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="Q159" t="s">
         <v>47</v>
@@ -11554,28 +11554,28 @@
         <v>34</v>
       </c>
       <c r="E160" t="s">
-        <v>94</v>
+        <v>432</v>
       </c>
       <c r="F160" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G160" t="s">
         <v>41</v>
       </c>
       <c r="H160" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I160" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="J160" t="s">
-        <v>439</v>
+        <v>119</v>
       </c>
       <c r="K160" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L160" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M160" t="s">
         <v>382</v>
@@ -11584,10 +11584,10 @@
         <v>47</v>
       </c>
       <c r="O160" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="P160" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q160" t="s">
         <v>47</v>
@@ -11610,28 +11610,28 @@
         <v>34</v>
       </c>
       <c r="E161" t="s">
-        <v>440</v>
+        <v>312</v>
       </c>
       <c r="F161" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G161" t="s">
         <v>41</v>
       </c>
       <c r="H161" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I161" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="J161" t="s">
-        <v>442</v>
+        <v>73</v>
       </c>
       <c r="K161" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L161" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M161" t="s">
         <v>382</v>
@@ -11640,10 +11640,10 @@
         <v>47</v>
       </c>
       <c r="O161" t="s">
-        <v>269</v>
+        <v>385</v>
       </c>
       <c r="P161" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="Q161" t="s">
         <v>47</v>
@@ -11666,28 +11666,28 @@
         <v>34</v>
       </c>
       <c r="E162" t="s">
-        <v>94</v>
+        <v>435</v>
       </c>
       <c r="F162" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G162" t="s">
         <v>41</v>
       </c>
       <c r="H162" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I162" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="J162" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="K162" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="L162" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M162" t="s">
         <v>382</v>
@@ -11696,10 +11696,10 @@
         <v>47</v>
       </c>
       <c r="O162" t="s">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="P162" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="Q162" t="s">
         <v>47</v>
@@ -11722,28 +11722,28 @@
         <v>34</v>
       </c>
       <c r="E163" t="s">
-        <v>440</v>
+        <v>276</v>
       </c>
       <c r="F163" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G163" t="s">
         <v>41</v>
       </c>
       <c r="H163" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I163" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="J163" t="s">
-        <v>439</v>
+        <v>78</v>
       </c>
       <c r="K163" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="L163" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M163" t="s">
         <v>382</v>
@@ -11752,10 +11752,10 @@
         <v>47</v>
       </c>
       <c r="O163" t="s">
-        <v>269</v>
+        <v>169</v>
       </c>
       <c r="P163" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="Q163" t="s">
         <v>47</v>
@@ -11778,28 +11778,28 @@
         <v>34</v>
       </c>
       <c r="E164" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="F164" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G164" t="s">
         <v>41</v>
       </c>
       <c r="H164" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I164" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="J164" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="K164" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L164" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M164" t="s">
         <v>382</v>
@@ -11808,10 +11808,10 @@
         <v>47</v>
       </c>
       <c r="O164" t="s">
-        <v>269</v>
+        <v>385</v>
       </c>
       <c r="P164" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="Q164" t="s">
         <v>47</v>
@@ -11834,28 +11834,28 @@
         <v>34</v>
       </c>
       <c r="E165" t="s">
-        <v>448</v>
+        <v>303</v>
       </c>
       <c r="F165" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G165" t="s">
         <v>41</v>
       </c>
       <c r="H165" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I165" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="J165" t="s">
-        <v>447</v>
+        <v>119</v>
       </c>
       <c r="K165" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L165" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M165" t="s">
         <v>382</v>
@@ -11864,10 +11864,10 @@
         <v>47</v>
       </c>
       <c r="O165" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="P165" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="Q165" t="s">
         <v>47</v>
@@ -11890,28 +11890,28 @@
         <v>34</v>
       </c>
       <c r="E166" t="s">
-        <v>87</v>
+        <v>298</v>
       </c>
       <c r="F166" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G166" t="s">
         <v>41</v>
       </c>
       <c r="H166" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I166" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="J166" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="K166" t="s">
         <v>73</v>
       </c>
       <c r="L166" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M166" t="s">
         <v>382</v>
@@ -11920,10 +11920,10 @@
         <v>47</v>
       </c>
       <c r="O166" t="s">
-        <v>412</v>
+        <v>115</v>
       </c>
       <c r="P166" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="Q166" t="s">
         <v>47</v>
@@ -11946,28 +11946,28 @@
         <v>34</v>
       </c>
       <c r="E167" t="s">
-        <v>166</v>
+        <v>442</v>
       </c>
       <c r="F167" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G167" t="s">
         <v>41</v>
       </c>
       <c r="H167" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I167" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="J167" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="K167" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="L167" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M167" t="s">
         <v>382</v>
@@ -11976,10 +11976,10 @@
         <v>47</v>
       </c>
       <c r="O167" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="P167" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="Q167" t="s">
         <v>47</v>
@@ -12002,28 +12002,28 @@
         <v>34</v>
       </c>
       <c r="E168" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F168" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G168" t="s">
         <v>41</v>
       </c>
       <c r="H168" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I168" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="J168" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="K168" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L168" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M168" t="s">
         <v>382</v>
@@ -12032,10 +12032,10 @@
         <v>47</v>
       </c>
       <c r="O168" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="P168" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="Q168" t="s">
         <v>47</v>
@@ -12058,28 +12058,28 @@
         <v>34</v>
       </c>
       <c r="E169" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="F169" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G169" t="s">
         <v>41</v>
       </c>
       <c r="H169" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I169" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="J169" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="K169" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="L169" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M169" t="s">
         <v>382</v>
@@ -12088,10 +12088,10 @@
         <v>47</v>
       </c>
       <c r="O169" t="s">
-        <v>262</v>
+        <v>152</v>
       </c>
       <c r="P169" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="Q169" t="s">
         <v>47</v>
@@ -12114,19 +12114,19 @@
         <v>34</v>
       </c>
       <c r="E170" t="s">
-        <v>87</v>
+        <v>448</v>
       </c>
       <c r="F170" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G170" t="s">
         <v>41</v>
       </c>
       <c r="H170" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I170" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="J170" t="s">
         <v>73</v>
@@ -12135,7 +12135,7 @@
         <v>73</v>
       </c>
       <c r="L170" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M170" t="s">
         <v>382</v>
@@ -12144,10 +12144,10 @@
         <v>47</v>
       </c>
       <c r="O170" t="s">
-        <v>412</v>
+        <v>294</v>
       </c>
       <c r="P170" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="Q170" t="s">
         <v>47</v>
@@ -12170,28 +12170,28 @@
         <v>34</v>
       </c>
       <c r="E171" t="s">
-        <v>457</v>
+        <v>280</v>
       </c>
       <c r="F171" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G171" t="s">
         <v>41</v>
       </c>
       <c r="H171" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I171" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="J171" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="K171" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="L171" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M171" t="s">
         <v>382</v>
@@ -12200,10 +12200,10 @@
         <v>47</v>
       </c>
       <c r="O171" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="P171" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="Q171" t="s">
         <v>47</v>
@@ -12226,28 +12226,28 @@
         <v>34</v>
       </c>
       <c r="E172" t="s">
-        <v>113</v>
+        <v>451</v>
       </c>
       <c r="F172" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G172" t="s">
         <v>41</v>
       </c>
       <c r="H172" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I172" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="J172" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="K172" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="L172" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M172" t="s">
         <v>382</v>
@@ -12256,10 +12256,10 @@
         <v>47</v>
       </c>
       <c r="O172" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="P172" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="Q172" t="s">
         <v>47</v>
@@ -12282,19 +12282,19 @@
         <v>34</v>
       </c>
       <c r="E173" t="s">
-        <v>113</v>
+        <v>453</v>
       </c>
       <c r="F173" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G173" t="s">
         <v>41</v>
       </c>
       <c r="H173" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I173" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="J173" t="s">
         <v>73</v>
@@ -12303,7 +12303,7 @@
         <v>73</v>
       </c>
       <c r="L173" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M173" t="s">
         <v>382</v>
@@ -12312,10 +12312,10 @@
         <v>47</v>
       </c>
       <c r="O173" t="s">
-        <v>115</v>
+        <v>294</v>
       </c>
       <c r="P173" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="Q173" t="s">
         <v>47</v>
@@ -12338,7 +12338,7 @@
         <v>34</v>
       </c>
       <c r="E174" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="F174" t="s">
         <v>208</v>
@@ -12347,16 +12347,16 @@
         <v>41</v>
       </c>
       <c r="H174" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I174" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="J174" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="K174" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="L174" t="s">
         <v>34</v>
@@ -12368,10 +12368,10 @@
         <v>47</v>
       </c>
       <c r="O174" t="s">
-        <v>262</v>
+        <v>48</v>
       </c>
       <c r="P174" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="Q174" t="s">
         <v>47</v>
@@ -12394,7 +12394,7 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F175" t="s">
         <v>208</v>
@@ -12403,16 +12403,16 @@
         <v>41</v>
       </c>
       <c r="H175" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I175" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="J175" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="K175" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="L175" t="s">
         <v>34</v>
@@ -12424,10 +12424,10 @@
         <v>47</v>
       </c>
       <c r="O175" t="s">
-        <v>269</v>
+        <v>459</v>
       </c>
       <c r="P175" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="Q175" t="s">
         <v>47</v>
@@ -12450,7 +12450,7 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>464</v>
+        <v>94</v>
       </c>
       <c r="F176" t="s">
         <v>208</v>
@@ -12459,16 +12459,16 @@
         <v>41</v>
       </c>
       <c r="H176" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I176" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="J176" t="s">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="K176" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L176" t="s">
         <v>34</v>
@@ -12480,10 +12480,10 @@
         <v>47</v>
       </c>
       <c r="O176" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="P176" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="Q176" t="s">
         <v>47</v>
@@ -12506,7 +12506,7 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F177" t="s">
         <v>208</v>
@@ -12515,16 +12515,16 @@
         <v>41</v>
       </c>
       <c r="H177" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I177" t="s">
         <v>463</v>
       </c>
       <c r="J177" t="s">
-        <v>68</v>
+        <v>464</v>
       </c>
       <c r="K177" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="L177" t="s">
         <v>34</v>
@@ -12536,7 +12536,7 @@
         <v>47</v>
       </c>
       <c r="O177" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="P177" t="s">
         <v>463</v>
@@ -12562,7 +12562,7 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>466</v>
+        <v>94</v>
       </c>
       <c r="F178" t="s">
         <v>208</v>
@@ -12571,16 +12571,16 @@
         <v>41</v>
       </c>
       <c r="H178" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I178" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J178" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="K178" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L178" t="s">
         <v>34</v>
@@ -12592,10 +12592,10 @@
         <v>47</v>
       </c>
       <c r="O178" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="P178" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="Q178" t="s">
         <v>47</v>
@@ -12618,7 +12618,7 @@
         <v>34</v>
       </c>
       <c r="E179" t="s">
-        <v>150</v>
+        <v>462</v>
       </c>
       <c r="F179" t="s">
         <v>208</v>
@@ -12627,16 +12627,16 @@
         <v>41</v>
       </c>
       <c r="H179" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I179" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="J179" t="s">
-        <v>120</v>
+        <v>461</v>
       </c>
       <c r="K179" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L179" t="s">
         <v>34</v>
@@ -12648,10 +12648,10 @@
         <v>47</v>
       </c>
       <c r="O179" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="P179" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="Q179" t="s">
         <v>47</v>
@@ -12674,7 +12674,7 @@
         <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>110</v>
+        <v>393</v>
       </c>
       <c r="F180" t="s">
         <v>208</v>
@@ -12683,16 +12683,16 @@
         <v>41</v>
       </c>
       <c r="H180" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I180" t="s">
+        <v>467</v>
+      </c>
+      <c r="J180" t="s">
         <v>468</v>
       </c>
-      <c r="J180" t="s">
-        <v>105</v>
-      </c>
       <c r="K180" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="L180" t="s">
         <v>34</v>
@@ -12704,10 +12704,10 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="P180" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Q180" t="s">
         <v>47</v>
@@ -12739,16 +12739,16 @@
         <v>41</v>
       </c>
       <c r="H181" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I181" t="s">
         <v>470</v>
       </c>
       <c r="J181" t="s">
-        <v>73</v>
+        <v>468</v>
       </c>
       <c r="K181" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L181" t="s">
         <v>34</v>
@@ -12760,7 +12760,7 @@
         <v>47</v>
       </c>
       <c r="O181" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="P181" t="s">
         <v>470</v>
@@ -12786,7 +12786,7 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="F182" t="s">
         <v>208</v>
@@ -12795,16 +12795,16 @@
         <v>41</v>
       </c>
       <c r="H182" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I182" t="s">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="J182" t="s">
-        <v>120</v>
+        <v>468</v>
       </c>
       <c r="K182" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="L182" t="s">
         <v>34</v>
@@ -12816,10 +12816,10 @@
         <v>47</v>
       </c>
       <c r="O182" t="s">
-        <v>152</v>
+        <v>385</v>
       </c>
       <c r="P182" t="s">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="Q182" t="s">
         <v>47</v>
@@ -12842,7 +12842,7 @@
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>471</v>
+        <v>166</v>
       </c>
       <c r="F183" t="s">
         <v>208</v>
@@ -12851,16 +12851,16 @@
         <v>41</v>
       </c>
       <c r="H183" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I183" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J183" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K183" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L183" t="s">
         <v>34</v>
@@ -12872,10 +12872,10 @@
         <v>47</v>
       </c>
       <c r="O183" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="P183" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q183" t="s">
         <v>47</v>
@@ -12898,7 +12898,7 @@
         <v>34</v>
       </c>
       <c r="E184" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F184" t="s">
         <v>208</v>
@@ -12907,16 +12907,16 @@
         <v>41</v>
       </c>
       <c r="H184" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I184" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J184" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="K184" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L184" t="s">
         <v>34</v>
@@ -12928,10 +12928,10 @@
         <v>47</v>
       </c>
       <c r="O184" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="P184" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q184" t="s">
         <v>47</v>
@@ -12954,7 +12954,7 @@
         <v>34</v>
       </c>
       <c r="E185" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F185" t="s">
         <v>208</v>
@@ -12963,16 +12963,16 @@
         <v>41</v>
       </c>
       <c r="H185" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I185" t="s">
         <v>475</v>
       </c>
       <c r="J185" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K185" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L185" t="s">
         <v>34</v>
@@ -12984,7 +12984,7 @@
         <v>47</v>
       </c>
       <c r="O185" t="s">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="P185" t="s">
         <v>475</v>
@@ -14048,7 +14048,7 @@
         <v>47</v>
       </c>
       <c r="O204" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="P204" t="s">
         <v>501</v>
@@ -14832,7 +14832,7 @@
         <v>47</v>
       </c>
       <c r="O218" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="P218" t="s">
         <v>523</v>
@@ -15392,7 +15392,7 @@
         <v>47</v>
       </c>
       <c r="O228" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="P228" t="s">
         <v>501</v>
@@ -16120,7 +16120,7 @@
         <v>47</v>
       </c>
       <c r="O241" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="P241" t="s">
         <v>535</v>
@@ -17490,25 +17490,25 @@
         <v>33</v>
       </c>
       <c r="E266" t="s">
+        <v>263</v>
+      </c>
+      <c r="F266" t="s">
+        <v>247</v>
+      </c>
+      <c r="G266" t="s">
+        <v>41</v>
+      </c>
+      <c r="H266" t="s">
         <v>565</v>
       </c>
-      <c r="F266" t="s">
-        <v>484</v>
-      </c>
-      <c r="G266" t="s">
-        <v>41</v>
-      </c>
-      <c r="H266" t="s">
-        <v>197</v>
-      </c>
       <c r="I266" t="s">
-        <v>550</v>
+        <v>491</v>
       </c>
       <c r="J266" t="s">
-        <v>124</v>
+        <v>566</v>
       </c>
       <c r="K266" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L266" t="s">
         <v>34</v>
@@ -17520,13 +17520,13 @@
         <v>47</v>
       </c>
       <c r="O266" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="P266" t="s">
-        <v>34</v>
+        <v>491</v>
       </c>
       <c r="Q266" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R266" t="s">
         <v>34</v>
@@ -17546,25 +17546,25 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>391</v>
+        <v>250</v>
       </c>
       <c r="F267" t="s">
-        <v>484</v>
+        <v>247</v>
       </c>
       <c r="G267" t="s">
         <v>41</v>
       </c>
       <c r="H267" t="s">
-        <v>197</v>
+        <v>565</v>
       </c>
       <c r="I267" t="s">
-        <v>494</v>
+        <v>567</v>
       </c>
       <c r="J267" t="s">
-        <v>165</v>
+        <v>568</v>
       </c>
       <c r="K267" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="L267" t="s">
         <v>34</v>
@@ -17576,13 +17576,13 @@
         <v>47</v>
       </c>
       <c r="O267" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="P267" t="s">
-        <v>34</v>
+        <v>567</v>
       </c>
       <c r="Q267" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R267" t="s">
         <v>34</v>
@@ -17602,25 +17602,25 @@
         <v>34</v>
       </c>
       <c r="E268" t="s">
-        <v>566</v>
+        <v>258</v>
       </c>
       <c r="F268" t="s">
-        <v>484</v>
+        <v>247</v>
       </c>
       <c r="G268" t="s">
         <v>41</v>
       </c>
       <c r="H268" t="s">
-        <v>197</v>
+        <v>569</v>
       </c>
       <c r="I268" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="J268" t="s">
-        <v>119</v>
+        <v>568</v>
       </c>
       <c r="K268" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L268" t="s">
         <v>34</v>
@@ -17632,13 +17632,13 @@
         <v>47</v>
       </c>
       <c r="O268" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="P268" t="s">
-        <v>34</v>
+        <v>502</v>
       </c>
       <c r="Q268" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R268" t="s">
         <v>34</v>
@@ -17658,25 +17658,25 @@
         <v>34</v>
       </c>
       <c r="E269" t="s">
-        <v>567</v>
+        <v>265</v>
       </c>
       <c r="F269" t="s">
-        <v>484</v>
+        <v>247</v>
       </c>
       <c r="G269" t="s">
         <v>41</v>
       </c>
       <c r="H269" t="s">
-        <v>197</v>
+        <v>570</v>
       </c>
       <c r="I269" t="s">
-        <v>568</v>
+        <v>497</v>
       </c>
       <c r="J269" t="s">
-        <v>78</v>
+        <v>571</v>
       </c>
       <c r="K269" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="L269" t="s">
         <v>34</v>
@@ -17688,13 +17688,13 @@
         <v>47</v>
       </c>
       <c r="O269" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="P269" t="s">
-        <v>34</v>
+        <v>497</v>
       </c>
       <c r="Q269" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R269" t="s">
         <v>34</v>
@@ -17714,22 +17714,22 @@
         <v>34</v>
       </c>
       <c r="E270" t="s">
-        <v>341</v>
+        <v>290</v>
       </c>
       <c r="F270" t="s">
-        <v>484</v>
+        <v>247</v>
       </c>
       <c r="G270" t="s">
         <v>41</v>
       </c>
       <c r="H270" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="I270" t="s">
-        <v>501</v>
+        <v>573</v>
       </c>
       <c r="J270" t="s">
-        <v>73</v>
+        <v>571</v>
       </c>
       <c r="K270" t="s">
         <v>73</v>
@@ -17744,13 +17744,13 @@
         <v>47</v>
       </c>
       <c r="O270" t="s">
-        <v>34</v>
+        <v>294</v>
       </c>
       <c r="P270" t="s">
-        <v>34</v>
+        <v>573</v>
       </c>
       <c r="Q270" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R270" t="s">
         <v>34</v>
@@ -17779,13 +17779,13 @@
         <v>41</v>
       </c>
       <c r="H271" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="I271" t="s">
         <v>495</v>
       </c>
       <c r="J271" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K271" t="s">
         <v>133</v>
@@ -17826,7 +17826,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="F272" t="s">
         <v>247</v>
@@ -17835,16 +17835,16 @@
         <v>41</v>
       </c>
       <c r="H272" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="I272" t="s">
-        <v>572</v>
+        <v>498</v>
       </c>
       <c r="J272" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="K272" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L272" t="s">
         <v>34</v>
@@ -17856,10 +17856,10 @@
         <v>47</v>
       </c>
       <c r="O272" t="s">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="P272" t="s">
-        <v>572</v>
+        <v>498</v>
       </c>
       <c r="Q272" t="s">
         <v>47</v>
@@ -17882,7 +17882,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="F273" t="s">
         <v>247</v>
@@ -17891,16 +17891,16 @@
         <v>41</v>
       </c>
       <c r="H273" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="I273" t="s">
-        <v>497</v>
+        <v>575</v>
       </c>
       <c r="J273" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="K273" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="L273" t="s">
         <v>34</v>
@@ -17912,10 +17912,10 @@
         <v>47</v>
       </c>
       <c r="O273" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="P273" t="s">
-        <v>497</v>
+        <v>575</v>
       </c>
       <c r="Q273" t="s">
         <v>47</v>
@@ -17938,7 +17938,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="F274" t="s">
         <v>247</v>
@@ -17947,16 +17947,16 @@
         <v>41</v>
       </c>
       <c r="H274" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="I274" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="J274" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="K274" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L274" t="s">
         <v>34</v>
@@ -17968,10 +17968,10 @@
         <v>47</v>
       </c>
       <c r="O274" t="s">
-        <v>115</v>
+        <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="Q274" t="s">
         <v>47</v>
@@ -17994,7 +17994,7 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F275" t="s">
         <v>247</v>
@@ -18003,16 +18003,16 @@
         <v>41</v>
       </c>
       <c r="H275" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="I275" t="s">
-        <v>577</v>
+        <v>500</v>
       </c>
       <c r="J275" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="K275" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="L275" t="s">
         <v>34</v>
@@ -18024,10 +18024,10 @@
         <v>47</v>
       </c>
       <c r="O275" t="s">
-        <v>112</v>
+        <v>385</v>
       </c>
       <c r="P275" t="s">
-        <v>577</v>
+        <v>500</v>
       </c>
       <c r="Q275" t="s">
         <v>47</v>
@@ -18050,7 +18050,7 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F276" t="s">
         <v>247</v>
@@ -18059,16 +18059,16 @@
         <v>41</v>
       </c>
       <c r="H276" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="I276" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="J276" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="K276" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L276" t="s">
         <v>34</v>
@@ -18080,10 +18080,10 @@
         <v>47</v>
       </c>
       <c r="O276" t="s">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="P276" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="Q276" t="s">
         <v>47</v>
@@ -18106,7 +18106,7 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
-        <v>260</v>
+        <v>576</v>
       </c>
       <c r="F277" t="s">
         <v>247</v>
@@ -18115,16 +18115,16 @@
         <v>41</v>
       </c>
       <c r="H277" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="I277" t="s">
-        <v>498</v>
+        <v>577</v>
       </c>
       <c r="J277" t="s">
-        <v>578</v>
+        <v>182</v>
       </c>
       <c r="K277" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="L277" t="s">
         <v>34</v>
@@ -18136,10 +18136,10 @@
         <v>47</v>
       </c>
       <c r="O277" t="s">
-        <v>262</v>
+        <v>578</v>
       </c>
       <c r="P277" t="s">
-        <v>498</v>
+        <v>577</v>
       </c>
       <c r="Q277" t="s">
         <v>47</v>
@@ -18162,7 +18162,7 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="F278" t="s">
         <v>247</v>
@@ -18171,16 +18171,16 @@
         <v>41</v>
       </c>
       <c r="H278" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="I278" t="s">
         <v>579</v>
       </c>
       <c r="J278" t="s">
-        <v>578</v>
+        <v>182</v>
       </c>
       <c r="K278" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L278" t="s">
         <v>34</v>
@@ -18192,7 +18192,7 @@
         <v>47</v>
       </c>
       <c r="O278" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="P278" t="s">
         <v>579</v>
@@ -18218,25 +18218,25 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>267</v>
+        <v>580</v>
       </c>
       <c r="F279" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
       <c r="G279" t="s">
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>570</v>
+        <v>192</v>
       </c>
       <c r="I279" t="s">
-        <v>496</v>
+        <v>581</v>
       </c>
       <c r="J279" t="s">
-        <v>578</v>
+        <v>78</v>
       </c>
       <c r="K279" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="L279" t="s">
         <v>34</v>
@@ -18248,13 +18248,13 @@
         <v>47</v>
       </c>
       <c r="O279" t="s">
-        <v>269</v>
+        <v>34</v>
       </c>
       <c r="P279" t="s">
-        <v>496</v>
+        <v>34</v>
       </c>
       <c r="Q279" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R279" t="s">
         <v>34</v>
@@ -18274,7 +18274,7 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>580</v>
+        <v>414</v>
       </c>
       <c r="F280" t="s">
         <v>484</v>
@@ -18283,16 +18283,16 @@
         <v>41</v>
       </c>
       <c r="H280" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I280" t="s">
-        <v>581</v>
+        <v>494</v>
       </c>
       <c r="J280" t="s">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="K280" t="s">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="L280" t="s">
         <v>34</v>
@@ -18330,25 +18330,25 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
-        <v>246</v>
+        <v>582</v>
       </c>
       <c r="F281" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
       <c r="G281" t="s">
         <v>41</v>
       </c>
       <c r="H281" t="s">
-        <v>570</v>
+        <v>192</v>
       </c>
       <c r="I281" t="s">
-        <v>503</v>
+        <v>550</v>
       </c>
       <c r="J281" t="s">
-        <v>578</v>
+        <v>124</v>
       </c>
       <c r="K281" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="L281" t="s">
         <v>34</v>
@@ -18360,13 +18360,13 @@
         <v>47</v>
       </c>
       <c r="O281" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="P281" t="s">
-        <v>503</v>
+        <v>34</v>
       </c>
       <c r="Q281" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R281" t="s">
         <v>34</v>
@@ -18386,25 +18386,25 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F282" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
       </c>
       <c r="H282" t="s">
-        <v>569</v>
+        <v>192</v>
       </c>
       <c r="I282" t="s">
-        <v>583</v>
+        <v>489</v>
       </c>
       <c r="J282" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="K282" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="L282" t="s">
         <v>34</v>
@@ -18416,13 +18416,13 @@
         <v>47</v>
       </c>
       <c r="O282" t="s">
-        <v>584</v>
+        <v>34</v>
       </c>
       <c r="P282" t="s">
-        <v>583</v>
+        <v>34</v>
       </c>
       <c r="Q282" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R282" t="s">
         <v>34</v>
@@ -18442,25 +18442,25 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="F283" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
       <c r="G283" t="s">
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="I283" t="s">
-        <v>585</v>
+        <v>501</v>
       </c>
       <c r="J283" t="s">
-        <v>182</v>
+        <v>73</v>
       </c>
       <c r="K283" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L283" t="s">
         <v>34</v>
@@ -18472,13 +18472,13 @@
         <v>47</v>
       </c>
       <c r="O283" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="P283" t="s">
-        <v>585</v>
+        <v>34</v>
       </c>
       <c r="Q283" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R283" t="s">
         <v>34</v>
@@ -18498,25 +18498,25 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>256</v>
+        <v>584</v>
       </c>
       <c r="F284" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
       <c r="G284" t="s">
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>570</v>
+        <v>192</v>
       </c>
       <c r="I284" t="s">
-        <v>500</v>
+        <v>585</v>
       </c>
       <c r="J284" t="s">
-        <v>578</v>
+        <v>78</v>
       </c>
       <c r="K284" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L284" t="s">
         <v>34</v>
@@ -18528,13 +18528,13 @@
         <v>47</v>
       </c>
       <c r="O284" t="s">
-        <v>412</v>
+        <v>34</v>
       </c>
       <c r="P284" t="s">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="Q284" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R284" t="s">
         <v>34</v>
@@ -18563,7 +18563,7 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I285" t="s">
         <v>588</v>
@@ -18619,7 +18619,7 @@
         <v>41</v>
       </c>
       <c r="H286" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I286" t="s">
         <v>589</v>
@@ -18675,7 +18675,7 @@
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I287" t="s">
         <v>590</v>
@@ -18731,7 +18731,7 @@
         <v>41</v>
       </c>
       <c r="H288" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I288" t="s">
         <v>591</v>
@@ -18834,7 +18834,7 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>473</v>
+        <v>405</v>
       </c>
       <c r="F290" t="s">
         <v>208</v>
@@ -19114,7 +19114,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="F295" t="s">
         <v>208</v>
@@ -19170,7 +19170,7 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="F296" t="s">
         <v>208</v>
@@ -19312,7 +19312,7 @@
         <v>47</v>
       </c>
       <c r="O298" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="P298" t="s">
         <v>608</v>
@@ -19403,7 +19403,7 @@
         <v>41</v>
       </c>
       <c r="H300" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I300" t="s">
         <v>612</v>
@@ -19536,7 +19536,7 @@
         <v>47</v>
       </c>
       <c r="O302" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="P302" t="s">
         <v>608</v>
@@ -20246,7 +20246,7 @@
         <v>638</v>
       </c>
       <c r="I315" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="J315" t="s">
         <v>105</v>
@@ -20267,7 +20267,7 @@
         <v>112</v>
       </c>
       <c r="P315" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="Q315" t="s">
         <v>47</v>
@@ -20290,7 +20290,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>473</v>
+        <v>405</v>
       </c>
       <c r="F316" t="s">
         <v>208</v>
@@ -20402,7 +20402,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="F318" t="s">
         <v>208</v>
@@ -20529,7 +20529,7 @@
         <v>650</v>
       </c>
       <c r="J320" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K320" t="s">
         <v>73</v>
@@ -20585,7 +20585,7 @@
         <v>651</v>
       </c>
       <c r="J321" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K321" t="s">
         <v>105</v>
@@ -20962,7 +20962,7 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="F328" t="s">
         <v>208</v>
@@ -21970,7 +21970,7 @@
         <v>33</v>
       </c>
       <c r="E346" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F346" t="s">
         <v>40</v>
@@ -21985,10 +21985,10 @@
         <v>92</v>
       </c>
       <c r="J346" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="K346" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="L346" t="s">
         <v>34</v>
@@ -22000,7 +22000,7 @@
         <v>47</v>
       </c>
       <c r="O346" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="P346" t="s">
         <v>92</v>
@@ -22026,7 +22026,7 @@
         <v>34</v>
       </c>
       <c r="E347" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="F347" t="s">
         <v>40</v>
@@ -22056,7 +22056,7 @@
         <v>47</v>
       </c>
       <c r="O347" t="s">
-        <v>294</v>
+        <v>115</v>
       </c>
       <c r="P347" t="s">
         <v>92</v>
@@ -22138,10 +22138,10 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>250</v>
+        <v>531</v>
       </c>
       <c r="F349" t="s">
-        <v>40</v>
+        <v>709</v>
       </c>
       <c r="G349" t="s">
         <v>41</v>
@@ -22153,10 +22153,10 @@
         <v>92</v>
       </c>
       <c r="J349" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="K349" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="L349" t="s">
         <v>34</v>
@@ -22168,13 +22168,13 @@
         <v>47</v>
       </c>
       <c r="O349" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="P349" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="Q349" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R349" t="s">
         <v>34</v>
@@ -22194,7 +22194,7 @@
         <v>34</v>
       </c>
       <c r="E350" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="F350" t="s">
         <v>40</v>
@@ -22209,10 +22209,10 @@
         <v>92</v>
       </c>
       <c r="J350" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K350" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L350" t="s">
         <v>34</v>
@@ -22224,7 +22224,7 @@
         <v>47</v>
       </c>
       <c r="O350" t="s">
-        <v>169</v>
+        <v>294</v>
       </c>
       <c r="P350" t="s">
         <v>92</v>
@@ -22250,7 +22250,7 @@
         <v>34</v>
       </c>
       <c r="E351" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F351" t="s">
         <v>40</v>
@@ -22265,10 +22265,10 @@
         <v>92</v>
       </c>
       <c r="J351" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="K351" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L351" t="s">
         <v>34</v>
@@ -22280,7 +22280,7 @@
         <v>47</v>
       </c>
       <c r="O351" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="P351" t="s">
         <v>92</v>
@@ -22306,7 +22306,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="F352" t="s">
         <v>40</v>
@@ -22321,10 +22321,10 @@
         <v>92</v>
       </c>
       <c r="J352" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="K352" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L352" t="s">
         <v>34</v>
@@ -22336,7 +22336,7 @@
         <v>47</v>
       </c>
       <c r="O352" t="s">
-        <v>88</v>
+        <v>269</v>
       </c>
       <c r="P352" t="s">
         <v>92</v>
@@ -22418,7 +22418,7 @@
         <v>34</v>
       </c>
       <c r="E354" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="F354" t="s">
         <v>40</v>
@@ -22433,10 +22433,10 @@
         <v>92</v>
       </c>
       <c r="J354" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K354" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L354" t="s">
         <v>34</v>
@@ -22448,7 +22448,7 @@
         <v>47</v>
       </c>
       <c r="O354" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="P354" t="s">
         <v>92</v>
@@ -22474,10 +22474,10 @@
         <v>34</v>
       </c>
       <c r="E355" t="s">
-        <v>531</v>
+        <v>272</v>
       </c>
       <c r="F355" t="s">
-        <v>709</v>
+        <v>40</v>
       </c>
       <c r="G355" t="s">
         <v>41</v>
@@ -22489,10 +22489,10 @@
         <v>92</v>
       </c>
       <c r="J355" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K355" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="L355" t="s">
         <v>34</v>
@@ -22504,13 +22504,13 @@
         <v>47</v>
       </c>
       <c r="O355" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="P355" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="Q355" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R355" t="s">
         <v>34</v>
@@ -22530,7 +22530,7 @@
         <v>34</v>
       </c>
       <c r="E356" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F356" t="s">
         <v>40</v>
@@ -22545,10 +22545,10 @@
         <v>92</v>
       </c>
       <c r="J356" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K356" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="L356" t="s">
         <v>34</v>
@@ -22560,7 +22560,7 @@
         <v>47</v>
       </c>
       <c r="O356" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="P356" t="s">
         <v>92</v>
@@ -22642,7 +22642,7 @@
         <v>34</v>
       </c>
       <c r="E358" t="s">
-        <v>260</v>
+        <v>487</v>
       </c>
       <c r="F358" t="s">
         <v>40</v>
@@ -22657,10 +22657,10 @@
         <v>92</v>
       </c>
       <c r="J358" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K358" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="L358" t="s">
         <v>34</v>
@@ -22672,7 +22672,7 @@
         <v>47</v>
       </c>
       <c r="O358" t="s">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="P358" t="s">
         <v>92</v>
@@ -22698,7 +22698,7 @@
         <v>34</v>
       </c>
       <c r="E359" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="F359" t="s">
         <v>40</v>
@@ -22713,10 +22713,10 @@
         <v>92</v>
       </c>
       <c r="J359" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="K359" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="L359" t="s">
         <v>34</v>
@@ -22728,7 +22728,7 @@
         <v>47</v>
       </c>
       <c r="O359" t="s">
-        <v>269</v>
+        <v>98</v>
       </c>
       <c r="P359" t="s">
         <v>92</v>
@@ -22754,7 +22754,7 @@
         <v>34</v>
       </c>
       <c r="E360" t="s">
-        <v>487</v>
+        <v>260</v>
       </c>
       <c r="F360" t="s">
         <v>40</v>
@@ -22769,10 +22769,10 @@
         <v>92</v>
       </c>
       <c r="J360" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K360" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="L360" t="s">
         <v>34</v>
@@ -22784,7 +22784,7 @@
         <v>47</v>
       </c>
       <c r="O360" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="P360" t="s">
         <v>92</v>
@@ -22922,7 +22922,7 @@
         <v>33</v>
       </c>
       <c r="E363" t="s">
-        <v>720</v>
+        <v>227</v>
       </c>
       <c r="F363" t="s">
         <v>40</v>
@@ -22931,16 +22931,16 @@
         <v>41</v>
       </c>
       <c r="H363" t="s">
+        <v>720</v>
+      </c>
+      <c r="I363" t="s">
         <v>721</v>
       </c>
-      <c r="I363" t="s">
+      <c r="J363" t="s">
         <v>722</v>
       </c>
-      <c r="J363" t="s">
-        <v>329</v>
-      </c>
       <c r="K363" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="L363" t="s">
         <v>723</v>
@@ -22955,7 +22955,7 @@
         <v>48</v>
       </c>
       <c r="P363" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="Q363" t="s">
         <v>47</v>
@@ -22978,7 +22978,7 @@
         <v>34</v>
       </c>
       <c r="E364" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F364" t="s">
         <v>40</v>
@@ -22987,19 +22987,19 @@
         <v>41</v>
       </c>
       <c r="H364" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I364" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J364" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K364" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L364" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M364" t="s">
         <v>718</v>
@@ -23011,7 +23011,7 @@
         <v>48</v>
       </c>
       <c r="P364" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="Q364" t="s">
         <v>47</v>
@@ -23034,7 +23034,7 @@
         <v>34</v>
       </c>
       <c r="E365" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="F365" t="s">
         <v>40</v>
@@ -23049,13 +23049,13 @@
         <v>731</v>
       </c>
       <c r="J365" t="s">
-        <v>230</v>
+        <v>369</v>
       </c>
       <c r="K365" t="s">
+        <v>45</v>
+      </c>
+      <c r="L365" t="s">
         <v>732</v>
-      </c>
-      <c r="L365" t="s">
-        <v>733</v>
       </c>
       <c r="M365" t="s">
         <v>718</v>
@@ -23090,7 +23090,7 @@
         <v>34</v>
       </c>
       <c r="E366" t="s">
-        <v>227</v>
+        <v>733</v>
       </c>
       <c r="F366" t="s">
         <v>40</v>
@@ -23105,10 +23105,10 @@
         <v>735</v>
       </c>
       <c r="J366" t="s">
+        <v>230</v>
+      </c>
+      <c r="K366" t="s">
         <v>736</v>
-      </c>
-      <c r="K366" t="s">
-        <v>67</v>
       </c>
       <c r="L366" t="s">
         <v>737</v>
@@ -23370,7 +23370,7 @@
         <v>33</v>
       </c>
       <c r="E371" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F371" t="s">
         <v>40</v>
@@ -23385,7 +23385,7 @@
         <v>750</v>
       </c>
       <c r="J371" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K371" t="s">
         <v>45</v>
@@ -23538,28 +23538,28 @@
         <v>33</v>
       </c>
       <c r="E374" t="s">
-        <v>720</v>
+        <v>757</v>
       </c>
       <c r="F374" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G374" t="s">
         <v>41</v>
       </c>
       <c r="H374" t="s">
-        <v>757</v>
+        <v>572</v>
       </c>
       <c r="I374" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="J374" t="s">
-        <v>329</v>
+        <v>530</v>
       </c>
       <c r="K374" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="L374" t="s">
-        <v>759</v>
+        <v>34</v>
       </c>
       <c r="M374" t="s">
         <v>756</v>
@@ -23571,7 +23571,7 @@
         <v>48</v>
       </c>
       <c r="P374" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="Q374" t="s">
         <v>47</v>
@@ -23594,7 +23594,7 @@
         <v>34</v>
       </c>
       <c r="E375" t="s">
-        <v>720</v>
+        <v>733</v>
       </c>
       <c r="F375" t="s">
         <v>40</v>
@@ -23603,19 +23603,19 @@
         <v>41</v>
       </c>
       <c r="H375" t="s">
-        <v>760</v>
+        <v>485</v>
       </c>
       <c r="I375" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="J375" t="s">
-        <v>726</v>
+        <v>67</v>
       </c>
       <c r="K375" t="s">
         <v>45</v>
       </c>
       <c r="L375" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="M375" t="s">
         <v>756</v>
@@ -23627,7 +23627,7 @@
         <v>48</v>
       </c>
       <c r="P375" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="Q375" t="s">
         <v>47</v>
@@ -23650,7 +23650,7 @@
         <v>34</v>
       </c>
       <c r="E376" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F376" t="s">
         <v>40</v>
@@ -23659,19 +23659,19 @@
         <v>41</v>
       </c>
       <c r="H376" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="I376" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="J376" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K376" t="s">
         <v>45</v>
       </c>
       <c r="L376" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="M376" t="s">
         <v>756</v>
@@ -23683,7 +23683,7 @@
         <v>48</v>
       </c>
       <c r="P376" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="Q376" t="s">
         <v>47</v>
@@ -23706,7 +23706,7 @@
         <v>34</v>
       </c>
       <c r="E377" t="s">
-        <v>227</v>
+        <v>724</v>
       </c>
       <c r="F377" t="s">
         <v>40</v>
@@ -23715,19 +23715,19 @@
         <v>41</v>
       </c>
       <c r="H377" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="I377" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="J377" t="s">
-        <v>767</v>
+        <v>727</v>
       </c>
       <c r="K377" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="L377" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="M377" t="s">
         <v>756</v>
@@ -23739,7 +23739,7 @@
         <v>48</v>
       </c>
       <c r="P377" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="Q377" t="s">
         <v>47</v>
@@ -23762,7 +23762,7 @@
         <v>34</v>
       </c>
       <c r="E378" t="s">
-        <v>720</v>
+        <v>227</v>
       </c>
       <c r="F378" t="s">
         <v>40</v>
@@ -23771,19 +23771,19 @@
         <v>41</v>
       </c>
       <c r="H378" t="s">
-        <v>769</v>
+        <v>508</v>
       </c>
       <c r="I378" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="J378" t="s">
-        <v>726</v>
+        <v>766</v>
       </c>
       <c r="K378" t="s">
         <v>45</v>
       </c>
       <c r="L378" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="M378" t="s">
         <v>756</v>
@@ -23795,7 +23795,7 @@
         <v>48</v>
       </c>
       <c r="P378" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="Q378" t="s">
         <v>47</v>
@@ -23818,7 +23818,7 @@
         <v>34</v>
       </c>
       <c r="E379" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F379" t="s">
         <v>40</v>
@@ -23827,19 +23827,19 @@
         <v>41</v>
       </c>
       <c r="H379" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="I379" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="J379" t="s">
-        <v>726</v>
+        <v>369</v>
       </c>
       <c r="K379" t="s">
         <v>45</v>
       </c>
       <c r="L379" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="M379" t="s">
         <v>756</v>
@@ -23851,7 +23851,7 @@
         <v>48</v>
       </c>
       <c r="P379" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="Q379" t="s">
         <v>47</v>
@@ -23883,19 +23883,19 @@
         <v>41</v>
       </c>
       <c r="H380" t="s">
-        <v>508</v>
+        <v>565</v>
       </c>
       <c r="I380" t="s">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="J380" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="K380" t="s">
         <v>45</v>
       </c>
       <c r="L380" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="M380" t="s">
         <v>756</v>
@@ -23907,7 +23907,7 @@
         <v>48</v>
       </c>
       <c r="P380" t="s">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="Q380" t="s">
         <v>47</v>
@@ -23930,7 +23930,7 @@
         <v>34</v>
       </c>
       <c r="E381" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F381" t="s">
         <v>40</v>
@@ -23939,19 +23939,19 @@
         <v>41</v>
       </c>
       <c r="H381" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="I381" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="J381" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K381" t="s">
         <v>45</v>
       </c>
       <c r="L381" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="M381" t="s">
         <v>756</v>
@@ -23963,7 +23963,7 @@
         <v>48</v>
       </c>
       <c r="P381" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="Q381" t="s">
         <v>47</v>
@@ -23986,7 +23986,7 @@
         <v>34</v>
       </c>
       <c r="E382" t="s">
-        <v>227</v>
+        <v>724</v>
       </c>
       <c r="F382" t="s">
         <v>40</v>
@@ -23995,19 +23995,19 @@
         <v>41</v>
       </c>
       <c r="H382" t="s">
-        <v>569</v>
+        <v>776</v>
       </c>
       <c r="I382" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="J382" t="s">
-        <v>780</v>
+        <v>727</v>
       </c>
       <c r="K382" t="s">
         <v>45</v>
       </c>
       <c r="L382" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="M382" t="s">
         <v>756</v>
@@ -24019,7 +24019,7 @@
         <v>48</v>
       </c>
       <c r="P382" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="Q382" t="s">
         <v>47</v>
@@ -24042,7 +24042,7 @@
         <v>34</v>
       </c>
       <c r="E383" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F383" t="s">
         <v>40</v>
@@ -24051,19 +24051,19 @@
         <v>41</v>
       </c>
       <c r="H383" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="I383" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="J383" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K383" t="s">
         <v>45</v>
       </c>
       <c r="L383" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="M383" t="s">
         <v>756</v>
@@ -24075,7 +24075,7 @@
         <v>48</v>
       </c>
       <c r="P383" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="Q383" t="s">
         <v>47</v>
@@ -24098,7 +24098,7 @@
         <v>34</v>
       </c>
       <c r="E384" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="F384" t="s">
         <v>40</v>
@@ -24107,19 +24107,19 @@
         <v>41</v>
       </c>
       <c r="H384" t="s">
-        <v>485</v>
+        <v>782</v>
       </c>
       <c r="I384" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="J384" t="s">
-        <v>67</v>
+        <v>727</v>
       </c>
       <c r="K384" t="s">
         <v>45</v>
       </c>
       <c r="L384" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="M384" t="s">
         <v>756</v>
@@ -24131,7 +24131,7 @@
         <v>48</v>
       </c>
       <c r="P384" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="Q384" t="s">
         <v>47</v>
@@ -24154,28 +24154,28 @@
         <v>34</v>
       </c>
       <c r="E385" t="s">
+        <v>227</v>
+      </c>
+      <c r="F385" t="s">
+        <v>40</v>
+      </c>
+      <c r="G385" t="s">
+        <v>41</v>
+      </c>
+      <c r="H385" t="s">
+        <v>785</v>
+      </c>
+      <c r="I385" t="s">
+        <v>786</v>
+      </c>
+      <c r="J385" t="s">
+        <v>766</v>
+      </c>
+      <c r="K385" t="s">
+        <v>120</v>
+      </c>
+      <c r="L385" t="s">
         <v>787</v>
-      </c>
-      <c r="F385" t="s">
-        <v>208</v>
-      </c>
-      <c r="G385" t="s">
-        <v>41</v>
-      </c>
-      <c r="H385" t="s">
-        <v>570</v>
-      </c>
-      <c r="I385" t="s">
-        <v>750</v>
-      </c>
-      <c r="J385" t="s">
-        <v>530</v>
-      </c>
-      <c r="K385" t="s">
-        <v>159</v>
-      </c>
-      <c r="L385" t="s">
-        <v>34</v>
       </c>
       <c r="M385" t="s">
         <v>756</v>
@@ -24187,7 +24187,7 @@
         <v>48</v>
       </c>
       <c r="P385" t="s">
-        <v>750</v>
+        <v>786</v>
       </c>
       <c r="Q385" t="s">
         <v>47</v>
@@ -24611,7 +24611,7 @@
         <v>41</v>
       </c>
       <c r="H393" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I393" t="s">
         <v>805</v>
@@ -24841,7 +24841,7 @@
         <v>814</v>
       </c>
       <c r="J397" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
       <c r="K397" t="s">
         <v>68</v>
@@ -25009,10 +25009,10 @@
         <v>823</v>
       </c>
       <c r="J400" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K400" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L400" t="s">
         <v>824</v>
@@ -25274,7 +25274,7 @@
         <v>33</v>
       </c>
       <c r="E405" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F405" t="s">
         <v>40</v>
@@ -25289,7 +25289,7 @@
         <v>843</v>
       </c>
       <c r="J405" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K405" t="s">
         <v>45</v>
@@ -25442,7 +25442,7 @@
         <v>33</v>
       </c>
       <c r="E408" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F408" t="s">
         <v>40</v>
@@ -25457,7 +25457,7 @@
         <v>855</v>
       </c>
       <c r="J408" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K408" t="s">
         <v>320</v>
@@ -25569,10 +25569,10 @@
         <v>861</v>
       </c>
       <c r="J410" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K410" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L410" t="s">
         <v>862</v>
@@ -25684,10 +25684,10 @@
         <v>179</v>
       </c>
       <c r="K412" t="s">
-        <v>293</v>
+        <v>664</v>
       </c>
       <c r="L412" t="s">
-        <v>34</v>
+        <v>869</v>
       </c>
       <c r="M412" t="s">
         <v>865</v>
@@ -25722,7 +25722,7 @@
         <v>34</v>
       </c>
       <c r="E413" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F413" t="s">
         <v>208</v>
@@ -25731,16 +25731,16 @@
         <v>41</v>
       </c>
       <c r="H413" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="I413" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="J413" t="s">
         <v>179</v>
       </c>
       <c r="K413" t="s">
-        <v>109</v>
+        <v>293</v>
       </c>
       <c r="L413" t="s">
         <v>34</v>
@@ -25755,7 +25755,7 @@
         <v>48</v>
       </c>
       <c r="P413" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="Q413" t="s">
         <v>47</v>
@@ -25778,7 +25778,7 @@
         <v>34</v>
       </c>
       <c r="E414" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F414" t="s">
         <v>208</v>
@@ -25787,19 +25787,19 @@
         <v>41</v>
       </c>
       <c r="H414" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="I414" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="J414" t="s">
         <v>179</v>
       </c>
       <c r="K414" t="s">
-        <v>664</v>
+        <v>109</v>
       </c>
       <c r="L414" t="s">
-        <v>875</v>
+        <v>34</v>
       </c>
       <c r="M414" t="s">
         <v>865</v>
@@ -25811,7 +25811,7 @@
         <v>48</v>
       </c>
       <c r="P414" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="Q414" t="s">
         <v>47</v>
@@ -26002,7 +26002,7 @@
         <v>33</v>
       </c>
       <c r="E418" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F418" t="s">
         <v>40</v>
@@ -26017,7 +26017,7 @@
         <v>888</v>
       </c>
       <c r="J418" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K418" t="s">
         <v>45</v>
@@ -26229,25 +26229,25 @@
         <v>903</v>
       </c>
       <c r="F422" t="s">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="G422" t="s">
         <v>41</v>
       </c>
       <c r="H422" t="s">
+        <v>898</v>
+      </c>
+      <c r="I422" t="s">
         <v>904</v>
       </c>
-      <c r="I422" t="s">
+      <c r="J422" t="s">
+        <v>373</v>
+      </c>
+      <c r="K422" t="s">
+        <v>45</v>
+      </c>
+      <c r="L422" t="s">
         <v>905</v>
-      </c>
-      <c r="J422" t="s">
-        <v>179</v>
-      </c>
-      <c r="K422" t="s">
-        <v>293</v>
-      </c>
-      <c r="L422" t="s">
-        <v>34</v>
       </c>
       <c r="M422" t="s">
         <v>902</v>
@@ -26259,7 +26259,7 @@
         <v>48</v>
       </c>
       <c r="P422" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="Q422" t="s">
         <v>47</v>
@@ -26282,7 +26282,7 @@
         <v>34</v>
       </c>
       <c r="E423" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F423" t="s">
         <v>40</v>
@@ -26291,19 +26291,19 @@
         <v>41</v>
       </c>
       <c r="H423" t="s">
+        <v>898</v>
+      </c>
+      <c r="I423" t="s">
         <v>906</v>
       </c>
-      <c r="I423" t="s">
+      <c r="J423" t="s">
+        <v>369</v>
+      </c>
+      <c r="K423" t="s">
+        <v>674</v>
+      </c>
+      <c r="L423" t="s">
         <v>907</v>
-      </c>
-      <c r="J423" t="s">
-        <v>329</v>
-      </c>
-      <c r="K423" t="s">
-        <v>45</v>
-      </c>
-      <c r="L423" t="s">
-        <v>908</v>
       </c>
       <c r="M423" t="s">
         <v>902</v>
@@ -26315,7 +26315,7 @@
         <v>48</v>
       </c>
       <c r="P423" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="Q423" t="s">
         <v>47</v>
@@ -26338,28 +26338,28 @@
         <v>34</v>
       </c>
       <c r="E424" t="s">
-        <v>720</v>
+        <v>908</v>
       </c>
       <c r="F424" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G424" t="s">
         <v>41</v>
       </c>
       <c r="H424" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="I424" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="J424" t="s">
-        <v>329</v>
+        <v>179</v>
       </c>
       <c r="K424" t="s">
-        <v>674</v>
+        <v>293</v>
       </c>
       <c r="L424" t="s">
-        <v>910</v>
+        <v>34</v>
       </c>
       <c r="M424" t="s">
         <v>902</v>
@@ -26371,7 +26371,7 @@
         <v>48</v>
       </c>
       <c r="P424" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="Q424" t="s">
         <v>47</v>
@@ -26394,7 +26394,7 @@
         <v>34</v>
       </c>
       <c r="E425" t="s">
-        <v>911</v>
+        <v>724</v>
       </c>
       <c r="F425" t="s">
         <v>40</v>
@@ -26403,13 +26403,13 @@
         <v>41</v>
       </c>
       <c r="H425" t="s">
-        <v>898</v>
+        <v>911</v>
       </c>
       <c r="I425" t="s">
         <v>912</v>
       </c>
       <c r="J425" t="s">
-        <v>325</v>
+        <v>369</v>
       </c>
       <c r="K425" t="s">
         <v>45</v>
@@ -26618,7 +26618,7 @@
         <v>33</v>
       </c>
       <c r="E429" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F429" t="s">
         <v>40</v>
@@ -26633,7 +26633,7 @@
         <v>925</v>
       </c>
       <c r="J429" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K429" t="s">
         <v>45</v>
@@ -26786,7 +26786,7 @@
         <v>33</v>
       </c>
       <c r="E432" t="s">
-        <v>821</v>
+        <v>724</v>
       </c>
       <c r="F432" t="s">
         <v>40</v>
@@ -26801,10 +26801,10 @@
         <v>937</v>
       </c>
       <c r="J432" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="K432" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="L432" t="s">
         <v>938</v>
@@ -26842,7 +26842,7 @@
         <v>34</v>
       </c>
       <c r="E433" t="s">
-        <v>720</v>
+        <v>821</v>
       </c>
       <c r="F433" t="s">
         <v>40</v>
@@ -26857,10 +26857,10 @@
         <v>940</v>
       </c>
       <c r="J433" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="K433" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="L433" t="s">
         <v>941</v>
@@ -26913,7 +26913,7 @@
         <v>945</v>
       </c>
       <c r="J434" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="K434" t="s">
         <v>45</v>
@@ -27066,7 +27066,7 @@
         <v>33</v>
       </c>
       <c r="E437" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="F437" t="s">
         <v>40</v>
@@ -27570,7 +27570,7 @@
         <v>34</v>
       </c>
       <c r="E446" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F446" t="s">
         <v>247</v>
@@ -27585,10 +27585,10 @@
         <v>970</v>
       </c>
       <c r="J446" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="K446" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L446" t="s">
         <v>969</v>
@@ -27600,7 +27600,7 @@
         <v>47</v>
       </c>
       <c r="O446" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="P446" t="s">
         <v>970</v>
@@ -27626,7 +27626,7 @@
         <v>34</v>
       </c>
       <c r="E447" t="s">
-        <v>518</v>
+        <v>254</v>
       </c>
       <c r="F447" t="s">
         <v>247</v>
@@ -27635,16 +27635,16 @@
         <v>41</v>
       </c>
       <c r="H447" t="s">
+        <v>967</v>
+      </c>
+      <c r="I447" t="s">
         <v>971</v>
       </c>
-      <c r="I447" t="s">
-        <v>972</v>
-      </c>
       <c r="J447" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K447" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L447" t="s">
         <v>969</v>
@@ -27656,10 +27656,10 @@
         <v>47</v>
       </c>
       <c r="O447" t="s">
-        <v>521</v>
+        <v>98</v>
       </c>
       <c r="P447" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="Q447" t="s">
         <v>47</v>
@@ -27682,7 +27682,7 @@
         <v>34</v>
       </c>
       <c r="E448" t="s">
-        <v>267</v>
+        <v>518</v>
       </c>
       <c r="F448" t="s">
         <v>247</v>
@@ -27691,16 +27691,16 @@
         <v>41</v>
       </c>
       <c r="H448" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="I448" t="s">
         <v>973</v>
       </c>
       <c r="J448" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="K448" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="L448" t="s">
         <v>969</v>
@@ -27712,7 +27712,7 @@
         <v>47</v>
       </c>
       <c r="O448" t="s">
-        <v>269</v>
+        <v>521</v>
       </c>
       <c r="P448" t="s">
         <v>973</v>
@@ -27738,7 +27738,7 @@
         <v>34</v>
       </c>
       <c r="E449" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F449" t="s">
         <v>247</v>
@@ -27768,7 +27768,7 @@
         <v>47</v>
       </c>
       <c r="O449" t="s">
-        <v>149</v>
+        <v>269</v>
       </c>
       <c r="P449" t="s">
         <v>974</v>
@@ -27794,7 +27794,7 @@
         <v>34</v>
       </c>
       <c r="E450" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="F450" t="s">
         <v>247</v>
@@ -27809,10 +27809,10 @@
         <v>975</v>
       </c>
       <c r="J450" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="K450" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="L450" t="s">
         <v>969</v>
@@ -27824,7 +27824,7 @@
         <v>47</v>
       </c>
       <c r="O450" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="P450" t="s">
         <v>975</v>
@@ -27850,7 +27850,7 @@
         <v>34</v>
       </c>
       <c r="E451" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="F451" t="s">
         <v>247</v>
@@ -27865,10 +27865,10 @@
         <v>976</v>
       </c>
       <c r="J451" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="K451" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="L451" t="s">
         <v>969</v>
@@ -27880,7 +27880,7 @@
         <v>47</v>
       </c>
       <c r="O451" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="P451" t="s">
         <v>976</v>
@@ -27906,7 +27906,7 @@
         <v>34</v>
       </c>
       <c r="E452" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="F452" t="s">
         <v>247</v>
@@ -27921,10 +27921,10 @@
         <v>977</v>
       </c>
       <c r="J452" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="K452" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="L452" t="s">
         <v>969</v>
@@ -27936,7 +27936,7 @@
         <v>47</v>
       </c>
       <c r="O452" t="s">
-        <v>412</v>
+        <v>152</v>
       </c>
       <c r="P452" t="s">
         <v>977</v>
@@ -27962,7 +27962,7 @@
         <v>34</v>
       </c>
       <c r="E453" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F453" t="s">
         <v>247</v>
@@ -27971,10 +27971,10 @@
         <v>41</v>
       </c>
       <c r="H453" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="I453" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J453" t="s">
         <v>73</v>
@@ -27992,10 +27992,10 @@
         <v>47</v>
       </c>
       <c r="O453" t="s">
-        <v>294</v>
+        <v>385</v>
       </c>
       <c r="P453" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="Q453" t="s">
         <v>47</v>
@@ -28018,7 +28018,7 @@
         <v>34</v>
       </c>
       <c r="E454" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="F454" t="s">
         <v>247</v>
@@ -28027,10 +28027,10 @@
         <v>41</v>
       </c>
       <c r="H454" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="I454" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="J454" t="s">
         <v>73</v>
@@ -28048,10 +28048,10 @@
         <v>47</v>
       </c>
       <c r="O454" t="s">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="P454" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="Q454" t="s">
         <v>47</v>
@@ -28074,7 +28074,7 @@
         <v>34</v>
       </c>
       <c r="E455" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F455" t="s">
         <v>247</v>
@@ -28086,13 +28086,13 @@
         <v>967</v>
       </c>
       <c r="I455" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="J455" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K455" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L455" t="s">
         <v>969</v>
@@ -28104,10 +28104,10 @@
         <v>47</v>
       </c>
       <c r="O455" t="s">
-        <v>262</v>
+        <v>330</v>
       </c>
       <c r="P455" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="Q455" t="s">
         <v>47</v>
@@ -28130,7 +28130,7 @@
         <v>34</v>
       </c>
       <c r="E456" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F456" t="s">
         <v>247</v>
@@ -28142,13 +28142,13 @@
         <v>967</v>
       </c>
       <c r="I456" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="J456" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K456" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L456" t="s">
         <v>969</v>
@@ -28160,10 +28160,10 @@
         <v>47</v>
       </c>
       <c r="O456" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
       <c r="P456" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="Q456" t="s">
         <v>47</v>
@@ -28186,7 +28186,7 @@
         <v>34</v>
       </c>
       <c r="E457" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F457" t="s">
         <v>247</v>
@@ -28198,13 +28198,13 @@
         <v>967</v>
       </c>
       <c r="I457" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="J457" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="K457" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="L457" t="s">
         <v>969</v>
@@ -28216,10 +28216,10 @@
         <v>47</v>
       </c>
       <c r="O457" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="P457" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="Q457" t="s">
         <v>47</v>
@@ -28242,7 +28242,7 @@
         <v>34</v>
       </c>
       <c r="E458" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F458" t="s">
         <v>247</v>
@@ -28254,13 +28254,13 @@
         <v>967</v>
       </c>
       <c r="I458" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="J458" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="K458" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="L458" t="s">
         <v>969</v>
@@ -28272,10 +28272,10 @@
         <v>47</v>
       </c>
       <c r="O458" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="P458" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="Q458" t="s">
         <v>47</v>

--- a/xlsx/dre/DRE_03_2026.xlsx
+++ b/xlsx/dre/DRE_03_2026.xlsx
@@ -588,21 +588,6 @@
     <t>R$  4.689,29</t>
   </si>
   <si>
-    <t>12/1</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>R$  736,71</t>
-  </si>
-  <si>
-    <t>23/04/26</t>
-  </si>
-  <si>
-    <t>Digisac</t>
-  </si>
-  <si>
     <t>5/1</t>
   </si>
   <si>
@@ -614,6 +599,21 @@
   <si>
     <t xml:space="preserve">Reembolso Pushing
 </t>
+  </si>
+  <si>
+    <t>12/1</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>R$  736,71</t>
+  </si>
+  <si>
+    <t>23/04/26</t>
+  </si>
+  <si>
+    <t>Digisac</t>
   </si>
   <si>
     <t>9/1</t>
@@ -1172,15 +1172,87 @@
     <t>4.02.02.01.01 Fretes sobre compra de mercadorias da marca - provisão</t>
   </si>
   <si>
+    <t>ENTREGADORA NOVO RUMO LTDA ME</t>
+  </si>
+  <si>
+    <t>R$  141,50</t>
+  </si>
+  <si>
+    <t>68501AMILTONF</t>
+  </si>
+  <si>
+    <t>63301n/0</t>
+  </si>
+  <si>
+    <t>R$  243,97</t>
+  </si>
+  <si>
+    <t>RODAG TRANSPORTES LTDA*</t>
+  </si>
+  <si>
+    <t>R$  11,98</t>
+  </si>
+  <si>
+    <t>R$  11,18</t>
+  </si>
+  <si>
+    <t>66301-/0</t>
+  </si>
+  <si>
+    <t>R$  101,41</t>
+  </si>
+  <si>
+    <t>67501-/0</t>
+  </si>
+  <si>
+    <t>R$  95,00</t>
+  </si>
+  <si>
+    <t>70601-/0</t>
+  </si>
+  <si>
+    <t>66301n/0</t>
+  </si>
+  <si>
+    <t>64801n/0</t>
+  </si>
+  <si>
+    <t>R$  190,00</t>
+  </si>
+  <si>
+    <t>R$  50,00</t>
+  </si>
+  <si>
+    <t>R$  98,75</t>
+  </si>
+  <si>
+    <t>64801R/0</t>
+  </si>
+  <si>
+    <t>R$  12,95</t>
+  </si>
+  <si>
+    <t>64801N/0</t>
+  </si>
+  <si>
+    <t>R$  12,09</t>
+  </si>
+  <si>
+    <t>63701/0</t>
+  </si>
+  <si>
+    <t>R$  14,09</t>
+  </si>
+  <si>
+    <t>R$  15,09</t>
+  </si>
+  <si>
     <t>67301/2</t>
   </si>
   <si>
     <t>PCP</t>
   </si>
   <si>
-    <t>ENTREGADORA NOVO RUMO LTDA ME</t>
-  </si>
-  <si>
     <t>R$  758,85</t>
   </si>
   <si>
@@ -1190,9 +1262,6 @@
     <t>67301/3</t>
   </si>
   <si>
-    <t>RODAG TRANSPORTES LTDA*</t>
-  </si>
-  <si>
     <t>R$  773,11</t>
   </si>
   <si>
@@ -1259,9 +1328,6 @@
     <t>R$  1.680,23</t>
   </si>
   <si>
-    <t>68501AMILTONF</t>
-  </si>
-  <si>
     <t>66301/2</t>
   </si>
   <si>
@@ -1358,9 +1424,6 @@
     <t>R$  264,04</t>
   </si>
   <si>
-    <t>67501-/0</t>
-  </si>
-  <si>
     <t>R$  136,00</t>
   </si>
   <si>
@@ -1373,9 +1436,6 @@
     <t>R$  33,33</t>
   </si>
   <si>
-    <t>R$  50,00</t>
-  </si>
-  <si>
     <t>R$  30,00</t>
   </si>
   <si>
@@ -1389,66 +1449,6 @@
   </si>
   <si>
     <t>R$  11,45</t>
-  </si>
-  <si>
-    <t>R$  141,50</t>
-  </si>
-  <si>
-    <t>63301n/0</t>
-  </si>
-  <si>
-    <t>R$  243,97</t>
-  </si>
-  <si>
-    <t>R$  11,98</t>
-  </si>
-  <si>
-    <t>R$  11,18</t>
-  </si>
-  <si>
-    <t>66301-/0</t>
-  </si>
-  <si>
-    <t>R$  101,41</t>
-  </si>
-  <si>
-    <t>R$  95,00</t>
-  </si>
-  <si>
-    <t>70601-/0</t>
-  </si>
-  <si>
-    <t>66301n/0</t>
-  </si>
-  <si>
-    <t>64801n/0</t>
-  </si>
-  <si>
-    <t>R$  190,00</t>
-  </si>
-  <si>
-    <t>R$  98,75</t>
-  </si>
-  <si>
-    <t>64801R/0</t>
-  </si>
-  <si>
-    <t>R$  12,95</t>
-  </si>
-  <si>
-    <t>64801N/0</t>
-  </si>
-  <si>
-    <t>R$  12,09</t>
-  </si>
-  <si>
-    <t>63701/0</t>
-  </si>
-  <si>
-    <t>R$  14,09</t>
-  </si>
-  <si>
-    <t>R$  15,09</t>
   </si>
   <si>
     <t>4.03 DESPESAS DE VENDAS</t>
@@ -2190,9 +2190,36 @@
     <t>R$ 9.161,99</t>
   </si>
   <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.588,50</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
     <t>12/3</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>01/03/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
@@ -2202,21 +2229,6 @@
     <t>Google 2026</t>
   </si>
   <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>01/03/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
     <t>1/1</t>
   </si>
   <si>
@@ -2232,18 +2244,6 @@
     <t>Facebook 2026</t>
   </si>
   <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.588,50</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
     <t>4.03.03.09.06 Marketing - outros gastos (CV)</t>
   </si>
   <si>
@@ -2643,6 +2643,18 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
+    <t>595/1</t>
+  </si>
+  <si>
+    <t>Oxxo</t>
+  </si>
+  <si>
+    <t>R$  110,94</t>
+  </si>
+  <si>
+    <t>Cafés loja</t>
+  </si>
+  <si>
     <t>593/1</t>
   </si>
   <si>
@@ -2659,18 +2671,6 @@
   </si>
   <si>
     <t>R$  19,98</t>
-  </si>
-  <si>
-    <t>595/1</t>
-  </si>
-  <si>
-    <t>Oxxo</t>
-  </si>
-  <si>
-    <t>R$  110,94</t>
-  </si>
-  <si>
-    <t>Cafés loja</t>
   </si>
   <si>
     <t>569/1</t>
@@ -2759,6 +2759,21 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>3/2</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>592/1</t>
   </si>
   <si>
@@ -2777,21 +2792,6 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>3/2</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
-  </si>
-  <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
   </si>
   <si>
@@ -2858,6 +2858,15 @@
     <t>R$ 400,33</t>
   </si>
   <si>
+    <t>Jackson Fernando de Araujo</t>
+  </si>
+  <si>
+    <t>R$  150,00</t>
+  </si>
+  <si>
+    <t>Segurança 2026</t>
+  </si>
+  <si>
     <t>VERISURE</t>
   </si>
   <si>
@@ -2865,15 +2874,6 @@
   </si>
   <si>
     <t>Verisure - Alarme 2026</t>
-  </si>
-  <si>
-    <t>Jackson Fernando de Araujo</t>
-  </si>
-  <si>
-    <t>R$  150,00</t>
-  </si>
-  <si>
-    <t>Segurança 2026</t>
   </si>
   <si>
     <t>4.04.02.14.08 Site e newsletter da loja</t>
@@ -6040,13 +6040,13 @@
         <v>193</v>
       </c>
       <c r="J61" t="s">
+        <v>83</v>
+      </c>
+      <c r="K61" t="s">
+        <v>67</v>
+      </c>
+      <c r="L61" t="s">
         <v>194</v>
-      </c>
-      <c r="K61" t="s">
-        <v>133</v>
-      </c>
-      <c r="L61" t="s">
-        <v>195</v>
       </c>
       <c r="M61" t="s">
         <v>183</v>
@@ -6081,7 +6081,7 @@
         <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F62" t="s">
         <v>64</v>
@@ -6090,16 +6090,16 @@
         <v>41</v>
       </c>
       <c r="H62" t="s">
+        <v>196</v>
+      </c>
+      <c r="I62" t="s">
         <v>197</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>198</v>
       </c>
-      <c r="J62" t="s">
-        <v>83</v>
-      </c>
       <c r="K62" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="L62" t="s">
         <v>199</v>
@@ -6114,7 +6114,7 @@
         <v>48</v>
       </c>
       <c r="P62" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q62" t="s">
         <v>47</v>
@@ -6146,7 +6146,7 @@
         <v>41</v>
       </c>
       <c r="H63" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I63" t="s">
         <v>201</v>
@@ -6320,7 +6320,7 @@
         <v>210</v>
       </c>
       <c r="J66" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K66" t="s">
         <v>159</v>
@@ -9889,19 +9889,19 @@
         <v>33</v>
       </c>
       <c r="E130" t="s">
+        <v>87</v>
+      </c>
+      <c r="F130" t="s">
+        <v>208</v>
+      </c>
+      <c r="G130" t="s">
+        <v>41</v>
+      </c>
+      <c r="H130" t="s">
         <v>383</v>
       </c>
-      <c r="F130" t="s">
+      <c r="I130" t="s">
         <v>384</v>
-      </c>
-      <c r="G130" t="s">
-        <v>41</v>
-      </c>
-      <c r="H130" t="s">
-        <v>385</v>
-      </c>
-      <c r="I130" t="s">
-        <v>386</v>
       </c>
       <c r="J130" t="s">
         <v>73</v>
@@ -9910,7 +9910,7 @@
         <v>73</v>
       </c>
       <c r="L130" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M130" t="s">
         <v>382</v>
@@ -9919,13 +9919,13 @@
         <v>47</v>
       </c>
       <c r="O130" t="s">
-        <v>34</v>
+        <v>385</v>
       </c>
       <c r="P130" t="s">
-        <v>34</v>
+        <v>384</v>
       </c>
       <c r="Q130" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R130" t="s">
         <v>34</v>
@@ -9945,28 +9945,28 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F131" t="s">
-        <v>384</v>
+        <v>208</v>
       </c>
       <c r="G131" t="s">
         <v>41</v>
       </c>
       <c r="H131" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I131" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="J131" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="K131" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L131" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M131" t="s">
         <v>382</v>
@@ -9975,13 +9975,13 @@
         <v>47</v>
       </c>
       <c r="O131" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="P131" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="Q131" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R131" t="s">
         <v>34</v>
@@ -10001,28 +10001,28 @@
         <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>391</v>
+        <v>113</v>
       </c>
       <c r="F132" t="s">
-        <v>384</v>
+        <v>208</v>
       </c>
       <c r="G132" t="s">
         <v>41</v>
       </c>
       <c r="H132" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I132" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J132" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="K132" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="L132" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M132" t="s">
         <v>382</v>
@@ -10031,13 +10031,13 @@
         <v>47</v>
       </c>
       <c r="O132" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="P132" t="s">
-        <v>34</v>
+        <v>389</v>
       </c>
       <c r="Q132" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R132" t="s">
         <v>34</v>
@@ -10057,28 +10057,28 @@
         <v>34</v>
       </c>
       <c r="E133" t="s">
-        <v>393</v>
+        <v>113</v>
       </c>
       <c r="F133" t="s">
-        <v>384</v>
+        <v>208</v>
       </c>
       <c r="G133" t="s">
         <v>41</v>
       </c>
       <c r="H133" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I133" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="J133" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="K133" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="L133" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M133" t="s">
         <v>382</v>
@@ -10087,13 +10087,13 @@
         <v>47</v>
       </c>
       <c r="O133" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="P133" t="s">
-        <v>34</v>
+        <v>390</v>
       </c>
       <c r="Q133" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R133" t="s">
         <v>34</v>
@@ -10113,28 +10113,28 @@
         <v>34</v>
       </c>
       <c r="E134" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F134" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G134" t="s">
         <v>41</v>
       </c>
       <c r="H134" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I134" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="J134" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K134" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L134" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M134" t="s">
         <v>382</v>
@@ -10143,10 +10143,10 @@
         <v>47</v>
       </c>
       <c r="O134" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
       <c r="P134" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="Q134" t="s">
         <v>47</v>
@@ -10169,28 +10169,28 @@
         <v>34</v>
       </c>
       <c r="E135" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F135" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G135" t="s">
         <v>41</v>
       </c>
       <c r="H135" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I135" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="J135" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="K135" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="L135" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M135" t="s">
         <v>382</v>
@@ -10199,10 +10199,10 @@
         <v>47</v>
       </c>
       <c r="O135" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="P135" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="Q135" t="s">
         <v>47</v>
@@ -10225,28 +10225,28 @@
         <v>34</v>
       </c>
       <c r="E136" t="s">
-        <v>300</v>
+        <v>395</v>
       </c>
       <c r="F136" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G136" t="s">
         <v>41</v>
       </c>
       <c r="H136" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I136" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="J136" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="K136" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L136" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M136" t="s">
         <v>382</v>
@@ -10255,10 +10255,10 @@
         <v>47</v>
       </c>
       <c r="O136" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="P136" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="Q136" t="s">
         <v>47</v>
@@ -10281,28 +10281,28 @@
         <v>34</v>
       </c>
       <c r="E137" t="s">
-        <v>333</v>
+        <v>396</v>
       </c>
       <c r="F137" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G137" t="s">
         <v>41</v>
       </c>
       <c r="H137" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I137" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="J137" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K137" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L137" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M137" t="s">
         <v>382</v>
@@ -10311,10 +10311,10 @@
         <v>47</v>
       </c>
       <c r="O137" t="s">
-        <v>330</v>
+        <v>262</v>
       </c>
       <c r="P137" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="Q137" t="s">
         <v>47</v>
@@ -10337,28 +10337,28 @@
         <v>34</v>
       </c>
       <c r="E138" t="s">
-        <v>285</v>
+        <v>397</v>
       </c>
       <c r="F138" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G138" t="s">
         <v>41</v>
       </c>
       <c r="H138" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I138" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J138" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K138" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L138" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M138" t="s">
         <v>382</v>
@@ -10367,10 +10367,10 @@
         <v>47</v>
       </c>
       <c r="O138" t="s">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="P138" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="Q138" t="s">
         <v>47</v>
@@ -10393,28 +10393,28 @@
         <v>34</v>
       </c>
       <c r="E139" t="s">
-        <v>331</v>
+        <v>150</v>
       </c>
       <c r="F139" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G139" t="s">
         <v>41</v>
       </c>
       <c r="H139" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I139" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J139" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="K139" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="L139" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M139" t="s">
         <v>382</v>
@@ -10423,10 +10423,10 @@
         <v>47</v>
       </c>
       <c r="O139" t="s">
-        <v>330</v>
+        <v>152</v>
       </c>
       <c r="P139" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="Q139" t="s">
         <v>47</v>
@@ -10449,28 +10449,28 @@
         <v>34</v>
       </c>
       <c r="E140" t="s">
-        <v>308</v>
+        <v>110</v>
       </c>
       <c r="F140" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G140" t="s">
         <v>41</v>
       </c>
       <c r="H140" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I140" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J140" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="K140" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L140" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M140" t="s">
         <v>382</v>
@@ -10479,10 +10479,10 @@
         <v>47</v>
       </c>
       <c r="O140" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="P140" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="Q140" t="s">
         <v>47</v>
@@ -10505,28 +10505,28 @@
         <v>34</v>
       </c>
       <c r="E141" t="s">
-        <v>306</v>
+        <v>401</v>
       </c>
       <c r="F141" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G141" t="s">
         <v>41</v>
       </c>
       <c r="H141" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I141" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J141" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="K141" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L141" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M141" t="s">
         <v>382</v>
@@ -10535,10 +10535,10 @@
         <v>47</v>
       </c>
       <c r="O141" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="P141" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Q141" t="s">
         <v>47</v>
@@ -10561,28 +10561,28 @@
         <v>34</v>
       </c>
       <c r="E142" t="s">
-        <v>405</v>
+        <v>150</v>
       </c>
       <c r="F142" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G142" t="s">
         <v>41</v>
       </c>
       <c r="H142" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I142" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="J142" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K142" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L142" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M142" t="s">
         <v>382</v>
@@ -10591,10 +10591,10 @@
         <v>47</v>
       </c>
       <c r="O142" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="P142" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="Q142" t="s">
         <v>47</v>
@@ -10617,28 +10617,28 @@
         <v>34</v>
       </c>
       <c r="E143" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F143" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G143" t="s">
         <v>41</v>
       </c>
       <c r="H143" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I143" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="J143" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K143" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L143" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M143" t="s">
         <v>382</v>
@@ -10647,10 +10647,10 @@
         <v>47</v>
       </c>
       <c r="O143" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="P143" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="Q143" t="s">
         <v>47</v>
@@ -10673,28 +10673,28 @@
         <v>34</v>
       </c>
       <c r="E144" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F144" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G144" t="s">
         <v>41</v>
       </c>
       <c r="H144" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I144" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="J144" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="K144" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L144" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M144" t="s">
         <v>382</v>
@@ -10703,10 +10703,10 @@
         <v>47</v>
       </c>
       <c r="O144" t="s">
-        <v>149</v>
+        <v>294</v>
       </c>
       <c r="P144" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="Q144" t="s">
         <v>47</v>
@@ -10729,19 +10729,19 @@
         <v>34</v>
       </c>
       <c r="E145" t="s">
-        <v>312</v>
+        <v>405</v>
       </c>
       <c r="F145" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="G145" t="s">
         <v>41</v>
       </c>
       <c r="H145" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I145" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="J145" t="s">
         <v>73</v>
@@ -10750,7 +10750,7 @@
         <v>73</v>
       </c>
       <c r="L145" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="M145" t="s">
         <v>382</v>
@@ -10759,10 +10759,10 @@
         <v>47</v>
       </c>
       <c r="O145" t="s">
-        <v>412</v>
+        <v>294</v>
       </c>
       <c r="P145" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="Q145" t="s">
         <v>47</v>
@@ -10785,28 +10785,28 @@
         <v>34</v>
       </c>
       <c r="E146" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F146" t="s">
-        <v>247</v>
+        <v>409</v>
       </c>
       <c r="G146" t="s">
         <v>41</v>
       </c>
       <c r="H146" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I146" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="J146" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K146" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L146" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M146" t="s">
         <v>382</v>
@@ -10815,13 +10815,13 @@
         <v>47</v>
       </c>
       <c r="O146" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="P146" t="s">
-        <v>414</v>
+        <v>34</v>
       </c>
       <c r="Q146" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R146" t="s">
         <v>34</v>
@@ -10841,28 +10841,28 @@
         <v>34</v>
       </c>
       <c r="E147" t="s">
-        <v>276</v>
+        <v>412</v>
       </c>
       <c r="F147" t="s">
-        <v>247</v>
+        <v>409</v>
       </c>
       <c r="G147" t="s">
         <v>41</v>
       </c>
       <c r="H147" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I147" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J147" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K147" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L147" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M147" t="s">
         <v>382</v>
@@ -10871,13 +10871,13 @@
         <v>47</v>
       </c>
       <c r="O147" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="P147" t="s">
-        <v>415</v>
+        <v>34</v>
       </c>
       <c r="Q147" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R147" t="s">
         <v>34</v>
@@ -10897,28 +10897,28 @@
         <v>34</v>
       </c>
       <c r="E148" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F148" t="s">
-        <v>247</v>
+        <v>409</v>
       </c>
       <c r="G148" t="s">
         <v>41</v>
       </c>
       <c r="H148" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I148" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J148" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="K148" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="L148" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M148" t="s">
         <v>382</v>
@@ -10927,13 +10927,13 @@
         <v>47</v>
       </c>
       <c r="O148" t="s">
-        <v>412</v>
+        <v>34</v>
       </c>
       <c r="P148" t="s">
-        <v>417</v>
+        <v>34</v>
       </c>
       <c r="Q148" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R148" t="s">
         <v>34</v>
@@ -10953,28 +10953,28 @@
         <v>34</v>
       </c>
       <c r="E149" t="s">
-        <v>303</v>
+        <v>416</v>
       </c>
       <c r="F149" t="s">
-        <v>247</v>
+        <v>409</v>
       </c>
       <c r="G149" t="s">
         <v>41</v>
       </c>
       <c r="H149" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I149" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J149" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="K149" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="L149" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M149" t="s">
         <v>382</v>
@@ -10983,13 +10983,13 @@
         <v>47</v>
       </c>
       <c r="O149" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="P149" t="s">
-        <v>418</v>
+        <v>34</v>
       </c>
       <c r="Q149" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R149" t="s">
         <v>34</v>
@@ -11009,7 +11009,7 @@
         <v>34</v>
       </c>
       <c r="E150" t="s">
-        <v>298</v>
+        <v>418</v>
       </c>
       <c r="F150" t="s">
         <v>247</v>
@@ -11018,7 +11018,7 @@
         <v>41</v>
       </c>
       <c r="H150" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I150" t="s">
         <v>419</v>
@@ -11030,7 +11030,7 @@
         <v>73</v>
       </c>
       <c r="L150" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M150" t="s">
         <v>382</v>
@@ -11074,19 +11074,19 @@
         <v>41</v>
       </c>
       <c r="H151" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I151" t="s">
         <v>421</v>
       </c>
       <c r="J151" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="K151" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L151" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M151" t="s">
         <v>382</v>
@@ -11095,7 +11095,7 @@
         <v>47</v>
       </c>
       <c r="O151" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="P151" t="s">
         <v>421</v>
@@ -11121,7 +11121,7 @@
         <v>34</v>
       </c>
       <c r="E152" t="s">
-        <v>422</v>
+        <v>300</v>
       </c>
       <c r="F152" t="s">
         <v>247</v>
@@ -11130,19 +11130,19 @@
         <v>41</v>
       </c>
       <c r="H152" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I152" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J152" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="K152" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L152" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M152" t="s">
         <v>382</v>
@@ -11151,10 +11151,10 @@
         <v>47</v>
       </c>
       <c r="O152" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="P152" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q152" t="s">
         <v>47</v>
@@ -11177,7 +11177,7 @@
         <v>34</v>
       </c>
       <c r="E153" t="s">
-        <v>424</v>
+        <v>333</v>
       </c>
       <c r="F153" t="s">
         <v>247</v>
@@ -11186,19 +11186,19 @@
         <v>41</v>
       </c>
       <c r="H153" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I153" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J153" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="K153" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="L153" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M153" t="s">
         <v>382</v>
@@ -11207,10 +11207,10 @@
         <v>47</v>
       </c>
       <c r="O153" t="s">
-        <v>152</v>
+        <v>330</v>
       </c>
       <c r="P153" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q153" t="s">
         <v>47</v>
@@ -11233,7 +11233,7 @@
         <v>34</v>
       </c>
       <c r="E154" t="s">
-        <v>426</v>
+        <v>285</v>
       </c>
       <c r="F154" t="s">
         <v>247</v>
@@ -11242,19 +11242,19 @@
         <v>41</v>
       </c>
       <c r="H154" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I154" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J154" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K154" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L154" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M154" t="s">
         <v>382</v>
@@ -11263,10 +11263,10 @@
         <v>47</v>
       </c>
       <c r="O154" t="s">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="P154" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="Q154" t="s">
         <v>47</v>
@@ -11289,7 +11289,7 @@
         <v>34</v>
       </c>
       <c r="E155" t="s">
-        <v>280</v>
+        <v>331</v>
       </c>
       <c r="F155" t="s">
         <v>247</v>
@@ -11298,19 +11298,19 @@
         <v>41</v>
       </c>
       <c r="H155" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I155" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J155" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="K155" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="L155" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M155" t="s">
         <v>382</v>
@@ -11319,10 +11319,10 @@
         <v>47</v>
       </c>
       <c r="O155" t="s">
-        <v>145</v>
+        <v>330</v>
       </c>
       <c r="P155" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="Q155" t="s">
         <v>47</v>
@@ -11345,7 +11345,7 @@
         <v>34</v>
       </c>
       <c r="E156" t="s">
-        <v>429</v>
+        <v>308</v>
       </c>
       <c r="F156" t="s">
         <v>247</v>
@@ -11354,19 +11354,19 @@
         <v>41</v>
       </c>
       <c r="H156" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I156" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="J156" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K156" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L156" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M156" t="s">
         <v>382</v>
@@ -11375,10 +11375,10 @@
         <v>47</v>
       </c>
       <c r="O156" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="P156" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="Q156" t="s">
         <v>47</v>
@@ -11401,7 +11401,7 @@
         <v>34</v>
       </c>
       <c r="E157" t="s">
-        <v>431</v>
+        <v>306</v>
       </c>
       <c r="F157" t="s">
         <v>247</v>
@@ -11410,19 +11410,19 @@
         <v>41</v>
       </c>
       <c r="H157" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I157" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="J157" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="K157" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L157" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="M157" t="s">
         <v>382</v>
@@ -11431,10 +11431,10 @@
         <v>47</v>
       </c>
       <c r="O157" t="s">
-        <v>294</v>
+        <v>98</v>
       </c>
       <c r="P157" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="Q157" t="s">
         <v>47</v>
@@ -11457,28 +11457,28 @@
         <v>34</v>
       </c>
       <c r="E158" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="F158" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G158" t="s">
         <v>41</v>
       </c>
       <c r="H158" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I158" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J158" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="K158" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="L158" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M158" t="s">
         <v>382</v>
@@ -11487,10 +11487,10 @@
         <v>47</v>
       </c>
       <c r="O158" t="s">
-        <v>48</v>
+        <v>269</v>
       </c>
       <c r="P158" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="Q158" t="s">
         <v>47</v>
@@ -11513,28 +11513,28 @@
         <v>34</v>
       </c>
       <c r="E159" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F159" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G159" t="s">
         <v>41</v>
       </c>
       <c r="H159" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I159" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="J159" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="K159" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="L159" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M159" t="s">
         <v>382</v>
@@ -11543,10 +11543,10 @@
         <v>47</v>
       </c>
       <c r="O159" t="s">
-        <v>437</v>
+        <v>169</v>
       </c>
       <c r="P159" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="Q159" t="s">
         <v>47</v>
@@ -11569,28 +11569,28 @@
         <v>34</v>
       </c>
       <c r="E160" t="s">
-        <v>94</v>
+        <v>432</v>
       </c>
       <c r="F160" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G160" t="s">
         <v>41</v>
       </c>
       <c r="H160" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I160" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="J160" t="s">
-        <v>439</v>
+        <v>119</v>
       </c>
       <c r="K160" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L160" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M160" t="s">
         <v>382</v>
@@ -11599,10 +11599,10 @@
         <v>47</v>
       </c>
       <c r="O160" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="P160" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q160" t="s">
         <v>47</v>
@@ -11625,28 +11625,28 @@
         <v>34</v>
       </c>
       <c r="E161" t="s">
-        <v>440</v>
+        <v>312</v>
       </c>
       <c r="F161" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G161" t="s">
         <v>41</v>
       </c>
       <c r="H161" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I161" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="J161" t="s">
-        <v>442</v>
+        <v>73</v>
       </c>
       <c r="K161" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L161" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M161" t="s">
         <v>382</v>
@@ -11655,10 +11655,10 @@
         <v>47</v>
       </c>
       <c r="O161" t="s">
-        <v>269</v>
+        <v>385</v>
       </c>
       <c r="P161" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="Q161" t="s">
         <v>47</v>
@@ -11681,28 +11681,28 @@
         <v>34</v>
       </c>
       <c r="E162" t="s">
-        <v>94</v>
+        <v>435</v>
       </c>
       <c r="F162" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G162" t="s">
         <v>41</v>
       </c>
       <c r="H162" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I162" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="J162" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="K162" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="L162" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M162" t="s">
         <v>382</v>
@@ -11711,10 +11711,10 @@
         <v>47</v>
       </c>
       <c r="O162" t="s">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="P162" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="Q162" t="s">
         <v>47</v>
@@ -11737,28 +11737,28 @@
         <v>34</v>
       </c>
       <c r="E163" t="s">
-        <v>440</v>
+        <v>276</v>
       </c>
       <c r="F163" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G163" t="s">
         <v>41</v>
       </c>
       <c r="H163" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I163" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="J163" t="s">
-        <v>439</v>
+        <v>78</v>
       </c>
       <c r="K163" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="L163" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M163" t="s">
         <v>382</v>
@@ -11767,10 +11767,10 @@
         <v>47</v>
       </c>
       <c r="O163" t="s">
-        <v>269</v>
+        <v>169</v>
       </c>
       <c r="P163" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="Q163" t="s">
         <v>47</v>
@@ -11793,28 +11793,28 @@
         <v>34</v>
       </c>
       <c r="E164" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="F164" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G164" t="s">
         <v>41</v>
       </c>
       <c r="H164" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I164" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="J164" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="K164" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L164" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M164" t="s">
         <v>382</v>
@@ -11823,10 +11823,10 @@
         <v>47</v>
       </c>
       <c r="O164" t="s">
-        <v>269</v>
+        <v>385</v>
       </c>
       <c r="P164" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="Q164" t="s">
         <v>47</v>
@@ -11849,28 +11849,28 @@
         <v>34</v>
       </c>
       <c r="E165" t="s">
-        <v>448</v>
+        <v>303</v>
       </c>
       <c r="F165" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G165" t="s">
         <v>41</v>
       </c>
       <c r="H165" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I165" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="J165" t="s">
-        <v>447</v>
+        <v>119</v>
       </c>
       <c r="K165" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L165" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M165" t="s">
         <v>382</v>
@@ -11879,10 +11879,10 @@
         <v>47</v>
       </c>
       <c r="O165" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="P165" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="Q165" t="s">
         <v>47</v>
@@ -11905,28 +11905,28 @@
         <v>34</v>
       </c>
       <c r="E166" t="s">
-        <v>87</v>
+        <v>298</v>
       </c>
       <c r="F166" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G166" t="s">
         <v>41</v>
       </c>
       <c r="H166" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I166" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="J166" t="s">
-        <v>447</v>
+        <v>73</v>
       </c>
       <c r="K166" t="s">
         <v>73</v>
       </c>
       <c r="L166" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M166" t="s">
         <v>382</v>
@@ -11935,10 +11935,10 @@
         <v>47</v>
       </c>
       <c r="O166" t="s">
-        <v>412</v>
+        <v>115</v>
       </c>
       <c r="P166" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="Q166" t="s">
         <v>47</v>
@@ -11961,28 +11961,28 @@
         <v>34</v>
       </c>
       <c r="E167" t="s">
-        <v>166</v>
+        <v>442</v>
       </c>
       <c r="F167" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G167" t="s">
         <v>41</v>
       </c>
       <c r="H167" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I167" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="J167" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="K167" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="L167" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M167" t="s">
         <v>382</v>
@@ -11991,10 +11991,10 @@
         <v>47</v>
       </c>
       <c r="O167" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="P167" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="Q167" t="s">
         <v>47</v>
@@ -12017,28 +12017,28 @@
         <v>34</v>
       </c>
       <c r="E168" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F168" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G168" t="s">
         <v>41</v>
       </c>
       <c r="H168" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I168" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="J168" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="K168" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L168" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M168" t="s">
         <v>382</v>
@@ -12047,10 +12047,10 @@
         <v>47</v>
       </c>
       <c r="O168" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="P168" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="Q168" t="s">
         <v>47</v>
@@ -12073,28 +12073,28 @@
         <v>34</v>
       </c>
       <c r="E169" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="F169" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G169" t="s">
         <v>41</v>
       </c>
       <c r="H169" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I169" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="J169" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="K169" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="L169" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M169" t="s">
         <v>382</v>
@@ -12103,10 +12103,10 @@
         <v>47</v>
       </c>
       <c r="O169" t="s">
-        <v>262</v>
+        <v>152</v>
       </c>
       <c r="P169" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="Q169" t="s">
         <v>47</v>
@@ -12129,19 +12129,19 @@
         <v>34</v>
       </c>
       <c r="E170" t="s">
-        <v>87</v>
+        <v>448</v>
       </c>
       <c r="F170" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G170" t="s">
         <v>41</v>
       </c>
       <c r="H170" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I170" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="J170" t="s">
         <v>73</v>
@@ -12150,7 +12150,7 @@
         <v>73</v>
       </c>
       <c r="L170" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M170" t="s">
         <v>382</v>
@@ -12159,10 +12159,10 @@
         <v>47</v>
       </c>
       <c r="O170" t="s">
-        <v>412</v>
+        <v>294</v>
       </c>
       <c r="P170" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="Q170" t="s">
         <v>47</v>
@@ -12185,28 +12185,28 @@
         <v>34</v>
       </c>
       <c r="E171" t="s">
-        <v>457</v>
+        <v>280</v>
       </c>
       <c r="F171" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G171" t="s">
         <v>41</v>
       </c>
       <c r="H171" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I171" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="J171" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="K171" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="L171" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M171" t="s">
         <v>382</v>
@@ -12215,10 +12215,10 @@
         <v>47</v>
       </c>
       <c r="O171" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="P171" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="Q171" t="s">
         <v>47</v>
@@ -12241,28 +12241,28 @@
         <v>34</v>
       </c>
       <c r="E172" t="s">
-        <v>113</v>
+        <v>451</v>
       </c>
       <c r="F172" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G172" t="s">
         <v>41</v>
       </c>
       <c r="H172" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I172" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="J172" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="K172" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="L172" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M172" t="s">
         <v>382</v>
@@ -12271,10 +12271,10 @@
         <v>47</v>
       </c>
       <c r="O172" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="P172" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="Q172" t="s">
         <v>47</v>
@@ -12297,19 +12297,19 @@
         <v>34</v>
       </c>
       <c r="E173" t="s">
-        <v>113</v>
+        <v>453</v>
       </c>
       <c r="F173" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G173" t="s">
         <v>41</v>
       </c>
       <c r="H173" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I173" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="J173" t="s">
         <v>73</v>
@@ -12318,7 +12318,7 @@
         <v>73</v>
       </c>
       <c r="L173" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="M173" t="s">
         <v>382</v>
@@ -12327,10 +12327,10 @@
         <v>47</v>
       </c>
       <c r="O173" t="s">
-        <v>115</v>
+        <v>294</v>
       </c>
       <c r="P173" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="Q173" t="s">
         <v>47</v>
@@ -12353,7 +12353,7 @@
         <v>34</v>
       </c>
       <c r="E174" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="F174" t="s">
         <v>208</v>
@@ -12362,16 +12362,16 @@
         <v>41</v>
       </c>
       <c r="H174" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I174" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="J174" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="K174" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="L174" t="s">
         <v>34</v>
@@ -12383,10 +12383,10 @@
         <v>47</v>
       </c>
       <c r="O174" t="s">
-        <v>262</v>
+        <v>48</v>
       </c>
       <c r="P174" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="Q174" t="s">
         <v>47</v>
@@ -12409,7 +12409,7 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F175" t="s">
         <v>208</v>
@@ -12418,16 +12418,16 @@
         <v>41</v>
       </c>
       <c r="H175" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I175" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="J175" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="K175" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="L175" t="s">
         <v>34</v>
@@ -12439,10 +12439,10 @@
         <v>47</v>
       </c>
       <c r="O175" t="s">
-        <v>269</v>
+        <v>459</v>
       </c>
       <c r="P175" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="Q175" t="s">
         <v>47</v>
@@ -12465,7 +12465,7 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>464</v>
+        <v>94</v>
       </c>
       <c r="F176" t="s">
         <v>208</v>
@@ -12474,16 +12474,16 @@
         <v>41</v>
       </c>
       <c r="H176" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I176" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="J176" t="s">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="K176" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L176" t="s">
         <v>34</v>
@@ -12495,10 +12495,10 @@
         <v>47</v>
       </c>
       <c r="O176" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="P176" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="Q176" t="s">
         <v>47</v>
@@ -12521,7 +12521,7 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F177" t="s">
         <v>208</v>
@@ -12530,16 +12530,16 @@
         <v>41</v>
       </c>
       <c r="H177" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I177" t="s">
         <v>463</v>
       </c>
       <c r="J177" t="s">
-        <v>68</v>
+        <v>464</v>
       </c>
       <c r="K177" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="L177" t="s">
         <v>34</v>
@@ -12551,7 +12551,7 @@
         <v>47</v>
       </c>
       <c r="O177" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="P177" t="s">
         <v>463</v>
@@ -12577,7 +12577,7 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>466</v>
+        <v>94</v>
       </c>
       <c r="F178" t="s">
         <v>208</v>
@@ -12586,16 +12586,16 @@
         <v>41</v>
       </c>
       <c r="H178" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I178" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J178" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="K178" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L178" t="s">
         <v>34</v>
@@ -12607,10 +12607,10 @@
         <v>47</v>
       </c>
       <c r="O178" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="P178" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="Q178" t="s">
         <v>47</v>
@@ -12633,7 +12633,7 @@
         <v>34</v>
       </c>
       <c r="E179" t="s">
-        <v>150</v>
+        <v>462</v>
       </c>
       <c r="F179" t="s">
         <v>208</v>
@@ -12642,16 +12642,16 @@
         <v>41</v>
       </c>
       <c r="H179" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I179" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="J179" t="s">
-        <v>120</v>
+        <v>461</v>
       </c>
       <c r="K179" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L179" t="s">
         <v>34</v>
@@ -12663,10 +12663,10 @@
         <v>47</v>
       </c>
       <c r="O179" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="P179" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="Q179" t="s">
         <v>47</v>
@@ -12689,7 +12689,7 @@
         <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>110</v>
+        <v>393</v>
       </c>
       <c r="F180" t="s">
         <v>208</v>
@@ -12698,16 +12698,16 @@
         <v>41</v>
       </c>
       <c r="H180" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I180" t="s">
+        <v>467</v>
+      </c>
+      <c r="J180" t="s">
         <v>468</v>
       </c>
-      <c r="J180" t="s">
-        <v>105</v>
-      </c>
       <c r="K180" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="L180" t="s">
         <v>34</v>
@@ -12719,10 +12719,10 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="P180" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Q180" t="s">
         <v>47</v>
@@ -12754,16 +12754,16 @@
         <v>41</v>
       </c>
       <c r="H181" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I181" t="s">
         <v>470</v>
       </c>
       <c r="J181" t="s">
-        <v>73</v>
+        <v>468</v>
       </c>
       <c r="K181" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L181" t="s">
         <v>34</v>
@@ -12775,7 +12775,7 @@
         <v>47</v>
       </c>
       <c r="O181" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="P181" t="s">
         <v>470</v>
@@ -12801,7 +12801,7 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="F182" t="s">
         <v>208</v>
@@ -12810,16 +12810,16 @@
         <v>41</v>
       </c>
       <c r="H182" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I182" t="s">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="J182" t="s">
-        <v>120</v>
+        <v>468</v>
       </c>
       <c r="K182" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="L182" t="s">
         <v>34</v>
@@ -12831,10 +12831,10 @@
         <v>47</v>
       </c>
       <c r="O182" t="s">
-        <v>152</v>
+        <v>385</v>
       </c>
       <c r="P182" t="s">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="Q182" t="s">
         <v>47</v>
@@ -12857,7 +12857,7 @@
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>471</v>
+        <v>166</v>
       </c>
       <c r="F183" t="s">
         <v>208</v>
@@ -12866,16 +12866,16 @@
         <v>41</v>
       </c>
       <c r="H183" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I183" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J183" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K183" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L183" t="s">
         <v>34</v>
@@ -12887,10 +12887,10 @@
         <v>47</v>
       </c>
       <c r="O183" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="P183" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q183" t="s">
         <v>47</v>
@@ -12913,7 +12913,7 @@
         <v>34</v>
       </c>
       <c r="E184" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F184" t="s">
         <v>208</v>
@@ -12922,16 +12922,16 @@
         <v>41</v>
       </c>
       <c r="H184" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I184" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J184" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="K184" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L184" t="s">
         <v>34</v>
@@ -12943,10 +12943,10 @@
         <v>47</v>
       </c>
       <c r="O184" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="P184" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q184" t="s">
         <v>47</v>
@@ -12969,7 +12969,7 @@
         <v>34</v>
       </c>
       <c r="E185" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F185" t="s">
         <v>208</v>
@@ -12978,16 +12978,16 @@
         <v>41</v>
       </c>
       <c r="H185" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I185" t="s">
         <v>475</v>
       </c>
       <c r="J185" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K185" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L185" t="s">
         <v>34</v>
@@ -12999,7 +12999,7 @@
         <v>47</v>
       </c>
       <c r="O185" t="s">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="P185" t="s">
         <v>475</v>
@@ -18039,7 +18039,7 @@
         <v>47</v>
       </c>
       <c r="O275" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="P275" t="s">
         <v>500</v>
@@ -18242,7 +18242,7 @@
         <v>41</v>
       </c>
       <c r="H279" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I279" t="s">
         <v>581</v>
@@ -18289,7 +18289,7 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="F280" t="s">
         <v>484</v>
@@ -18298,7 +18298,7 @@
         <v>41</v>
       </c>
       <c r="H280" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I280" t="s">
         <v>494</v>
@@ -18354,7 +18354,7 @@
         <v>41</v>
       </c>
       <c r="H281" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I281" t="s">
         <v>550</v>
@@ -18410,7 +18410,7 @@
         <v>41</v>
       </c>
       <c r="H282" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I282" t="s">
         <v>489</v>
@@ -18522,7 +18522,7 @@
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I284" t="s">
         <v>585</v>
@@ -18578,7 +18578,7 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I285" t="s">
         <v>588</v>
@@ -18634,7 +18634,7 @@
         <v>41</v>
       </c>
       <c r="H286" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I286" t="s">
         <v>589</v>
@@ -18690,7 +18690,7 @@
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I287" t="s">
         <v>590</v>
@@ -18746,7 +18746,7 @@
         <v>41</v>
       </c>
       <c r="H288" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I288" t="s">
         <v>591</v>
@@ -18849,7 +18849,7 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>473</v>
+        <v>405</v>
       </c>
       <c r="F290" t="s">
         <v>208</v>
@@ -19129,7 +19129,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="F295" t="s">
         <v>208</v>
@@ -19185,7 +19185,7 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="F296" t="s">
         <v>208</v>
@@ -19418,7 +19418,7 @@
         <v>41</v>
       </c>
       <c r="H300" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I300" t="s">
         <v>612</v>
@@ -20261,7 +20261,7 @@
         <v>638</v>
       </c>
       <c r="I315" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="J315" t="s">
         <v>105</v>
@@ -20282,7 +20282,7 @@
         <v>112</v>
       </c>
       <c r="P315" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="Q315" t="s">
         <v>47</v>
@@ -20305,7 +20305,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>473</v>
+        <v>405</v>
       </c>
       <c r="F316" t="s">
         <v>208</v>
@@ -20417,7 +20417,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="F318" t="s">
         <v>208</v>
@@ -20977,7 +20977,7 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="F328" t="s">
         <v>208</v>
@@ -21985,7 +21985,7 @@
         <v>33</v>
       </c>
       <c r="E346" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F346" t="s">
         <v>40</v>
@@ -22000,10 +22000,10 @@
         <v>92</v>
       </c>
       <c r="J346" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="K346" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="L346" t="s">
         <v>34</v>
@@ -22015,7 +22015,7 @@
         <v>47</v>
       </c>
       <c r="O346" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="P346" t="s">
         <v>92</v>
@@ -22041,7 +22041,7 @@
         <v>34</v>
       </c>
       <c r="E347" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="F347" t="s">
         <v>40</v>
@@ -22071,7 +22071,7 @@
         <v>47</v>
       </c>
       <c r="O347" t="s">
-        <v>294</v>
+        <v>115</v>
       </c>
       <c r="P347" t="s">
         <v>92</v>
@@ -22153,10 +22153,10 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>250</v>
+        <v>531</v>
       </c>
       <c r="F349" t="s">
-        <v>40</v>
+        <v>709</v>
       </c>
       <c r="G349" t="s">
         <v>41</v>
@@ -22168,10 +22168,10 @@
         <v>92</v>
       </c>
       <c r="J349" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="K349" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="L349" t="s">
         <v>34</v>
@@ -22183,13 +22183,13 @@
         <v>47</v>
       </c>
       <c r="O349" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="P349" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="Q349" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R349" t="s">
         <v>34</v>
@@ -22209,7 +22209,7 @@
         <v>34</v>
       </c>
       <c r="E350" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="F350" t="s">
         <v>40</v>
@@ -22224,10 +22224,10 @@
         <v>92</v>
       </c>
       <c r="J350" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K350" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L350" t="s">
         <v>34</v>
@@ -22239,7 +22239,7 @@
         <v>47</v>
       </c>
       <c r="O350" t="s">
-        <v>169</v>
+        <v>294</v>
       </c>
       <c r="P350" t="s">
         <v>92</v>
@@ -22265,7 +22265,7 @@
         <v>34</v>
       </c>
       <c r="E351" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F351" t="s">
         <v>40</v>
@@ -22280,10 +22280,10 @@
         <v>92</v>
       </c>
       <c r="J351" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="K351" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L351" t="s">
         <v>34</v>
@@ -22295,7 +22295,7 @@
         <v>47</v>
       </c>
       <c r="O351" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="P351" t="s">
         <v>92</v>
@@ -22321,7 +22321,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="F352" t="s">
         <v>40</v>
@@ -22336,10 +22336,10 @@
         <v>92</v>
       </c>
       <c r="J352" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="K352" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L352" t="s">
         <v>34</v>
@@ -22351,7 +22351,7 @@
         <v>47</v>
       </c>
       <c r="O352" t="s">
-        <v>88</v>
+        <v>269</v>
       </c>
       <c r="P352" t="s">
         <v>92</v>
@@ -22433,7 +22433,7 @@
         <v>34</v>
       </c>
       <c r="E354" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="F354" t="s">
         <v>40</v>
@@ -22448,10 +22448,10 @@
         <v>92</v>
       </c>
       <c r="J354" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K354" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L354" t="s">
         <v>34</v>
@@ -22463,7 +22463,7 @@
         <v>47</v>
       </c>
       <c r="O354" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="P354" t="s">
         <v>92</v>
@@ -22489,10 +22489,10 @@
         <v>34</v>
       </c>
       <c r="E355" t="s">
-        <v>531</v>
+        <v>272</v>
       </c>
       <c r="F355" t="s">
-        <v>709</v>
+        <v>40</v>
       </c>
       <c r="G355" t="s">
         <v>41</v>
@@ -22504,10 +22504,10 @@
         <v>92</v>
       </c>
       <c r="J355" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K355" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="L355" t="s">
         <v>34</v>
@@ -22519,13 +22519,13 @@
         <v>47</v>
       </c>
       <c r="O355" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="P355" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="Q355" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R355" t="s">
         <v>34</v>
@@ -22545,7 +22545,7 @@
         <v>34</v>
       </c>
       <c r="E356" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F356" t="s">
         <v>40</v>
@@ -22560,10 +22560,10 @@
         <v>92</v>
       </c>
       <c r="J356" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K356" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="L356" t="s">
         <v>34</v>
@@ -22575,7 +22575,7 @@
         <v>47</v>
       </c>
       <c r="O356" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="P356" t="s">
         <v>92</v>
@@ -22657,7 +22657,7 @@
         <v>34</v>
       </c>
       <c r="E358" t="s">
-        <v>260</v>
+        <v>487</v>
       </c>
       <c r="F358" t="s">
         <v>40</v>
@@ -22672,10 +22672,10 @@
         <v>92</v>
       </c>
       <c r="J358" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K358" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="L358" t="s">
         <v>34</v>
@@ -22687,7 +22687,7 @@
         <v>47</v>
       </c>
       <c r="O358" t="s">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="P358" t="s">
         <v>92</v>
@@ -22713,7 +22713,7 @@
         <v>34</v>
       </c>
       <c r="E359" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="F359" t="s">
         <v>40</v>
@@ -22728,10 +22728,10 @@
         <v>92</v>
       </c>
       <c r="J359" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="K359" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="L359" t="s">
         <v>34</v>
@@ -22743,7 +22743,7 @@
         <v>47</v>
       </c>
       <c r="O359" t="s">
-        <v>269</v>
+        <v>98</v>
       </c>
       <c r="P359" t="s">
         <v>92</v>
@@ -22769,7 +22769,7 @@
         <v>34</v>
       </c>
       <c r="E360" t="s">
-        <v>487</v>
+        <v>260</v>
       </c>
       <c r="F360" t="s">
         <v>40</v>
@@ -22784,10 +22784,10 @@
         <v>92</v>
       </c>
       <c r="J360" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K360" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="L360" t="s">
         <v>34</v>
@@ -22799,7 +22799,7 @@
         <v>47</v>
       </c>
       <c r="O360" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="P360" t="s">
         <v>92</v>
@@ -22937,7 +22937,7 @@
         <v>33</v>
       </c>
       <c r="E363" t="s">
-        <v>720</v>
+        <v>227</v>
       </c>
       <c r="F363" t="s">
         <v>40</v>
@@ -22946,16 +22946,16 @@
         <v>41</v>
       </c>
       <c r="H363" t="s">
+        <v>720</v>
+      </c>
+      <c r="I363" t="s">
         <v>721</v>
       </c>
-      <c r="I363" t="s">
+      <c r="J363" t="s">
         <v>722</v>
       </c>
-      <c r="J363" t="s">
-        <v>369</v>
-      </c>
       <c r="K363" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="L363" t="s">
         <v>723</v>
@@ -22970,7 +22970,7 @@
         <v>48</v>
       </c>
       <c r="P363" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="Q363" t="s">
         <v>47</v>
@@ -22993,7 +22993,7 @@
         <v>34</v>
       </c>
       <c r="E364" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F364" t="s">
         <v>40</v>
@@ -23002,19 +23002,19 @@
         <v>41</v>
       </c>
       <c r="H364" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I364" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J364" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K364" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L364" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M364" t="s">
         <v>718</v>
@@ -23026,7 +23026,7 @@
         <v>48</v>
       </c>
       <c r="P364" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="Q364" t="s">
         <v>47</v>
@@ -23049,7 +23049,7 @@
         <v>34</v>
       </c>
       <c r="E365" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="F365" t="s">
         <v>40</v>
@@ -23064,13 +23064,13 @@
         <v>731</v>
       </c>
       <c r="J365" t="s">
-        <v>230</v>
+        <v>369</v>
       </c>
       <c r="K365" t="s">
+        <v>45</v>
+      </c>
+      <c r="L365" t="s">
         <v>732</v>
-      </c>
-      <c r="L365" t="s">
-        <v>733</v>
       </c>
       <c r="M365" t="s">
         <v>718</v>
@@ -23105,7 +23105,7 @@
         <v>34</v>
       </c>
       <c r="E366" t="s">
-        <v>227</v>
+        <v>733</v>
       </c>
       <c r="F366" t="s">
         <v>40</v>
@@ -23120,10 +23120,10 @@
         <v>735</v>
       </c>
       <c r="J366" t="s">
+        <v>230</v>
+      </c>
+      <c r="K366" t="s">
         <v>736</v>
-      </c>
-      <c r="K366" t="s">
-        <v>67</v>
       </c>
       <c r="L366" t="s">
         <v>737</v>
@@ -23385,7 +23385,7 @@
         <v>33</v>
       </c>
       <c r="E371" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F371" t="s">
         <v>40</v>
@@ -23400,7 +23400,7 @@
         <v>750</v>
       </c>
       <c r="J371" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K371" t="s">
         <v>45</v>
@@ -23609,7 +23609,7 @@
         <v>34</v>
       </c>
       <c r="E375" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F375" t="s">
         <v>40</v>
@@ -23624,7 +23624,7 @@
         <v>762</v>
       </c>
       <c r="J375" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K375" t="s">
         <v>45</v>
@@ -23665,7 +23665,7 @@
         <v>34</v>
       </c>
       <c r="E376" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="F376" t="s">
         <v>40</v>
@@ -23739,7 +23739,7 @@
         <v>530</v>
       </c>
       <c r="K377" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L377" t="s">
         <v>34</v>
@@ -23795,7 +23795,7 @@
         <v>179</v>
       </c>
       <c r="K378" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L378" t="s">
         <v>34</v>
@@ -23833,7 +23833,7 @@
         <v>34</v>
       </c>
       <c r="E379" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F379" t="s">
         <v>40</v>
@@ -23848,7 +23848,7 @@
         <v>772</v>
       </c>
       <c r="J379" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K379" t="s">
         <v>45</v>
@@ -23889,7 +23889,7 @@
         <v>34</v>
       </c>
       <c r="E380" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F380" t="s">
         <v>40</v>
@@ -23904,7 +23904,7 @@
         <v>750</v>
       </c>
       <c r="J380" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K380" t="s">
         <v>45</v>
@@ -23945,7 +23945,7 @@
         <v>34</v>
       </c>
       <c r="E381" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F381" t="s">
         <v>40</v>
@@ -24001,7 +24001,7 @@
         <v>34</v>
       </c>
       <c r="E382" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F382" t="s">
         <v>40</v>
@@ -24016,7 +24016,7 @@
         <v>780</v>
       </c>
       <c r="J382" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K382" t="s">
         <v>45</v>
@@ -24113,7 +24113,7 @@
         <v>34</v>
       </c>
       <c r="E384" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F384" t="s">
         <v>40</v>
@@ -24128,7 +24128,7 @@
         <v>785</v>
       </c>
       <c r="J384" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K384" t="s">
         <v>45</v>
@@ -24281,7 +24281,7 @@
         <v>34</v>
       </c>
       <c r="E387" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F387" t="s">
         <v>40</v>
@@ -24296,7 +24296,7 @@
         <v>791</v>
       </c>
       <c r="J387" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K387" t="s">
         <v>45</v>
@@ -24738,7 +24738,7 @@
         <v>41</v>
       </c>
       <c r="H395" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I395" t="s">
         <v>810</v>
@@ -24968,7 +24968,7 @@
         <v>819</v>
       </c>
       <c r="J399" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
       <c r="K399" t="s">
         <v>68</v>
@@ -25136,10 +25136,10 @@
         <v>828</v>
       </c>
       <c r="J402" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K402" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L402" t="s">
         <v>829</v>
@@ -25401,7 +25401,7 @@
         <v>33</v>
       </c>
       <c r="E407" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F407" t="s">
         <v>40</v>
@@ -25416,7 +25416,7 @@
         <v>848</v>
       </c>
       <c r="J407" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K407" t="s">
         <v>45</v>
@@ -25569,7 +25569,7 @@
         <v>33</v>
       </c>
       <c r="E410" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F410" t="s">
         <v>40</v>
@@ -25584,7 +25584,7 @@
         <v>860</v>
       </c>
       <c r="J410" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K410" t="s">
         <v>320</v>
@@ -25696,10 +25696,10 @@
         <v>866</v>
       </c>
       <c r="J412" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K412" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L412" t="s">
         <v>867</v>
@@ -25811,10 +25811,10 @@
         <v>179</v>
       </c>
       <c r="K414" t="s">
-        <v>293</v>
+        <v>664</v>
       </c>
       <c r="L414" t="s">
-        <v>34</v>
+        <v>874</v>
       </c>
       <c r="M414" t="s">
         <v>870</v>
@@ -25849,7 +25849,7 @@
         <v>34</v>
       </c>
       <c r="E415" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F415" t="s">
         <v>208</v>
@@ -25858,16 +25858,16 @@
         <v>41</v>
       </c>
       <c r="H415" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="I415" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="J415" t="s">
         <v>179</v>
       </c>
       <c r="K415" t="s">
-        <v>109</v>
+        <v>293</v>
       </c>
       <c r="L415" t="s">
         <v>34</v>
@@ -25882,7 +25882,7 @@
         <v>48</v>
       </c>
       <c r="P415" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Q415" t="s">
         <v>47</v>
@@ -25905,7 +25905,7 @@
         <v>34</v>
       </c>
       <c r="E416" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F416" t="s">
         <v>208</v>
@@ -25914,19 +25914,19 @@
         <v>41</v>
       </c>
       <c r="H416" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="I416" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="J416" t="s">
         <v>179</v>
       </c>
       <c r="K416" t="s">
-        <v>664</v>
+        <v>109</v>
       </c>
       <c r="L416" t="s">
-        <v>880</v>
+        <v>34</v>
       </c>
       <c r="M416" t="s">
         <v>870</v>
@@ -25938,7 +25938,7 @@
         <v>48</v>
       </c>
       <c r="P416" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="Q416" t="s">
         <v>47</v>
@@ -26129,7 +26129,7 @@
         <v>33</v>
       </c>
       <c r="E420" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F420" t="s">
         <v>40</v>
@@ -26144,7 +26144,7 @@
         <v>893</v>
       </c>
       <c r="J420" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K420" t="s">
         <v>45</v>
@@ -26356,25 +26356,25 @@
         <v>908</v>
       </c>
       <c r="F424" t="s">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="G424" t="s">
         <v>41</v>
       </c>
       <c r="H424" t="s">
+        <v>903</v>
+      </c>
+      <c r="I424" t="s">
         <v>909</v>
       </c>
-      <c r="I424" t="s">
+      <c r="J424" t="s">
+        <v>373</v>
+      </c>
+      <c r="K424" t="s">
+        <v>45</v>
+      </c>
+      <c r="L424" t="s">
         <v>910</v>
-      </c>
-      <c r="J424" t="s">
-        <v>179</v>
-      </c>
-      <c r="K424" t="s">
-        <v>293</v>
-      </c>
-      <c r="L424" t="s">
-        <v>34</v>
       </c>
       <c r="M424" t="s">
         <v>907</v>
@@ -26386,7 +26386,7 @@
         <v>48</v>
       </c>
       <c r="P424" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="Q424" t="s">
         <v>47</v>
@@ -26409,7 +26409,7 @@
         <v>34</v>
       </c>
       <c r="E425" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F425" t="s">
         <v>40</v>
@@ -26418,19 +26418,19 @@
         <v>41</v>
       </c>
       <c r="H425" t="s">
+        <v>903</v>
+      </c>
+      <c r="I425" t="s">
         <v>911</v>
-      </c>
-      <c r="I425" t="s">
-        <v>912</v>
       </c>
       <c r="J425" t="s">
         <v>369</v>
       </c>
       <c r="K425" t="s">
-        <v>45</v>
+        <v>674</v>
       </c>
       <c r="L425" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="M425" t="s">
         <v>907</v>
@@ -26442,7 +26442,7 @@
         <v>48</v>
       </c>
       <c r="P425" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="Q425" t="s">
         <v>47</v>
@@ -26465,28 +26465,28 @@
         <v>34</v>
       </c>
       <c r="E426" t="s">
-        <v>720</v>
+        <v>913</v>
       </c>
       <c r="F426" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G426" t="s">
         <v>41</v>
       </c>
       <c r="H426" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="I426" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="J426" t="s">
-        <v>369</v>
+        <v>179</v>
       </c>
       <c r="K426" t="s">
-        <v>674</v>
+        <v>293</v>
       </c>
       <c r="L426" t="s">
-        <v>915</v>
+        <v>34</v>
       </c>
       <c r="M426" t="s">
         <v>907</v>
@@ -26498,7 +26498,7 @@
         <v>48</v>
       </c>
       <c r="P426" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="Q426" t="s">
         <v>47</v>
@@ -26521,7 +26521,7 @@
         <v>34</v>
       </c>
       <c r="E427" t="s">
-        <v>916</v>
+        <v>724</v>
       </c>
       <c r="F427" t="s">
         <v>40</v>
@@ -26530,13 +26530,13 @@
         <v>41</v>
       </c>
       <c r="H427" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="I427" t="s">
         <v>917</v>
       </c>
       <c r="J427" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="K427" t="s">
         <v>45</v>
@@ -26745,7 +26745,7 @@
         <v>33</v>
       </c>
       <c r="E431" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F431" t="s">
         <v>40</v>
@@ -26760,7 +26760,7 @@
         <v>930</v>
       </c>
       <c r="J431" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K431" t="s">
         <v>45</v>
@@ -26913,7 +26913,7 @@
         <v>33</v>
       </c>
       <c r="E434" t="s">
-        <v>826</v>
+        <v>724</v>
       </c>
       <c r="F434" t="s">
         <v>40</v>
@@ -26928,10 +26928,10 @@
         <v>942</v>
       </c>
       <c r="J434" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="K434" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="L434" t="s">
         <v>943</v>
@@ -26969,7 +26969,7 @@
         <v>34</v>
       </c>
       <c r="E435" t="s">
-        <v>720</v>
+        <v>826</v>
       </c>
       <c r="F435" t="s">
         <v>40</v>
@@ -26984,10 +26984,10 @@
         <v>945</v>
       </c>
       <c r="J435" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="K435" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="L435" t="s">
         <v>946</v>
@@ -27193,7 +27193,7 @@
         <v>33</v>
       </c>
       <c r="E439" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="F439" t="s">
         <v>40</v>
@@ -28119,7 +28119,7 @@
         <v>47</v>
       </c>
       <c r="O455" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="P455" t="s">
         <v>975</v>

--- a/xlsx/dre/DRE_03_2026.xlsx
+++ b/xlsx/dre/DRE_03_2026.xlsx
@@ -1952,124 +1952,76 @@
     <t>67301SamirF</t>
   </si>
   <si>
+    <t>67301U/0</t>
+  </si>
+  <si>
+    <t>R$  11,67</t>
+  </si>
+  <si>
+    <t>R$  10,64</t>
+  </si>
+  <si>
+    <t>R$  30,52</t>
+  </si>
+  <si>
+    <t>69301U/0</t>
+  </si>
+  <si>
+    <t>R$  17,28</t>
+  </si>
+  <si>
+    <t>R$  44,66</t>
+  </si>
+  <si>
+    <t>R$  31,32</t>
+  </si>
+  <si>
+    <t>R$  20,25</t>
+  </si>
+  <si>
+    <t>05/06/26</t>
+  </si>
+  <si>
+    <t>R$  41,40</t>
+  </si>
+  <si>
+    <t>R$  23,72</t>
+  </si>
+  <si>
+    <t>51701U/0</t>
+  </si>
+  <si>
+    <t>R$  15,52</t>
+  </si>
+  <si>
+    <t>67501UBER/0</t>
+  </si>
+  <si>
+    <t>R$  7,81</t>
+  </si>
+  <si>
+    <t>R$  20,94</t>
+  </si>
+  <si>
+    <t>63301UBER/0</t>
+  </si>
+  <si>
+    <t>R$  10,38</t>
+  </si>
+  <si>
+    <t>R$  40,49</t>
+  </si>
+  <si>
     <t>64301U/0</t>
   </si>
   <si>
-    <t>R$  10,64</t>
-  </si>
-  <si>
-    <t>R$  44,66</t>
-  </si>
-  <si>
-    <t>R$  31,32</t>
-  </si>
-  <si>
-    <t>69301U/0</t>
-  </si>
-  <si>
-    <t>R$  17,28</t>
-  </si>
-  <si>
-    <t>67301U/0</t>
-  </si>
-  <si>
-    <t>R$  11,67</t>
-  </si>
-  <si>
-    <t>R$  30,52</t>
-  </si>
-  <si>
-    <t>67501UBER/0</t>
-  </si>
-  <si>
-    <t>R$  7,81</t>
-  </si>
-  <si>
-    <t>R$  20,94</t>
-  </si>
-  <si>
-    <t>63301UBER/0</t>
-  </si>
-  <si>
-    <t>R$  10,38</t>
-  </si>
-  <si>
-    <t>R$  20,25</t>
-  </si>
-  <si>
-    <t>05/06/26</t>
-  </si>
-  <si>
-    <t>R$  23,72</t>
-  </si>
-  <si>
-    <t>R$  41,40</t>
-  </si>
-  <si>
-    <t>R$  40,49</t>
-  </si>
-  <si>
-    <t>47701/0</t>
-  </si>
-  <si>
-    <t>R$  13,69</t>
+    <t>ADM/7</t>
+  </si>
+  <si>
+    <t>R$  129,61</t>
   </si>
   <si>
     <t>06/03/26</t>
-  </si>
-  <si>
-    <t>47701LurdesCRN</t>
-  </si>
-  <si>
-    <t>44701/0</t>
-  </si>
-  <si>
-    <t>R$  28,15</t>
-  </si>
-  <si>
-    <t>44701WILMAHENR</t>
-  </si>
-  <si>
-    <t>47101/0</t>
-  </si>
-  <si>
-    <t>R$  57,95</t>
-  </si>
-  <si>
-    <t>47101MarciaOA</t>
-  </si>
-  <si>
-    <t>48801/0</t>
-  </si>
-  <si>
-    <t>R$  16,34</t>
-  </si>
-  <si>
-    <t>08/03/26</t>
-  </si>
-  <si>
-    <t>48801ANACASS</t>
-  </si>
-  <si>
-    <t>47101/1/0</t>
-  </si>
-  <si>
-    <t>R$  20,93</t>
-  </si>
-  <si>
-    <t>4901/0</t>
-  </si>
-  <si>
-    <t>R$  33,96</t>
-  </si>
-  <si>
-    <t>WilliamW004901</t>
-  </si>
-  <si>
-    <t>ADM/7</t>
-  </si>
-  <si>
-    <t>R$  129,61</t>
   </si>
   <si>
     <t xml:space="preserve">29,25	Liana 	Uber	OK	ADM - DE 00751
@@ -2082,6 +2034,66 @@
 </t>
   </si>
   <si>
+    <t>47701/0</t>
+  </si>
+  <si>
+    <t>R$  13,69</t>
+  </si>
+  <si>
+    <t>47701LurdesCRN</t>
+  </si>
+  <si>
+    <t>44701/0</t>
+  </si>
+  <si>
+    <t>R$  28,15</t>
+  </si>
+  <si>
+    <t>44701WILMAHENR</t>
+  </si>
+  <si>
+    <t>R$  12,57</t>
+  </si>
+  <si>
+    <t>47101/1/0</t>
+  </si>
+  <si>
+    <t>R$  20,93</t>
+  </si>
+  <si>
+    <t>47101MarciaOA</t>
+  </si>
+  <si>
+    <t>4901/0</t>
+  </si>
+  <si>
+    <t>R$  33,96</t>
+  </si>
+  <si>
+    <t>WilliamW004901</t>
+  </si>
+  <si>
+    <t>46201/0</t>
+  </si>
+  <si>
+    <t>R$  12,98</t>
+  </si>
+  <si>
+    <t>08/03/26</t>
+  </si>
+  <si>
+    <t>46201ANGELASC</t>
+  </si>
+  <si>
+    <t>50701/0</t>
+  </si>
+  <si>
+    <t>R$  27,26</t>
+  </si>
+  <si>
+    <t>50701MoniqueES</t>
+  </si>
+  <si>
     <t>45901/0</t>
   </si>
   <si>
@@ -2091,13 +2103,10 @@
     <t>45901ANAMARIDEO</t>
   </si>
   <si>
-    <t>50701/0</t>
-  </si>
-  <si>
-    <t>R$  27,26</t>
-  </si>
-  <si>
-    <t>50701MoniqueES</t>
+    <t>47101/0</t>
+  </si>
+  <si>
+    <t>R$  57,95</t>
   </si>
   <si>
     <t>34601/0</t>
@@ -2124,22 +2133,13 @@
     <t>29901FL8</t>
   </si>
   <si>
-    <t>46201/0</t>
-  </si>
-  <si>
-    <t>R$  12,98</t>
-  </si>
-  <si>
-    <t>46201ANGELASC</t>
-  </si>
-  <si>
-    <t>R$  12,57</t>
-  </si>
-  <si>
-    <t>51701U/0</t>
-  </si>
-  <si>
-    <t>R$  15,52</t>
+    <t>48801/0</t>
+  </si>
+  <si>
+    <t>R$  16,34</t>
+  </si>
+  <si>
+    <t>48801ANACASS</t>
   </si>
   <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
@@ -20261,13 +20261,13 @@
         <v>638</v>
       </c>
       <c r="I315" t="s">
-        <v>475</v>
+        <v>644</v>
       </c>
       <c r="J315" t="s">
-        <v>105</v>
+        <v>574</v>
       </c>
       <c r="K315" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="L315" t="s">
         <v>34</v>
@@ -20279,10 +20279,10 @@
         <v>47</v>
       </c>
       <c r="O315" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="P315" t="s">
-        <v>475</v>
+        <v>644</v>
       </c>
       <c r="Q315" t="s">
         <v>47</v>
@@ -20317,7 +20317,7 @@
         <v>638</v>
       </c>
       <c r="I316" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J316" t="s">
         <v>73</v>
@@ -20338,7 +20338,7 @@
         <v>294</v>
       </c>
       <c r="P316" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -20361,7 +20361,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="F317" t="s">
         <v>208</v>
@@ -20373,13 +20373,13 @@
         <v>638</v>
       </c>
       <c r="I317" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J317" t="s">
-        <v>120</v>
+        <v>574</v>
       </c>
       <c r="K317" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="L317" t="s">
         <v>34</v>
@@ -20391,10 +20391,10 @@
         <v>47</v>
       </c>
       <c r="O317" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="P317" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Q317" t="s">
         <v>47</v>
@@ -20417,7 +20417,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>474</v>
+        <v>647</v>
       </c>
       <c r="F318" t="s">
         <v>208</v>
@@ -20429,13 +20429,13 @@
         <v>638</v>
       </c>
       <c r="I318" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="J318" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="K318" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="L318" t="s">
         <v>34</v>
@@ -20447,10 +20447,10 @@
         <v>47</v>
       </c>
       <c r="O318" t="s">
-        <v>262</v>
+        <v>149</v>
       </c>
       <c r="P318" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q318" t="s">
         <v>47</v>
@@ -20473,7 +20473,7 @@
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>647</v>
+        <v>150</v>
       </c>
       <c r="F319" t="s">
         <v>208</v>
@@ -20485,13 +20485,13 @@
         <v>638</v>
       </c>
       <c r="I319" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="J319" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K319" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L319" t="s">
         <v>34</v>
@@ -20503,10 +20503,10 @@
         <v>47</v>
       </c>
       <c r="O319" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="P319" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Q319" t="s">
         <v>47</v>
@@ -20529,7 +20529,7 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>649</v>
+        <v>474</v>
       </c>
       <c r="F320" t="s">
         <v>208</v>
@@ -20544,10 +20544,10 @@
         <v>650</v>
       </c>
       <c r="J320" t="s">
-        <v>574</v>
+        <v>68</v>
       </c>
       <c r="K320" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L320" t="s">
         <v>34</v>
@@ -20559,7 +20559,7 @@
         <v>47</v>
       </c>
       <c r="O320" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="P320" t="s">
         <v>650</v>
@@ -20585,7 +20585,7 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="F321" t="s">
         <v>208</v>
@@ -20600,10 +20600,10 @@
         <v>651</v>
       </c>
       <c r="J321" t="s">
-        <v>574</v>
+        <v>652</v>
       </c>
       <c r="K321" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L321" t="s">
         <v>34</v>
@@ -20615,7 +20615,7 @@
         <v>47</v>
       </c>
       <c r="O321" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="P321" t="s">
         <v>651</v>
@@ -20641,7 +20641,7 @@
         <v>34</v>
       </c>
       <c r="E322" t="s">
-        <v>652</v>
+        <v>84</v>
       </c>
       <c r="F322" t="s">
         <v>208</v>
@@ -20656,10 +20656,10 @@
         <v>653</v>
       </c>
       <c r="J322" t="s">
-        <v>617</v>
+        <v>652</v>
       </c>
       <c r="K322" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L322" t="s">
         <v>34</v>
@@ -20671,7 +20671,7 @@
         <v>47</v>
       </c>
       <c r="O322" t="s">
-        <v>269</v>
+        <v>86</v>
       </c>
       <c r="P322" t="s">
         <v>653</v>
@@ -20697,7 +20697,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="F323" t="s">
         <v>208</v>
@@ -20715,7 +20715,7 @@
         <v>617</v>
       </c>
       <c r="K323" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="L323" t="s">
         <v>34</v>
@@ -20727,7 +20727,7 @@
         <v>47</v>
       </c>
       <c r="O323" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="P323" t="s">
         <v>654</v>
@@ -20768,10 +20768,10 @@
         <v>656</v>
       </c>
       <c r="J324" t="s">
-        <v>617</v>
+        <v>652</v>
       </c>
       <c r="K324" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="L324" t="s">
         <v>34</v>
@@ -20783,7 +20783,7 @@
         <v>47</v>
       </c>
       <c r="O324" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="P324" t="s">
         <v>656</v>
@@ -20809,7 +20809,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>94</v>
+        <v>657</v>
       </c>
       <c r="F325" t="s">
         <v>208</v>
@@ -20821,13 +20821,13 @@
         <v>638</v>
       </c>
       <c r="I325" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J325" t="s">
-        <v>658</v>
+        <v>617</v>
       </c>
       <c r="K325" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L325" t="s">
         <v>34</v>
@@ -20839,10 +20839,10 @@
         <v>47</v>
       </c>
       <c r="O325" t="s">
-        <v>98</v>
+        <v>269</v>
       </c>
       <c r="P325" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Q325" t="s">
         <v>47</v>
@@ -20865,7 +20865,7 @@
         <v>34</v>
       </c>
       <c r="E326" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="F326" t="s">
         <v>208</v>
@@ -20883,7 +20883,7 @@
         <v>617</v>
       </c>
       <c r="K326" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L326" t="s">
         <v>34</v>
@@ -20895,7 +20895,7 @@
         <v>47</v>
       </c>
       <c r="O326" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="P326" t="s">
         <v>659</v>
@@ -20921,7 +20921,7 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>84</v>
+        <v>660</v>
       </c>
       <c r="F327" t="s">
         <v>208</v>
@@ -20933,13 +20933,13 @@
         <v>638</v>
       </c>
       <c r="I327" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J327" t="s">
-        <v>658</v>
+        <v>617</v>
       </c>
       <c r="K327" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L327" t="s">
         <v>34</v>
@@ -20951,10 +20951,10 @@
         <v>47</v>
       </c>
       <c r="O327" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="P327" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="Q327" t="s">
         <v>47</v>
@@ -20989,10 +20989,10 @@
         <v>638</v>
       </c>
       <c r="I328" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="J328" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="K328" t="s">
         <v>119</v>
@@ -21010,7 +21010,7 @@
         <v>269</v>
       </c>
       <c r="P328" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="Q328" t="s">
         <v>47</v>
@@ -21033,7 +21033,7 @@
         <v>34</v>
       </c>
       <c r="E329" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F329" t="s">
         <v>208</v>
@@ -21045,13 +21045,13 @@
         <v>638</v>
       </c>
       <c r="I329" t="s">
-        <v>663</v>
+        <v>475</v>
       </c>
       <c r="J329" t="s">
-        <v>664</v>
+        <v>105</v>
       </c>
       <c r="K329" t="s">
-        <v>664</v>
+        <v>105</v>
       </c>
       <c r="L329" t="s">
         <v>34</v>
@@ -21063,10 +21063,10 @@
         <v>47</v>
       </c>
       <c r="O329" t="s">
-        <v>665</v>
+        <v>112</v>
       </c>
       <c r="P329" t="s">
-        <v>663</v>
+        <v>475</v>
       </c>
       <c r="Q329" t="s">
         <v>47</v>
@@ -21089,7 +21089,7 @@
         <v>34</v>
       </c>
       <c r="E330" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F330" t="s">
         <v>208</v>
@@ -21101,16 +21101,16 @@
         <v>638</v>
       </c>
       <c r="I330" t="s">
+        <v>665</v>
+      </c>
+      <c r="J330" t="s">
+        <v>666</v>
+      </c>
+      <c r="K330" t="s">
+        <v>666</v>
+      </c>
+      <c r="L330" t="s">
         <v>667</v>
-      </c>
-      <c r="J330" t="s">
-        <v>664</v>
-      </c>
-      <c r="K330" t="s">
-        <v>664</v>
-      </c>
-      <c r="L330" t="s">
-        <v>34</v>
       </c>
       <c r="M330" t="s">
         <v>636</v>
@@ -21119,10 +21119,10 @@
         <v>47</v>
       </c>
       <c r="O330" t="s">
-        <v>668</v>
+        <v>48</v>
       </c>
       <c r="P330" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="Q330" t="s">
         <v>47</v>
@@ -21145,7 +21145,7 @@
         <v>34</v>
       </c>
       <c r="E331" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F331" t="s">
         <v>208</v>
@@ -21157,13 +21157,13 @@
         <v>638</v>
       </c>
       <c r="I331" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J331" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K331" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L331" t="s">
         <v>34</v>
@@ -21175,10 +21175,10 @@
         <v>47</v>
       </c>
       <c r="O331" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P331" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="Q331" t="s">
         <v>47</v>
@@ -21201,7 +21201,7 @@
         <v>34</v>
       </c>
       <c r="E332" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F332" t="s">
         <v>208</v>
@@ -21213,13 +21213,13 @@
         <v>638</v>
       </c>
       <c r="I332" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="J332" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="K332" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="L332" t="s">
         <v>34</v>
@@ -21231,10 +21231,10 @@
         <v>47</v>
       </c>
       <c r="O332" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="P332" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="Q332" t="s">
         <v>47</v>
@@ -21257,7 +21257,7 @@
         <v>34</v>
       </c>
       <c r="E333" t="s">
-        <v>676</v>
+        <v>134</v>
       </c>
       <c r="F333" t="s">
         <v>208</v>
@@ -21269,13 +21269,13 @@
         <v>638</v>
       </c>
       <c r="I333" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="J333" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K333" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L333" t="s">
         <v>34</v>
@@ -21287,10 +21287,10 @@
         <v>47</v>
       </c>
       <c r="O333" t="s">
-        <v>671</v>
+        <v>137</v>
       </c>
       <c r="P333" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="Q333" t="s">
         <v>47</v>
@@ -21313,7 +21313,7 @@
         <v>34</v>
       </c>
       <c r="E334" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F334" t="s">
         <v>208</v>
@@ -21325,13 +21325,13 @@
         <v>638</v>
       </c>
       <c r="I334" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="J334" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K334" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L334" t="s">
         <v>34</v>
@@ -21343,10 +21343,10 @@
         <v>47</v>
       </c>
       <c r="O334" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="P334" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="Q334" t="s">
         <v>47</v>
@@ -21369,7 +21369,7 @@
         <v>34</v>
       </c>
       <c r="E335" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F335" t="s">
         <v>208</v>
@@ -21381,16 +21381,16 @@
         <v>638</v>
       </c>
       <c r="I335" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="J335" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K335" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L335" t="s">
-        <v>683</v>
+        <v>34</v>
       </c>
       <c r="M335" t="s">
         <v>636</v>
@@ -21399,10 +21399,10 @@
         <v>47</v>
       </c>
       <c r="O335" t="s">
-        <v>48</v>
+        <v>680</v>
       </c>
       <c r="P335" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="Q335" t="s">
         <v>47</v>
@@ -21425,7 +21425,7 @@
         <v>34</v>
       </c>
       <c r="E336" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F336" t="s">
         <v>208</v>
@@ -21437,13 +21437,13 @@
         <v>638</v>
       </c>
       <c r="I336" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="J336" t="s">
-        <v>664</v>
+        <v>683</v>
       </c>
       <c r="K336" t="s">
-        <v>664</v>
+        <v>683</v>
       </c>
       <c r="L336" t="s">
         <v>34</v>
@@ -21455,10 +21455,10 @@
         <v>47</v>
       </c>
       <c r="O336" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="P336" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="Q336" t="s">
         <v>47</v>
@@ -21481,7 +21481,7 @@
         <v>34</v>
       </c>
       <c r="E337" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F337" t="s">
         <v>208</v>
@@ -21493,13 +21493,13 @@
         <v>638</v>
       </c>
       <c r="I337" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J337" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K337" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L337" t="s">
         <v>34</v>
@@ -21511,10 +21511,10 @@
         <v>47</v>
       </c>
       <c r="O337" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="P337" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="Q337" t="s">
         <v>47</v>
@@ -21537,7 +21537,7 @@
         <v>34</v>
       </c>
       <c r="E338" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F338" t="s">
         <v>208</v>
@@ -21549,13 +21549,13 @@
         <v>638</v>
       </c>
       <c r="I338" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="J338" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K338" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L338" t="s">
         <v>34</v>
@@ -21567,10 +21567,10 @@
         <v>47</v>
       </c>
       <c r="O338" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="P338" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="Q338" t="s">
         <v>47</v>
@@ -21593,7 +21593,7 @@
         <v>34</v>
       </c>
       <c r="E339" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F339" t="s">
         <v>208</v>
@@ -21605,13 +21605,13 @@
         <v>638</v>
       </c>
       <c r="I339" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="J339" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K339" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L339" t="s">
         <v>34</v>
@@ -21623,10 +21623,10 @@
         <v>47</v>
       </c>
       <c r="O339" t="s">
-        <v>694</v>
+        <v>677</v>
       </c>
       <c r="P339" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="Q339" t="s">
         <v>47</v>
@@ -21649,7 +21649,7 @@
         <v>34</v>
       </c>
       <c r="E340" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F340" t="s">
         <v>208</v>
@@ -21661,13 +21661,13 @@
         <v>638</v>
       </c>
       <c r="I340" t="s">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="J340" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K340" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L340" t="s">
         <v>34</v>
@@ -21679,10 +21679,10 @@
         <v>47</v>
       </c>
       <c r="O340" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="P340" t="s">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="Q340" t="s">
         <v>47</v>
@@ -21705,7 +21705,7 @@
         <v>34</v>
       </c>
       <c r="E341" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="F341" t="s">
         <v>208</v>
@@ -21717,13 +21717,13 @@
         <v>638</v>
       </c>
       <c r="I341" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="J341" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="K341" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="L341" t="s">
         <v>34</v>
@@ -21735,10 +21735,10 @@
         <v>47</v>
       </c>
       <c r="O341" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="P341" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="Q341" t="s">
         <v>47</v>
@@ -21761,7 +21761,7 @@
         <v>34</v>
       </c>
       <c r="E342" t="s">
-        <v>134</v>
+        <v>698</v>
       </c>
       <c r="F342" t="s">
         <v>208</v>
@@ -21773,13 +21773,13 @@
         <v>638</v>
       </c>
       <c r="I342" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="J342" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K342" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L342" t="s">
         <v>34</v>
@@ -21791,10 +21791,10 @@
         <v>47</v>
       </c>
       <c r="O342" t="s">
-        <v>137</v>
+        <v>700</v>
       </c>
       <c r="P342" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="Q342" t="s">
         <v>47</v>
@@ -21817,7 +21817,7 @@
         <v>34</v>
       </c>
       <c r="E343" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F343" t="s">
         <v>208</v>
@@ -21829,13 +21829,13 @@
         <v>638</v>
       </c>
       <c r="I343" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="J343" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="K343" t="s">
-        <v>124</v>
+        <v>683</v>
       </c>
       <c r="L343" t="s">
         <v>34</v>
@@ -21847,10 +21847,10 @@
         <v>47</v>
       </c>
       <c r="O343" t="s">
-        <v>126</v>
+        <v>703</v>
       </c>
       <c r="P343" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="Q343" t="s">
         <v>47</v>
@@ -25811,7 +25811,7 @@
         <v>179</v>
       </c>
       <c r="K414" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L414" t="s">
         <v>874</v>
@@ -26427,7 +26427,7 @@
         <v>369</v>
       </c>
       <c r="K425" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="L425" t="s">
         <v>912</v>
@@ -33144,10 +33144,10 @@
         <v>100</v>
       </c>
       <c r="J545" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K545" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L545" t="s">
         <v>1097</v>
